--- a/research/traditional_assets/database/data/japan/japan_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ40"/>
+  <dimension ref="A1:AQ39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.064</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="E2">
-        <v>0.07215000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="F2">
-        <v>0.241</v>
+        <v>0.2095</v>
       </c>
       <c r="G2">
-        <v>0.1619028405957809</v>
+        <v>0.1750730845703707</v>
       </c>
       <c r="H2">
-        <v>0.1618799298112396</v>
+        <v>0.1750677081203505</v>
       </c>
       <c r="I2">
-        <v>0.09664802881352501</v>
+        <v>0.07444894022797564</v>
       </c>
       <c r="J2">
-        <v>0.07284269953049276</v>
+        <v>0.05251519384081224</v>
       </c>
       <c r="K2">
-        <v>18930.871</v>
+        <v>18455.436</v>
       </c>
       <c r="L2">
-        <v>0.1901451585524723</v>
+        <v>0.1827343080187029</v>
       </c>
       <c r="M2">
-        <v>3213.20049</v>
+        <v>2586.4135</v>
       </c>
       <c r="N2">
-        <v>0.04234548079482766</v>
+        <v>0.03939838714836925</v>
       </c>
       <c r="O2">
-        <v>0.1697333677885186</v>
+        <v>0.140143722424114</v>
       </c>
       <c r="P2">
-        <v>2207.19849</v>
+        <v>1886.7505</v>
       </c>
       <c r="Q2">
-        <v>0.02908778383407617</v>
+        <v>0.02874054231907592</v>
       </c>
       <c r="R2">
-        <v>0.1165925482245376</v>
+        <v>0.1022327784615871</v>
       </c>
       <c r="S2">
-        <v>1006.002</v>
+        <v>699.6629999999999</v>
       </c>
       <c r="T2">
-        <v>0.3130841051253543</v>
+        <v>0.2705147494783799</v>
       </c>
       <c r="U2">
-        <v>46846.29</v>
+        <v>40262.54</v>
       </c>
       <c r="V2">
-        <v>0.6173684709925857</v>
+        <v>0.613312271412403</v>
       </c>
       <c r="W2">
-        <v>0.0925706228848002</v>
+        <v>0.07342439903072931</v>
       </c>
       <c r="X2">
-        <v>0.0308614332865555</v>
+        <v>0.06074352519534205</v>
       </c>
       <c r="Y2">
-        <v>0.0617091895982447</v>
+        <v>0.01268087383538725</v>
       </c>
       <c r="Z2">
-        <v>0.06937949816486237</v>
+        <v>0.07054458529169601</v>
       </c>
       <c r="AA2">
-        <v>0.03289648402193373</v>
+        <v>0.02592517798027897</v>
       </c>
       <c r="AB2">
-        <v>0.02612886793308659</v>
+        <v>0.05142642338193332</v>
       </c>
       <c r="AC2">
-        <v>0.006182103742701943</v>
+        <v>-0.02917092292872446</v>
       </c>
       <c r="AD2">
-        <v>1358096.836</v>
+        <v>1115833.209</v>
       </c>
       <c r="AE2">
-        <v>2732.212932612851</v>
+        <v>2191.155441229852</v>
       </c>
       <c r="AF2">
-        <v>1360829.048932613</v>
+        <v>1118024.36444123</v>
       </c>
       <c r="AG2">
-        <v>1313982.758932613</v>
+        <v>1077761.82444123</v>
       </c>
       <c r="AH2">
-        <v>0.9471844571682422</v>
+        <v>0.9445389462401566</v>
       </c>
       <c r="AI2">
-        <v>0.9170163041798799</v>
+        <v>0.9117614983642617</v>
       </c>
       <c r="AJ2">
-        <v>0.945404273368085</v>
+        <v>0.9425860126256328</v>
       </c>
       <c r="AK2">
-        <v>0.9143112723308147</v>
+        <v>0.9087658660686911</v>
       </c>
       <c r="AL2">
-        <v>760.138</v>
+        <v>715.349</v>
       </c>
       <c r="AM2">
-        <v>598.8480000000001</v>
+        <v>576.635</v>
       </c>
       <c r="AN2">
-        <v>72.39987491387799</v>
+        <v>71.51372377886806</v>
       </c>
       <c r="AO2">
-        <v>12.68397843549461</v>
+        <v>10.41201707138753</v>
       </c>
       <c r="AP2">
-        <v>70.04816215160778</v>
+        <v>69.07372964958869</v>
       </c>
       <c r="AQ2">
-        <v>16.10020238858608</v>
+        <v>12.9167081429327</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Casa Inc. (TSE:7196)</t>
+          <t>J Trust Co., Ltd. (TSE:8508)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,119 +724,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0745</v>
-      </c>
-      <c r="E3">
-        <v>-0.0678</v>
-      </c>
       <c r="G3">
-        <v>0.1419213973799127</v>
+        <v>0.166383701188455</v>
       </c>
       <c r="H3">
-        <v>0.1419213973799127</v>
+        <v>0.166383701188455</v>
       </c>
       <c r="I3">
-        <v>0.1146288209606987</v>
+        <v>0.1621392190152801</v>
       </c>
       <c r="J3">
-        <v>0.06799826175435622</v>
+        <v>0.1372354827612992</v>
       </c>
       <c r="K3">
-        <v>6.08</v>
+        <v>74</v>
       </c>
       <c r="L3">
-        <v>0.06637554585152838</v>
+        <v>0.1570458404074703</v>
       </c>
       <c r="M3">
-        <v>2.61159</v>
+        <v>0.8449000000000001</v>
       </c>
       <c r="N3">
-        <v>0.03248246268656716</v>
+        <v>0.001842748091603054</v>
       </c>
       <c r="O3">
-        <v>0.4295378289473684</v>
+        <v>0.01141756756756757</v>
       </c>
       <c r="P3">
-        <v>2.61159</v>
+        <v>0.8169000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.03248246268656716</v>
+        <v>0.001781679389312977</v>
       </c>
       <c r="R3">
-        <v>0.4295378289473684</v>
+        <v>0.01103918918918919</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.02800000000000002</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.03314001657000831</v>
       </c>
       <c r="U3">
-        <v>21</v>
+        <v>673.8</v>
       </c>
       <c r="V3">
-        <v>0.2611940298507462</v>
+        <v>1.469574700109051</v>
       </c>
       <c r="W3">
-        <v>0.09411764705882354</v>
+        <v>0.08593659273022877</v>
       </c>
       <c r="X3">
-        <v>0.02434444226676222</v>
+        <v>0.05423779239503952</v>
       </c>
       <c r="Y3">
-        <v>0.06977320479206132</v>
-      </c>
-      <c r="Z3">
-        <v>57.2500000000002</v>
-      </c>
-      <c r="AA3">
-        <v>3.892900485436907</v>
+        <v>0.03169880033518925</v>
       </c>
       <c r="AB3">
-        <v>0.02431848960859521</v>
-      </c>
-      <c r="AC3">
-        <v>3.868581995828312</v>
+        <v>0.05248662215712567</v>
       </c>
       <c r="AD3">
-        <v>0.526</v>
+        <v>221.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.526</v>
+        <v>221.8</v>
       </c>
       <c r="AG3">
-        <v>-20.474</v>
+        <v>-451.9999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.006499765217606208</v>
+        <v>0.3260326326620609</v>
       </c>
       <c r="AI3">
-        <v>0.008453058207180278</v>
+        <v>0.191256359403294</v>
       </c>
       <c r="AJ3">
-        <v>-0.3416547074725494</v>
+        <v>-69.53846153846092</v>
       </c>
       <c r="AK3">
-        <v>-0.4966283413379906</v>
+        <v>-0.9302325581395346</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.026</v>
+        <v>-14.3</v>
       </c>
       <c r="AN3">
-        <v>0.03925373134328358</v>
+        <v>2.215784215784216</v>
       </c>
       <c r="AP3">
-        <v>-1.527910447761194</v>
+        <v>-4.515484515484515</v>
       </c>
       <c r="AQ3">
-        <v>-403.8461538461539</v>
+        <v>-5.342657342657342</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZENKOKU HOSHO Co.,Ltd. (TSE:7164)</t>
+          <t>eGuarantee, Inc. (TSE:8771)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +841,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0762</v>
+        <v>0.111</v>
       </c>
       <c r="E4">
-        <v>0.1</v>
+        <v>0.139</v>
       </c>
       <c r="G4">
-        <v>0.7992198256080771</v>
+        <v>0.5537918871252204</v>
       </c>
       <c r="H4">
-        <v>0.7992198256080771</v>
+        <v>0.5537918871252204</v>
       </c>
       <c r="I4">
-        <v>0.820100963744837</v>
+        <v>0.4814814814814815</v>
       </c>
       <c r="J4">
-        <v>0.567225240986613</v>
+        <v>0.3391304347826086</v>
       </c>
       <c r="K4">
-        <v>251.9</v>
+        <v>18.6</v>
       </c>
       <c r="L4">
-        <v>0.5780174391922901</v>
+        <v>0.328042328042328</v>
       </c>
       <c r="M4">
-        <v>3.98</v>
+        <v>8.513999999999999</v>
       </c>
       <c r="N4">
-        <v>0.001329636187485384</v>
+        <v>0.009724728726442032</v>
       </c>
       <c r="O4">
-        <v>0.01579992060341405</v>
+        <v>0.4577419354838709</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>8.513999999999999</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.009724728726442032</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.4577419354838709</v>
       </c>
       <c r="S4">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1407.9</v>
+        <v>108.5</v>
       </c>
       <c r="V4">
-        <v>0.4703504493368523</v>
+        <v>0.123929183323815</v>
       </c>
       <c r="W4">
-        <v>0.1787158566867684</v>
+        <v>0.123015873015873</v>
       </c>
       <c r="X4">
-        <v>0.02487645734324034</v>
+        <v>0.05005596463140148</v>
       </c>
       <c r="Y4">
-        <v>0.153839399343528</v>
+        <v>0.07295990838447156</v>
       </c>
       <c r="Z4">
-        <v>2.797175866495504</v>
+        <v>7.0875</v>
       </c>
       <c r="AA4">
-        <v>1.58662875495485</v>
+        <v>2.403586956521739</v>
       </c>
       <c r="AB4">
-        <v>0.024503348914165</v>
+        <v>0.05005596463140148</v>
       </c>
       <c r="AC4">
-        <v>1.562125406040685</v>
+        <v>2.353530991890338</v>
       </c>
       <c r="AD4">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-1138.9</v>
+        <v>-108.5</v>
       </c>
       <c r="AH4">
-        <v>0.08245716212488122</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.1513276327632763</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.6141609145815359</v>
+        <v>-0.1414602346805737</v>
       </c>
       <c r="AK4">
-        <v>-3.08060589667298</v>
+        <v>-3.422712933753945</v>
       </c>
       <c r="AL4">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-7.94</v>
+        <v>-0.124</v>
       </c>
       <c r="AN4">
-        <v>0.7470147181338517</v>
-      </c>
-      <c r="AO4">
-        <v>50.62322946175637</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>-3.162732574284921</v>
+        <v>-3.888888888888889</v>
       </c>
       <c r="AQ4">
-        <v>-45.01259445843828</v>
+        <v>-220.1612903225806</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Uzabase, Inc. (TSE:3966)</t>
+          <t>Entrust Inc. (TSE:7191)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,25 +972,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.274</v>
+        <v>0.144</v>
+      </c>
+      <c r="E5">
+        <v>0.118</v>
       </c>
       <c r="G5">
-        <v>0.06354538956397426</v>
+        <v>0.2623376623376623</v>
       </c>
       <c r="H5">
-        <v>0.06354538956397426</v>
+        <v>0.2623376623376623</v>
       </c>
       <c r="I5">
-        <v>0.1193709792709078</v>
+        <v>0.2462337662337662</v>
       </c>
       <c r="J5">
-        <v>0.1193709792709078</v>
+        <v>0.1591734782789096</v>
       </c>
       <c r="K5">
-        <v>0.771</v>
+        <v>6.08</v>
       </c>
       <c r="L5">
-        <v>0.005511079342387419</v>
+        <v>0.1579220779220779</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1032,73 +1017,70 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>82.90000000000001</v>
+        <v>26.8</v>
       </c>
       <c r="V5">
-        <v>0.1767967583706548</v>
+        <v>0.1932227829848594</v>
       </c>
       <c r="W5">
-        <v>0.01384201077199282</v>
+        <v>0.1617021276595745</v>
       </c>
       <c r="X5">
-        <v>0.02475474134525219</v>
+        <v>0.05005596463140148</v>
       </c>
       <c r="Y5">
-        <v>-0.01091273057325937</v>
+        <v>0.111646163028173</v>
       </c>
       <c r="Z5">
-        <v>8.049482163406216</v>
+        <v>4.277777777777778</v>
       </c>
       <c r="AA5">
-        <v>0.9608745684695054</v>
+        <v>0.6809087681931133</v>
       </c>
       <c r="AB5">
-        <v>0.02467543994363327</v>
+        <v>0.05005596463140148</v>
       </c>
       <c r="AC5">
-        <v>0.9361991285258721</v>
+        <v>0.6308528035617118</v>
       </c>
       <c r="AD5">
-        <v>33.2</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>33.2</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-49.7</v>
+        <v>-26.8</v>
       </c>
       <c r="AH5">
-        <v>0.06612228639713205</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.2948490230905861</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.1185591603053435</v>
+        <v>-0.2394995531724755</v>
       </c>
       <c r="AK5">
-        <v>-1.673400673400673</v>
+        <v>-4.187499999999999</v>
       </c>
       <c r="AL5">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.134</v>
+        <v>-0.035</v>
       </c>
       <c r="AN5">
-        <v>1.389121338912134</v>
-      </c>
-      <c r="AO5">
-        <v>93.29608938547486</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>-2.079497907949791</v>
+        <v>-2.688064192577733</v>
       </c>
       <c r="AQ5">
-        <v>124.6268656716418</v>
+        <v>-270.8571428571428</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Entrust Inc. (TSE:7191)</t>
+          <t>ZENKOKU HOSHO Co.,Ltd. (TSE:7164)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,32 +1099,38 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.0619</v>
+      </c>
+      <c r="E6">
+        <v>0.06570000000000001</v>
+      </c>
       <c r="G6">
-        <v>0.2604422604422604</v>
+        <v>0.9520488230165649</v>
       </c>
       <c r="H6">
-        <v>0.2604422604422604</v>
+        <v>0.9520488230165649</v>
       </c>
       <c r="I6">
-        <v>0.257985257985258</v>
+        <v>0.7974426038942167</v>
       </c>
       <c r="J6">
-        <v>0.1660933660933661</v>
+        <v>0.5513358052464804</v>
       </c>
       <c r="K6">
-        <v>6.74</v>
+        <v>195</v>
       </c>
       <c r="L6">
-        <v>0.1656019656019656</v>
+        <v>0.5666957279860505</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.007</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>2.657151533556028e-06</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>3.58974358974359e-05</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1154,73 +1142,79 @@
         <v>-0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.007</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>28.6</v>
+        <v>968.7</v>
       </c>
       <c r="V6">
-        <v>0.1956224350205198</v>
+        <v>0.367711812936532</v>
       </c>
       <c r="W6">
-        <v>0.1936781609195403</v>
+        <v>0.1292589155508418</v>
       </c>
       <c r="X6">
-        <v>0.02430267097692251</v>
+        <v>0.05073620362604647</v>
       </c>
       <c r="Y6">
-        <v>0.1693754899426178</v>
+        <v>0.07852271192479537</v>
       </c>
       <c r="Z6">
-        <v>5.732394366197185</v>
+        <v>0.9307546659453616</v>
       </c>
       <c r="AA6">
-        <v>0.9521126760563383</v>
+        <v>0.5131583732359047</v>
       </c>
       <c r="AB6">
-        <v>0.02430267097692251</v>
+        <v>0.05016842751905451</v>
       </c>
       <c r="AC6">
-        <v>0.9278100050794158</v>
+        <v>0.4629899457168503</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>207.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>207.3</v>
       </c>
       <c r="AG6">
-        <v>-28.6</v>
+        <v>-761.4000000000001</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.07294929091740859</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.1372484110169492</v>
       </c>
       <c r="AJ6">
-        <v>-0.2431972789115646</v>
+        <v>-0.406513614522157</v>
       </c>
       <c r="AK6">
-        <v>-3.177777777777778</v>
+        <v>-1.405575041535906</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AM6">
-        <v>-0.027</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>0.7491868449584388</v>
+      </c>
+      <c r="AO6">
+        <v>50.44117647058822</v>
       </c>
       <c r="AP6">
-        <v>-2.672897196261683</v>
+        <v>-2.751716660643297</v>
       </c>
       <c r="AQ6">
-        <v>-388.8888888888889</v>
+        <v>-30.9706546275395</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eGuarantee, Inc. (TSE:8771)</t>
+          <t>Anshin Guarantor Service Co., Ltd. (TSE:7183)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1240,118 +1234,118 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.111</v>
+        <v>0.116</v>
       </c>
       <c r="E7">
-        <v>0.136</v>
+        <v>0.195</v>
       </c>
       <c r="G7">
-        <v>0.4191176470588235</v>
+        <v>0.1516778523489933</v>
       </c>
       <c r="H7">
-        <v>0.4191176470588235</v>
+        <v>0.1516778523489933</v>
       </c>
       <c r="I7">
-        <v>0.4470588235294117</v>
+        <v>0.1130872483221477</v>
       </c>
       <c r="J7">
-        <v>0.3181835600689787</v>
+        <v>0.07737548569410102</v>
       </c>
       <c r="K7">
-        <v>19.8</v>
+        <v>2.86</v>
       </c>
       <c r="L7">
-        <v>0.2911764705882353</v>
+        <v>0.0959731543624161</v>
       </c>
       <c r="M7">
-        <v>9.199900000000001</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.009797550585729502</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.4646414141414142</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>9.199900000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.009797550585729502</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.4646414141414142</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>143.2</v>
+        <v>9.49</v>
       </c>
       <c r="V7">
-        <v>0.1525026624068158</v>
+        <v>0.2696022727272727</v>
       </c>
       <c r="W7">
-        <v>0.1423436376707405</v>
+        <v>0.2057553956834532</v>
       </c>
       <c r="X7">
-        <v>0.02430267097692251</v>
+        <v>0.05056432492493605</v>
       </c>
       <c r="Y7">
-        <v>0.118040966693818</v>
+        <v>0.1551910707585172</v>
       </c>
       <c r="Z7">
-        <v>2.730923694779118</v>
+        <v>6.094069529652351</v>
       </c>
       <c r="AA7">
-        <v>0.8689350234815486</v>
+        <v>0.4715315897104724</v>
       </c>
       <c r="AB7">
-        <v>0.02430267097692251</v>
+        <v>0.05014158934036884</v>
       </c>
       <c r="AC7">
-        <v>0.8446323525046261</v>
+        <v>0.4213900003701036</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG7">
-        <v>-143.2</v>
+        <v>-7.42</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.05554064931580359</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.1355599214145383</v>
       </c>
       <c r="AJ7">
-        <v>-0.1799447097260618</v>
+        <v>-0.2670986321094312</v>
       </c>
       <c r="AK7">
-        <v>-7.65775401069518</v>
+        <v>-1.283737024221453</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="AM7">
-        <v>-0.117</v>
+        <v>0.097</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>0.5175</v>
+      </c>
+      <c r="AO7">
+        <v>34.74226804123711</v>
       </c>
       <c r="AP7">
-        <v>-4.619354838709677</v>
+        <v>-1.855</v>
       </c>
       <c r="AQ7">
-        <v>-259.8290598290598</v>
+        <v>34.74226804123711</v>
       </c>
     </row>
     <row r="8">
@@ -1370,116 +1364,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.171</v>
+      </c>
+      <c r="E8">
+        <v>0.711</v>
+      </c>
       <c r="G8">
-        <v>0.131578947368421</v>
+        <v>0.255043227665706</v>
       </c>
       <c r="H8">
-        <v>0.131578947368421</v>
+        <v>0.255043227665706</v>
       </c>
       <c r="I8">
-        <v>0.1763157894736842</v>
+        <v>0.2291066282420749</v>
       </c>
       <c r="J8">
-        <v>0.114268782643632</v>
+        <v>0.1602296355743625</v>
       </c>
       <c r="K8">
-        <v>8.449999999999999</v>
+        <v>11</v>
       </c>
       <c r="L8">
-        <v>0.1111842105263158</v>
+        <v>0.1585014409221902</v>
       </c>
       <c r="M8">
-        <v>1.5931</v>
+        <v>4.015779999999999</v>
       </c>
       <c r="N8">
-        <v>0.01059946773120426</v>
+        <v>0.02062547508988187</v>
       </c>
       <c r="O8">
-        <v>0.1885325443786982</v>
+        <v>0.3650709090909091</v>
       </c>
       <c r="P8">
-        <v>1.5931</v>
+        <v>3.08978</v>
       </c>
       <c r="Q8">
-        <v>0.01059946773120426</v>
+        <v>0.01586944016435542</v>
       </c>
       <c r="R8">
-        <v>0.1885325443786982</v>
+        <v>0.2808890909090909</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.9259999999999997</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.2305903211829333</v>
       </c>
       <c r="U8">
-        <v>10.5</v>
+        <v>7.42</v>
       </c>
       <c r="V8">
-        <v>0.06986027944111776</v>
+        <v>0.03810991268618388</v>
       </c>
       <c r="W8">
-        <v>1.057571964956195</v>
+        <v>0.7006369426751593</v>
       </c>
       <c r="X8">
-        <v>0.02531795396866271</v>
+        <v>0.05064203790848056</v>
       </c>
       <c r="Y8">
-        <v>1.032254010987532</v>
+        <v>0.6499949047666788</v>
       </c>
       <c r="Z8">
-        <v>2.436678422571337</v>
+        <v>2.384879725085912</v>
       </c>
       <c r="AA8">
-        <v>0.2784362770412322</v>
+        <v>0.3821284092392014</v>
       </c>
       <c r="AB8">
-        <v>0.02507613770721326</v>
+        <v>0.05052931437155067</v>
       </c>
       <c r="AC8">
-        <v>0.2533601393340189</v>
+        <v>0.3315990948676508</v>
       </c>
       <c r="AD8">
-        <v>23.9</v>
+        <v>13.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>23.9</v>
+        <v>13.2</v>
       </c>
       <c r="AG8">
-        <v>13.4</v>
+        <v>5.779999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.1371986222732491</v>
+        <v>0.0634920634920635</v>
       </c>
       <c r="AI8">
-        <v>0.6035353535353536</v>
+        <v>0.4012158054711246</v>
       </c>
       <c r="AJ8">
-        <v>0.08185705558949295</v>
+        <v>0.02883080606544294</v>
       </c>
       <c r="AK8">
-        <v>0.4604810996563574</v>
+        <v>0.2268445839874411</v>
       </c>
       <c r="AL8">
-        <v>0.269</v>
+        <v>0.159</v>
       </c>
       <c r="AM8">
-        <v>0.269</v>
+        <v>0.159</v>
       </c>
       <c r="AN8">
-        <v>1.593333333333333</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="AO8">
-        <v>49.81412639405205</v>
+        <v>100</v>
       </c>
       <c r="AP8">
-        <v>0.8933333333333332</v>
+        <v>0.3360465116279069</v>
       </c>
       <c r="AQ8">
-        <v>49.81412639405205</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MINKABU THE INFONOID, Inc. (TSE:4436)</t>
+          <t>Japan Exchange Group, Inc. (TSE:8697)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1498,116 +1498,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.0425</v>
+      </c>
+      <c r="E9">
+        <v>0.0144</v>
+      </c>
       <c r="G9">
-        <v>0.2685185185185185</v>
+        <v>0.785532456512516</v>
       </c>
       <c r="H9">
-        <v>0.2685185185185185</v>
+        <v>0.785532456512516</v>
       </c>
       <c r="I9">
-        <v>0.178989177884593</v>
+        <v>0.5156979210861264</v>
       </c>
       <c r="J9">
-        <v>0.1472159510411741</v>
+        <v>0.3569815030424198</v>
       </c>
       <c r="K9">
-        <v>5.22</v>
+        <v>335.8</v>
       </c>
       <c r="L9">
-        <v>0.1208333333333333</v>
+        <v>0.3561731014000849</v>
       </c>
       <c r="M9">
-        <v>2.3989</v>
+        <v>221.2198</v>
       </c>
       <c r="N9">
-        <v>0.006744166432386844</v>
+        <v>0.02918929118066185</v>
       </c>
       <c r="O9">
-        <v>0.4595593869731802</v>
+        <v>0.6587843954734962</v>
       </c>
       <c r="P9">
-        <v>2.3989</v>
+        <v>207.5198</v>
       </c>
       <c r="Q9">
-        <v>0.006744166432386844</v>
+        <v>0.02738161714255555</v>
       </c>
       <c r="R9">
-        <v>0.4595593869731802</v>
+        <v>0.6179863013698631</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>13.69999999999999</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.06192935713710973</v>
       </c>
       <c r="U9">
-        <v>38.1</v>
+        <v>692</v>
       </c>
       <c r="V9">
-        <v>0.1071127354512229</v>
+        <v>0.09130733097588009</v>
       </c>
       <c r="W9">
-        <v>0.1591463414634146</v>
+        <v>0.1234014405409378</v>
       </c>
       <c r="X9">
-        <v>0.02456632655895177</v>
+        <v>0.05047354802776965</v>
       </c>
       <c r="Y9">
-        <v>0.1345800149044629</v>
+        <v>0.0729278925131682</v>
       </c>
       <c r="Z9">
-        <v>1.887424102113331</v>
+        <v>0.5056854752199098</v>
       </c>
       <c r="AA9">
-        <v>0.2778589342106481</v>
+        <v>0.1805203610107237</v>
       </c>
       <c r="AB9">
-        <v>0.02452623773497548</v>
+        <v>0.05012700405832073</v>
       </c>
       <c r="AC9">
-        <v>0.2533326964756726</v>
+        <v>0.130393356952403</v>
       </c>
       <c r="AD9">
-        <v>13.9</v>
+        <v>366.1</v>
       </c>
       <c r="AE9">
-        <v>0.7883375769279256</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>14.68833757692793</v>
+        <v>366.1</v>
       </c>
       <c r="AG9">
-        <v>-23.41166242307207</v>
+        <v>-325.9</v>
       </c>
       <c r="AH9">
-        <v>0.03965658765883045</v>
+        <v>0.04607987514002693</v>
       </c>
       <c r="AI9">
-        <v>0.1787155940851061</v>
+        <v>0.1414277988101677</v>
       </c>
       <c r="AJ9">
-        <v>-0.07045586551063367</v>
+        <v>-0.04493375063767596</v>
       </c>
       <c r="AK9">
-        <v>-0.5310171285597246</v>
+        <v>-0.1718338078667088</v>
       </c>
       <c r="AL9">
-        <v>0.108</v>
+        <v>0.629</v>
       </c>
       <c r="AM9">
-        <v>0.108</v>
+        <v>0.249</v>
       </c>
       <c r="AN9">
-        <v>1.045112781954887</v>
+        <v>0.5983003758784116</v>
       </c>
       <c r="AO9">
-        <v>66.57407407407408</v>
+        <v>772.9729729729729</v>
       </c>
       <c r="AP9">
-        <v>-1.760275370155795</v>
+        <v>-0.5326033665631639</v>
       </c>
       <c r="AQ9">
-        <v>66.57407407407408</v>
+        <v>1952.610441767068</v>
       </c>
     </row>
     <row r="10">
@@ -1618,7 +1624,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Japan Exchange Group, Inc. (TSE:8697)</t>
+          <t>Casa Inc. (TSE:7196)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1627,121 +1633,118 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0424</v>
+        <v>0.052</v>
       </c>
       <c r="E10">
-        <v>0.05139999999999999</v>
+        <v>0.0139</v>
       </c>
       <c r="G10">
-        <v>0.665482485128883</v>
+        <v>0.174992700729927</v>
       </c>
       <c r="H10">
-        <v>0.665482485128883</v>
+        <v>0.1737226277372263</v>
       </c>
       <c r="I10">
-        <v>0.5478354263053535</v>
+        <v>0.06481751824817519</v>
       </c>
       <c r="J10">
-        <v>0.3832340543089864</v>
+        <v>0.0324087591240876</v>
       </c>
       <c r="K10">
-        <v>467.7</v>
+        <v>2.16</v>
       </c>
       <c r="L10">
-        <v>0.3864011896893588</v>
+        <v>0.03153284671532847</v>
       </c>
       <c r="M10">
-        <v>456.6</v>
+        <v>2.00182</v>
       </c>
       <c r="N10">
-        <v>0.03957907146076766</v>
+        <v>0.03028472012102875</v>
       </c>
       <c r="O10">
-        <v>0.976266837716485</v>
+        <v>0.9267685185185186</v>
       </c>
       <c r="P10">
-        <v>274.3</v>
+        <v>2.00182</v>
       </c>
       <c r="Q10">
-        <v>0.02377691480877917</v>
+        <v>0.03028472012102875</v>
       </c>
       <c r="R10">
-        <v>0.5864870643574942</v>
+        <v>0.9267685185185186</v>
       </c>
       <c r="S10">
-        <v>182.3</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.3992553657468244</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>723.1</v>
+        <v>19.2</v>
       </c>
       <c r="V10">
-        <v>0.06267986546929719</v>
+        <v>0.2904689863842663</v>
       </c>
       <c r="W10">
-        <v>0.1610370829459766</v>
+        <v>0.03500810372771475</v>
       </c>
       <c r="X10">
-        <v>0.024562958207958</v>
+        <v>0.05009820668299488</v>
       </c>
       <c r="Y10">
-        <v>0.1364741247380186</v>
+        <v>-0.01509010295528013</v>
       </c>
       <c r="Z10">
-        <v>0.6187190103767315</v>
+        <v>5.38268112525538</v>
       </c>
       <c r="AA10">
-        <v>0.2371141948247187</v>
+        <v>0.1744460160301744</v>
       </c>
       <c r="AB10">
-        <v>0.0243979994339564</v>
+        <v>0.05006346136695353</v>
       </c>
       <c r="AC10">
-        <v>0.2127161953907623</v>
+        <v>0.1243825546632208</v>
       </c>
       <c r="AD10">
-        <v>470.3</v>
+        <v>0.323</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>470.3</v>
+        <v>0.323</v>
       </c>
       <c r="AG10">
-        <v>-252.8</v>
+        <v>-18.877</v>
       </c>
       <c r="AH10">
-        <v>0.03916979686341793</v>
+        <v>0.004862773436911914</v>
       </c>
       <c r="AI10">
-        <v>0.1442151421299561</v>
+        <v>0.006927911116830749</v>
       </c>
       <c r="AJ10">
-        <v>-0.02240419724201496</v>
+        <v>-0.3997416513139783</v>
       </c>
       <c r="AK10">
-        <v>-0.0996059889676911</v>
+        <v>-0.6883637822265981</v>
       </c>
       <c r="AL10">
-        <v>0.825</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1.195</v>
+        <v>-0.047</v>
       </c>
       <c r="AN10">
-        <v>0.5795440542205792</v>
-      </c>
-      <c r="AO10">
-        <v>803.7575757575759</v>
+        <v>0.04792284866468843</v>
       </c>
       <c r="AP10">
-        <v>-0.3115218730745533</v>
+        <v>-2.800741839762611</v>
       </c>
       <c r="AQ10">
-        <v>-554.8953974895397</v>
+        <v>-94.46808510638299</v>
       </c>
     </row>
     <row r="11">
@@ -1752,7 +1755,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Morningstar Japan K.K. (TSE:4765)</t>
+          <t>Premium Group Co., Ltd. (TSE:7199)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1761,121 +1764,118 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.108</v>
-      </c>
-      <c r="E11">
-        <v>0.0679</v>
+        <v>0.425</v>
       </c>
       <c r="G11">
-        <v>0.2957142857142857</v>
+        <v>0.2693538067818298</v>
       </c>
       <c r="H11">
-        <v>0.2957142857142857</v>
+        <v>0.2693538067818298</v>
       </c>
       <c r="I11">
-        <v>0.2414285714285714</v>
+        <v>0.1906589891234805</v>
       </c>
       <c r="J11">
-        <v>0.1675657708628005</v>
+        <v>0.1454271299850714</v>
       </c>
       <c r="K11">
-        <v>12.1</v>
+        <v>29.2</v>
       </c>
       <c r="L11">
-        <v>0.1728571428571428</v>
+        <v>0.1868202175303903</v>
       </c>
       <c r="M11">
-        <v>13.2756</v>
+        <v>4.9993</v>
       </c>
       <c r="N11">
-        <v>0.02646650717703349</v>
+        <v>0.009794866771159875</v>
       </c>
       <c r="O11">
-        <v>1.097157024793388</v>
+        <v>0.171208904109589</v>
       </c>
       <c r="P11">
-        <v>13.2756</v>
+        <v>4.9923</v>
       </c>
       <c r="Q11">
-        <v>0.02646650717703349</v>
+        <v>0.009781152037617556</v>
       </c>
       <c r="R11">
-        <v>1.097157024793388</v>
+        <v>0.1709691780821918</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>0.006999999999999673</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.001400196027443777</v>
       </c>
       <c r="U11">
-        <v>38.3</v>
+        <v>81.5</v>
       </c>
       <c r="V11">
-        <v>0.07635566188197766</v>
+        <v>0.1596786833855799</v>
       </c>
       <c r="W11">
-        <v>0.1411901983663944</v>
+        <v>0.3940620782726046</v>
       </c>
       <c r="X11">
-        <v>0.02431641818221296</v>
+        <v>0.05277602670508636</v>
       </c>
       <c r="Y11">
-        <v>0.1168737801841814</v>
+        <v>0.3412860515675182</v>
       </c>
       <c r="Z11">
-        <v>1.320754716981132</v>
+        <v>1.154357459379616</v>
       </c>
       <c r="AA11">
-        <v>0.2213132822716233</v>
+        <v>0.1678748922944363</v>
       </c>
       <c r="AB11">
-        <v>0.02430789979333227</v>
+        <v>0.0518403379551278</v>
       </c>
       <c r="AC11">
-        <v>0.197005382478291</v>
+        <v>0.1160345543393085</v>
       </c>
       <c r="AD11">
-        <v>1.08</v>
+        <v>160.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.08</v>
+        <v>160.6</v>
       </c>
       <c r="AG11">
-        <v>-37.22</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.00214848412508952</v>
+        <v>0.239344262295082</v>
       </c>
       <c r="AI11">
-        <v>0.00915409391422275</v>
+        <v>0.6547085201793721</v>
       </c>
       <c r="AJ11">
-        <v>-0.08014987725569576</v>
+        <v>0.1341815097540288</v>
       </c>
       <c r="AK11">
-        <v>-0.4671184738955823</v>
+        <v>0.4829059829059829</v>
       </c>
       <c r="AL11">
-        <v>0.018</v>
+        <v>0.263</v>
       </c>
       <c r="AM11">
-        <v>-3.222</v>
+        <v>0.242</v>
       </c>
       <c r="AN11">
-        <v>0.04931506849315069</v>
+        <v>4.096938775510203</v>
       </c>
       <c r="AO11">
-        <v>938.8888888888889</v>
+        <v>113.3079847908745</v>
       </c>
       <c r="AP11">
-        <v>-1.699543378995434</v>
+        <v>2.017857142857142</v>
       </c>
       <c r="AQ11">
-        <v>-5.245189323401613</v>
+        <v>123.1404958677686</v>
       </c>
     </row>
     <row r="12">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Money Partners Group Co.,Ltd. (TSE:8732)</t>
+          <t>Morningstar Japan K.K. (TSE:4765)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1895,43 +1895,46 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0366</v>
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="E12">
+        <v>0.0603</v>
       </c>
       <c r="G12">
-        <v>0.009868995633187773</v>
+        <v>0.3905429071803853</v>
       </c>
       <c r="H12">
-        <v>0.009868995633187773</v>
+        <v>0.3905429071803853</v>
       </c>
       <c r="I12">
-        <v>0.1004112280628038</v>
+        <v>0.2609457092819615</v>
       </c>
       <c r="J12">
-        <v>0.1004112280628038</v>
+        <v>0.1719259444583437</v>
       </c>
       <c r="K12">
-        <v>-1.15</v>
+        <v>10.1</v>
       </c>
       <c r="L12">
-        <v>-0.02510917030567686</v>
+        <v>0.1768826619964974</v>
       </c>
       <c r="M12">
-        <v>1.0846</v>
+        <v>10.6743</v>
       </c>
       <c r="N12">
-        <v>0.01832094594594594</v>
+        <v>0.03457823129251701</v>
       </c>
       <c r="O12">
-        <v>-0.9431304347826088</v>
+        <v>1.056861386138614</v>
       </c>
       <c r="P12">
-        <v>1.0846</v>
+        <v>10.6743</v>
       </c>
       <c r="Q12">
-        <v>0.01832094594594594</v>
+        <v>0.03457823129251701</v>
       </c>
       <c r="R12">
-        <v>-0.9431304347826088</v>
+        <v>1.056861386138614</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1940,73 +1943,70 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>89.2</v>
+        <v>18.1</v>
       </c>
       <c r="V12">
-        <v>1.506756756756757</v>
+        <v>0.05863297700032395</v>
       </c>
       <c r="W12">
-        <v>-0.009410801963993453</v>
+        <v>0.08993766696349065</v>
       </c>
       <c r="X12">
-        <v>0.02609363573173984</v>
+        <v>0.05005809287287737</v>
       </c>
       <c r="Y12">
-        <v>-0.03550443769573329</v>
+        <v>0.03987957409061328</v>
       </c>
       <c r="Z12">
-        <v>2.149646488134371</v>
+        <v>0.9616032334119233</v>
       </c>
       <c r="AA12">
-        <v>0.2158486437744656</v>
+        <v>0.1653245440985421</v>
       </c>
       <c r="AB12">
-        <v>0.02483579616254368</v>
+        <v>0.05005634408459395</v>
       </c>
       <c r="AC12">
-        <v>0.1910128476119219</v>
+        <v>0.1152682000139481</v>
       </c>
       <c r="AD12">
-        <v>15.1</v>
+        <v>0.076</v>
       </c>
       <c r="AE12">
-        <v>1.505828773617934</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>16.60582877361793</v>
+        <v>0.076</v>
       </c>
       <c r="AG12">
-        <v>-72.59417122638207</v>
+        <v>-18.024</v>
       </c>
       <c r="AH12">
-        <v>0.2190574134240865</v>
+        <v>0.0002461331191543384</v>
       </c>
       <c r="AI12">
-        <v>0.1266597292351618</v>
+        <v>0.000899663809839481</v>
       </c>
       <c r="AJ12">
-        <v>5.419833000446915</v>
+        <v>-0.06200718325558354</v>
       </c>
       <c r="AK12">
-        <v>-1.732316800570812</v>
+        <v>-0.271543931541521</v>
       </c>
       <c r="AL12">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>-0.179</v>
+        <v>-2.06</v>
       </c>
       <c r="AN12">
-        <v>1.463178294573643</v>
-      </c>
-      <c r="AO12">
-        <v>37.22222222222222</v>
+        <v>0.004</v>
       </c>
       <c r="AP12">
-        <v>-7.034318917285084</v>
+        <v>-0.9486315789473685</v>
       </c>
       <c r="AQ12">
-        <v>-18.71508379888268</v>
+        <v>-7.233009708737864</v>
       </c>
     </row>
     <row r="13">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Anshin Guarantor Service Co., Ltd. (TSE:7183)</t>
+          <t>MINKABU THE INFONOID, Inc. (TSE:4436)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2026,118 +2026,118 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.126</v>
-      </c>
-      <c r="E13">
-        <v>0.136</v>
+        <v>0.326</v>
       </c>
       <c r="G13">
-        <v>0.1879781420765027</v>
+        <v>0.312039312039312</v>
       </c>
       <c r="H13">
-        <v>0.1879781420765027</v>
+        <v>0.312039312039312</v>
       </c>
       <c r="I13">
-        <v>0.1456284153005464</v>
+        <v>0.1398454078639532</v>
       </c>
       <c r="J13">
-        <v>0.09814088857210737</v>
+        <v>0.1274869764713248</v>
       </c>
       <c r="K13">
-        <v>4.34</v>
+        <v>3.82</v>
       </c>
       <c r="L13">
-        <v>0.1185792349726776</v>
+        <v>0.09385749385749385</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>2.49</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.008302767589196401</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>0.6518324607329844</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>2.49</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.008302767589196401</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.6518324607329844</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>11.7</v>
+        <v>23.2</v>
       </c>
       <c r="V13">
-        <v>0.256578947368421</v>
+        <v>0.07735911970656886</v>
       </c>
       <c r="W13">
-        <v>0.1722222222222222</v>
+        <v>0.058678955453149</v>
       </c>
       <c r="X13">
-        <v>0.02467931894409338</v>
+        <v>0.0504197766584935</v>
       </c>
       <c r="Y13">
-        <v>0.1475429032781289</v>
+        <v>0.0082591787946555</v>
       </c>
       <c r="Z13">
-        <v>2.122969837587007</v>
+        <v>1.234775420074719</v>
       </c>
       <c r="AA13">
-        <v>0.2083501462725714</v>
+        <v>0.1574177849264358</v>
       </c>
       <c r="AB13">
-        <v>0.02461671241838867</v>
+        <v>0.05035705193017032</v>
       </c>
       <c r="AC13">
-        <v>0.1837334338541827</v>
+        <v>0.1070607329962655</v>
       </c>
       <c r="AD13">
-        <v>2.69</v>
+        <v>11.8</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>0.821459499685515</v>
       </c>
       <c r="AF13">
-        <v>2.69</v>
+        <v>12.62145949968552</v>
       </c>
       <c r="AG13">
-        <v>-9.01</v>
+        <v>-10.57854050031448</v>
       </c>
       <c r="AH13">
-        <v>0.05570511493062746</v>
+        <v>0.04038589708332722</v>
       </c>
       <c r="AI13">
-        <v>0.1621458710066305</v>
+        <v>0.2009100011397968</v>
       </c>
       <c r="AJ13">
-        <v>-0.2462421426619295</v>
+        <v>-0.03656327642825949</v>
       </c>
       <c r="AK13">
-        <v>-1.842535787321063</v>
+        <v>-0.2669901773910788</v>
       </c>
       <c r="AL13">
-        <v>0.09</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AM13">
-        <v>0.09</v>
+        <v>0.048</v>
       </c>
       <c r="AN13">
-        <v>0.4388254486133769</v>
+        <v>1.095025983667409</v>
       </c>
       <c r="AO13">
-        <v>59.22222222222223</v>
+        <v>73.47826086956522</v>
       </c>
       <c r="AP13">
-        <v>-1.469820554649266</v>
+        <v>-0.981675992976474</v>
       </c>
       <c r="AQ13">
-        <v>59.22222222222223</v>
+        <v>105.625</v>
       </c>
     </row>
     <row r="14">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mortgage Service Japan Limited (TSE:7192)</t>
+          <t>Money Partners Group Co.,Ltd. (TSE:8732)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2157,46 +2157,46 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.16</v>
+        <v>-0.00559</v>
       </c>
       <c r="E14">
-        <v>0.294</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="G14">
-        <v>0.2075187969924812</v>
+        <v>0.3203125000000001</v>
       </c>
       <c r="H14">
-        <v>0.2075187969924812</v>
+        <v>0.3203125000000001</v>
       </c>
       <c r="I14">
-        <v>0.2210526315789474</v>
+        <v>0.2254603150883679</v>
       </c>
       <c r="J14">
-        <v>0.1506766917293233</v>
+        <v>0.1522143243997611</v>
       </c>
       <c r="K14">
-        <v>9.92</v>
+        <v>5.31</v>
       </c>
       <c r="L14">
-        <v>0.1491729323308271</v>
+        <v>0.13828125</v>
       </c>
       <c r="M14">
-        <v>2.6313</v>
+        <v>0.8293999999999999</v>
       </c>
       <c r="N14">
-        <v>0.01813439007580979</v>
+        <v>0.01183166904422254</v>
       </c>
       <c r="O14">
-        <v>0.2652520161290323</v>
+        <v>0.156195856873823</v>
       </c>
       <c r="P14">
-        <v>2.6313</v>
+        <v>0.8293999999999999</v>
       </c>
       <c r="Q14">
-        <v>0.01813439007580979</v>
+        <v>0.01183166904422254</v>
       </c>
       <c r="R14">
-        <v>0.2652520161290323</v>
+        <v>0.156195856873823</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2205,70 +2205,73 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>39.4</v>
+        <v>60.6</v>
       </c>
       <c r="V14">
-        <v>0.2715368711233632</v>
+        <v>0.8644793152639088</v>
       </c>
       <c r="W14">
-        <v>0.1964356435643564</v>
+        <v>0.04637554585152838</v>
       </c>
       <c r="X14">
-        <v>0.02820572352054807</v>
+        <v>0.05206747837426871</v>
       </c>
       <c r="Y14">
-        <v>0.1682299200438084</v>
+        <v>-0.005691932522740334</v>
       </c>
       <c r="Z14">
-        <v>1.108333333333333</v>
+        <v>0.816819339685209</v>
       </c>
       <c r="AA14">
-        <v>0.167</v>
+        <v>0.124331603946843</v>
       </c>
       <c r="AB14">
-        <v>0.02522598696833148</v>
+        <v>0.05146326771328864</v>
       </c>
       <c r="AC14">
-        <v>0.1417740130316685</v>
+        <v>0.0728683362335544</v>
       </c>
       <c r="AD14">
-        <v>88.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>6.611619503033362</v>
       </c>
       <c r="AF14">
-        <v>88.7</v>
+        <v>16.31161950303336</v>
       </c>
       <c r="AG14">
-        <v>49.3</v>
+        <v>-44.28838049696664</v>
       </c>
       <c r="AH14">
-        <v>0.3793840889649273</v>
+        <v>0.1887665061347538</v>
       </c>
       <c r="AI14">
-        <v>0.610041265474553</v>
+        <v>0.1505989807730328</v>
       </c>
       <c r="AJ14">
-        <v>0.2536008230452675</v>
+        <v>-1.715831139218595</v>
       </c>
       <c r="AK14">
-        <v>0.4650943396226416</v>
+        <v>-0.9282514607191423</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AM14">
-        <v>-3.84</v>
+        <v>0.04100000000000001</v>
       </c>
       <c r="AN14">
-        <v>5.613924050632911</v>
+        <v>0.7201187824795842</v>
+      </c>
+      <c r="AO14">
+        <v>114.6376811594203</v>
       </c>
       <c r="AP14">
-        <v>3.120253164556962</v>
+        <v>-3.287927282625585</v>
       </c>
       <c r="AQ14">
-        <v>-3.828125</v>
+        <v>192.9268292682926</v>
       </c>
     </row>
     <row r="15">
@@ -2279,7 +2282,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Premium Group Co., Ltd. (TSE:7199)</t>
+          <t>Financial Products Group Co., Ltd. (TSE:7148)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2288,118 +2291,118 @@
         </is>
       </c>
       <c r="D15">
-        <v>3.663</v>
+        <v>0.229</v>
+      </c>
+      <c r="E15">
+        <v>-0.0242</v>
       </c>
       <c r="G15">
-        <v>0.2226027397260274</v>
+        <v>0.2036176973845026</v>
       </c>
       <c r="H15">
-        <v>0.2226027397260274</v>
+        <v>0.2036176973845026</v>
       </c>
       <c r="I15">
-        <v>0.1449771689497717</v>
+        <v>0.2027593204906841</v>
       </c>
       <c r="J15">
-        <v>0.1045940895459409</v>
+        <v>0.1392328431638031</v>
       </c>
       <c r="K15">
-        <v>21.8</v>
+        <v>58.6</v>
       </c>
       <c r="L15">
-        <v>0.1244292237442922</v>
+        <v>0.1432412613053043</v>
       </c>
       <c r="M15">
-        <v>5.568000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.01324768022840828</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.2554128440366973</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>5.568000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.01324768022840828</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.2554128440366973</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>73.3</v>
+        <v>90.7</v>
       </c>
       <c r="V15">
-        <v>0.1743992386390673</v>
+        <v>0.1258324084350722</v>
       </c>
       <c r="W15">
-        <v>0.3639398998330551</v>
+        <v>0.2234935163996949</v>
       </c>
       <c r="X15">
-        <v>0.02688667457520107</v>
+        <v>0.05836481012013579</v>
       </c>
       <c r="Y15">
-        <v>0.3370532252578541</v>
+        <v>0.1651287062795591</v>
       </c>
       <c r="Z15">
-        <v>1.477234401349072</v>
+        <v>0.743999704304926</v>
       </c>
       <c r="AA15">
-        <v>0.1545099872550492</v>
+        <v>0.1035891941434036</v>
       </c>
       <c r="AB15">
-        <v>0.02592690967058684</v>
+        <v>0.05370977413252478</v>
       </c>
       <c r="AC15">
-        <v>0.1285830775844624</v>
+        <v>0.04987942001087886</v>
       </c>
       <c r="AD15">
-        <v>170.1</v>
+        <v>690.1</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>2.705809936305637</v>
       </c>
       <c r="AF15">
-        <v>170.1</v>
+        <v>692.8058099363056</v>
       </c>
       <c r="AG15">
-        <v>96.8</v>
+        <v>602.1058099363056</v>
       </c>
       <c r="AH15">
-        <v>0.288109756097561</v>
+        <v>0.4900983039731013</v>
       </c>
       <c r="AI15">
-        <v>0.6945692119232341</v>
+        <v>0.7349119976073081</v>
       </c>
       <c r="AJ15">
-        <v>0.187197834074647</v>
+        <v>0.4551388355950265</v>
       </c>
       <c r="AK15">
-        <v>0.5641025641025641</v>
+        <v>0.7066921409624166</v>
       </c>
       <c r="AL15">
-        <v>0.663</v>
+        <v>2.86</v>
       </c>
       <c r="AM15">
-        <v>0.636</v>
+        <v>-4.27</v>
       </c>
       <c r="AN15">
-        <v>4.57258064516129</v>
+        <v>8.062857810491879</v>
       </c>
       <c r="AO15">
-        <v>38.31070889894419</v>
+        <v>28.39160839160839</v>
       </c>
       <c r="AP15">
-        <v>2.602150537634409</v>
+        <v>7.03476819647512</v>
       </c>
       <c r="AQ15">
-        <v>39.93710691823899</v>
+        <v>-19.01639344262295</v>
       </c>
     </row>
     <row r="16">
@@ -2410,7 +2413,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARUHI Corporation (TSE:7198)</t>
+          <t>Acom Co., Ltd. (TSE:8572)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2418,116 +2421,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.00983</v>
+      </c>
       <c r="G16">
-        <v>0.3709609735627361</v>
+        <v>0.173262206738882</v>
       </c>
       <c r="H16">
-        <v>0.3709609735627361</v>
+        <v>0.173262206738882</v>
       </c>
       <c r="I16">
-        <v>0.2849349559378934</v>
+        <v>0.3703978529639348</v>
       </c>
       <c r="J16">
-        <v>0.1916019310007567</v>
+        <v>0.3703978529639348</v>
       </c>
       <c r="K16">
-        <v>42.8</v>
+        <v>342.4</v>
       </c>
       <c r="L16">
-        <v>0.1796055392362568</v>
+        <v>0.186380708725709</v>
       </c>
       <c r="M16">
-        <v>23.0214</v>
+        <v>97.1292</v>
       </c>
       <c r="N16">
-        <v>0.07182964118564743</v>
+        <v>0.02587352157698455</v>
       </c>
       <c r="O16">
-        <v>0.5378831775700935</v>
+        <v>0.2836717289719626</v>
       </c>
       <c r="P16">
-        <v>18.9914</v>
+        <v>97.1292</v>
       </c>
       <c r="Q16">
-        <v>0.05925553822152885</v>
+        <v>0.02587352157698455</v>
       </c>
       <c r="R16">
-        <v>0.4437242990654205</v>
+        <v>0.2836717289719626</v>
       </c>
       <c r="S16">
-        <v>4.030000000000001</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>0.1750545144952089</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>278.3</v>
+        <v>611.5</v>
       </c>
       <c r="V16">
-        <v>0.8683307332293292</v>
+        <v>0.1628929142248269</v>
       </c>
       <c r="W16">
-        <v>0.1590486807878112</v>
+        <v>0.07342439903072931</v>
       </c>
       <c r="X16">
-        <v>0.03739303198672482</v>
+        <v>0.05959279912998308</v>
       </c>
       <c r="Y16">
-        <v>0.1216556488010864</v>
+        <v>0.01383159990074623</v>
       </c>
       <c r="Z16">
-        <v>0.5495848708487084</v>
+        <v>0.1993755225325253</v>
       </c>
       <c r="AA16">
-        <v>0.105301522503414</v>
+        <v>0.07384826547960997</v>
       </c>
       <c r="AB16">
-        <v>0.02809199865293981</v>
+        <v>0.05086462230809706</v>
       </c>
       <c r="AC16">
-        <v>0.07720952385047421</v>
+        <v>0.02298364317151291</v>
       </c>
       <c r="AD16">
-        <v>657.1</v>
+        <v>4141.1</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>0.3705215997764823</v>
       </c>
       <c r="AF16">
-        <v>657.1</v>
+        <v>4141.470521599776</v>
       </c>
       <c r="AG16">
-        <v>378.8</v>
+        <v>3529.970521599776</v>
       </c>
       <c r="AH16">
-        <v>0.6721563011456628</v>
+        <v>0.5245375193625108</v>
       </c>
       <c r="AI16">
-        <v>0.7030815322062914</v>
+        <v>0.4973084345753794</v>
       </c>
       <c r="AJ16">
-        <v>0.5416845416845417</v>
+        <v>0.4846217473192753</v>
       </c>
       <c r="AK16">
-        <v>0.5771750723754381</v>
+        <v>0.4574710686617977</v>
       </c>
       <c r="AL16">
-        <v>3.4</v>
+        <v>0.028</v>
       </c>
       <c r="AM16">
-        <v>3.4</v>
+        <v>-0.152</v>
       </c>
       <c r="AN16">
-        <v>8.102342786683108</v>
+        <v>5.859505441949707</v>
       </c>
       <c r="AO16">
-        <v>19.97058823529412</v>
+        <v>24300</v>
       </c>
       <c r="AP16">
-        <v>4.670776818742294</v>
+        <v>4.99477952264759</v>
       </c>
       <c r="AQ16">
-        <v>19.97058823529412</v>
+        <v>-4476.315789473684</v>
       </c>
     </row>
     <row r="17">
@@ -2538,7 +2544,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Acom Co., Ltd. (TSE:8572)</t>
+          <t>Mortgage Service Japan Limited (TSE:7192)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2547,121 +2553,118 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0183</v>
+        <v>0.0529</v>
       </c>
       <c r="E17">
-        <v>0.348</v>
+        <v>0.187</v>
       </c>
       <c r="G17">
-        <v>0.3944821731748727</v>
+        <v>0.2848948374760994</v>
       </c>
       <c r="H17">
-        <v>0.3944821731748727</v>
+        <v>0.2848948374760994</v>
       </c>
       <c r="I17">
-        <v>0.374672016363343</v>
+        <v>0.2122370936902486</v>
       </c>
       <c r="J17">
-        <v>0.3199035843506882</v>
+        <v>0.1431191729132473</v>
       </c>
       <c r="K17">
-        <v>668</v>
+        <v>7.64</v>
       </c>
       <c r="L17">
-        <v>0.2835314091680815</v>
+        <v>0.1460803059273423</v>
       </c>
       <c r="M17">
-        <v>84.59639999999999</v>
+        <v>2.0496</v>
       </c>
       <c r="N17">
-        <v>0.0187841726618705</v>
+        <v>0.02082926829268292</v>
       </c>
       <c r="O17">
-        <v>0.1266413173652695</v>
+        <v>0.2682722513089005</v>
       </c>
       <c r="P17">
-        <v>84.59639999999999</v>
+        <v>2.0286</v>
       </c>
       <c r="Q17">
-        <v>0.0187841726618705</v>
+        <v>0.02061585365853658</v>
       </c>
       <c r="R17">
-        <v>0.1266413173652695</v>
+        <v>0.2655235602094241</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>0.02099999999999991</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>0.01024590163934422</v>
       </c>
       <c r="U17">
-        <v>638</v>
+        <v>31.1</v>
       </c>
       <c r="V17">
-        <v>0.1416644462208011</v>
+        <v>0.3160569105691057</v>
       </c>
       <c r="W17">
-        <v>0.1553705168163</v>
+        <v>0.1352212389380531</v>
       </c>
       <c r="X17">
-        <v>0.03167888901685499</v>
+        <v>0.05561696023075925</v>
       </c>
       <c r="Y17">
-        <v>0.123691627799445</v>
+        <v>0.07960427870729386</v>
       </c>
       <c r="Z17">
-        <v>0.2476689409985263</v>
+        <v>0.4943289224952742</v>
       </c>
       <c r="AA17">
-        <v>0.0792301819577677</v>
+        <v>0.07074794653462035</v>
       </c>
       <c r="AB17">
-        <v>0.02560720079975025</v>
+        <v>0.05065947098381482</v>
       </c>
       <c r="AC17">
-        <v>0.05362298115801745</v>
+        <v>0.02008847555080553</v>
       </c>
       <c r="AD17">
-        <v>5202.1</v>
+        <v>63.3</v>
       </c>
       <c r="AE17">
-        <v>0.7986472398192633</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>5202.898647239819</v>
+        <v>63.3</v>
       </c>
       <c r="AG17">
-        <v>4564.898647239819</v>
+        <v>32.2</v>
       </c>
       <c r="AH17">
-        <v>0.5360221884664186</v>
+        <v>0.3914656771799629</v>
       </c>
       <c r="AI17">
-        <v>0.5131469288903021</v>
+        <v>0.5621669626998224</v>
       </c>
       <c r="AJ17">
-        <v>0.5033797572026146</v>
+        <v>0.2465543644716692</v>
       </c>
       <c r="AK17">
-        <v>0.4804550264366866</v>
+        <v>0.3950920245398772</v>
       </c>
       <c r="AL17">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>-0.027</v>
+        <v>-2.59</v>
       </c>
       <c r="AN17">
-        <v>5.684193503622757</v>
-      </c>
-      <c r="AO17">
-        <v>8911.111111111111</v>
+        <v>5.274999999999999</v>
       </c>
       <c r="AP17">
-        <v>4.987940876826069</v>
+        <v>2.683333333333333</v>
       </c>
       <c r="AQ17">
-        <v>-32674.07407407408</v>
+        <v>-4.285714285714286</v>
       </c>
     </row>
     <row r="18">
@@ -2672,7 +2675,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J Trust Co., Ltd. (TSE:8508)</t>
+          <t>ARUHI Corporation (TSE:7198)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2681,112 +2684,115 @@
         </is>
       </c>
       <c r="G18">
-        <v>-0.01146118721461187</v>
+        <v>0.3985507246376812</v>
       </c>
       <c r="H18">
-        <v>-0.01146118721461187</v>
+        <v>0.3985507246376812</v>
       </c>
       <c r="I18">
-        <v>0.2333333333333333</v>
+        <v>0.2373188405797101</v>
       </c>
       <c r="J18">
-        <v>0.1166666666666667</v>
+        <v>0.1633161913666823</v>
       </c>
       <c r="K18">
-        <v>-37.3</v>
+        <v>25.7</v>
       </c>
       <c r="L18">
-        <v>-0.1703196347031963</v>
+        <v>0.1551932367149758</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>14.7325</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.05412380602498163</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>0.573249027237354</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>14.7325</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.05412380602498163</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>0.573249027237354</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>851.8</v>
+        <v>181.2</v>
       </c>
       <c r="V18">
-        <v>1.628058103975535</v>
+        <v>0.665686994856723</v>
       </c>
       <c r="W18">
-        <v>-0.04089015566761674</v>
+        <v>0.09257925072046108</v>
       </c>
       <c r="X18">
-        <v>0.02716924705256853</v>
+        <v>0.06490927270423678</v>
       </c>
       <c r="Y18">
-        <v>-0.06805940272018526</v>
+        <v>0.0276699780162243</v>
       </c>
       <c r="Z18">
-        <v>0.4188982402448355</v>
+        <v>0.3788606726149621</v>
       </c>
       <c r="AA18">
-        <v>0.04887146136189748</v>
+        <v>0.06187408211009512</v>
       </c>
       <c r="AB18">
-        <v>0.02604949199044901</v>
+        <v>0.05476852627097097</v>
       </c>
       <c r="AC18">
-        <v>0.02282196937144847</v>
+        <v>0.007105555839124152</v>
       </c>
       <c r="AD18">
-        <v>234.9</v>
+        <v>467.7</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>234.9</v>
+        <v>467.7</v>
       </c>
       <c r="AG18">
-        <v>-616.9</v>
+        <v>286.5</v>
       </c>
       <c r="AH18">
-        <v>0.3098535813217254</v>
+        <v>0.6321124476280578</v>
       </c>
       <c r="AI18">
-        <v>0.1956521739130435</v>
+        <v>0.6744051910598413</v>
       </c>
       <c r="AJ18">
-        <v>6.583778014941307</v>
+        <v>0.5127975657776982</v>
       </c>
       <c r="AK18">
-        <v>-1.768635321100917</v>
+        <v>0.5592426312707398</v>
       </c>
       <c r="AL18">
-        <v>5.85</v>
+        <v>2.74</v>
       </c>
       <c r="AM18">
-        <v>-8.75</v>
+        <v>2.699</v>
       </c>
       <c r="AN18">
-        <v>2.973417721518987</v>
+        <v>9.391566265060241</v>
       </c>
       <c r="AO18">
-        <v>8.735042735042736</v>
+        <v>14.34306569343065</v>
       </c>
       <c r="AP18">
-        <v>-7.808860759493671</v>
+        <v>5.753012048192772</v>
       </c>
       <c r="AQ18">
-        <v>-5.84</v>
+        <v>14.56094849944424</v>
       </c>
     </row>
     <row r="19">
@@ -2797,7 +2803,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORIX Corporation (TSE:8591)</t>
+          <t>Asax Co., Ltd. (TSE:8772)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2806,124 +2812,115 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.00247</v>
+        <v>-0.00357</v>
       </c>
       <c r="E19">
-        <v>0.00346</v>
-      </c>
-      <c r="F19">
-        <v>0.241</v>
+        <v>0.00302</v>
       </c>
       <c r="G19">
-        <v>0.2728344914891486</v>
+        <v>0.7729468599033816</v>
       </c>
       <c r="H19">
-        <v>0.2728344914891486</v>
+        <v>0.7729468599033816</v>
       </c>
       <c r="I19">
-        <v>0.1699186888924692</v>
+        <v>0.7004830917874396</v>
       </c>
       <c r="J19">
-        <v>0.1153643803704274</v>
+        <v>0.4565217391304349</v>
       </c>
       <c r="K19">
-        <v>2198.5</v>
+        <v>18.9</v>
       </c>
       <c r="L19">
-        <v>0.1001129315762151</v>
+        <v>0.4565217391304348</v>
       </c>
       <c r="M19">
-        <v>1531.7</v>
+        <v>-0</v>
       </c>
       <c r="N19">
-        <v>0.06296192770291933</v>
+        <v>-0</v>
       </c>
       <c r="O19">
-        <v>0.696702297020696</v>
+        <v>-0</v>
       </c>
       <c r="P19">
-        <v>861.6</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.03541685506877019</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>0.3919035706163293</v>
+        <v>-0</v>
       </c>
       <c r="S19">
-        <v>670.1</v>
-      </c>
-      <c r="T19">
-        <v>0.4374877586994843</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>9242.1</v>
+        <v>16.5</v>
       </c>
       <c r="V19">
-        <v>0.3799049631279956</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="W19">
-        <v>0.077820529611446</v>
+        <v>0.05251458738538483</v>
       </c>
       <c r="X19">
-        <v>0.03637560319480546</v>
+        <v>0.06772350863142915</v>
       </c>
       <c r="Y19">
-        <v>0.04144492641664054</v>
+        <v>-0.01520892124604432</v>
       </c>
       <c r="Z19">
-        <v>0.3684142482028012</v>
+        <v>0.06320610687022901</v>
       </c>
       <c r="AA19">
-        <v>0.042501881463553</v>
+        <v>0.02885496183206107</v>
       </c>
       <c r="AB19">
-        <v>0.02799011978697015</v>
+        <v>0.05109112685846042</v>
       </c>
       <c r="AC19">
-        <v>0.01451176167658285</v>
+        <v>-0.02223616502639935</v>
       </c>
       <c r="AD19">
-        <v>43616</v>
+        <v>303.5</v>
       </c>
       <c r="AE19">
-        <v>2384.258040917988</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>46000.25804091799</v>
+        <v>303.5</v>
       </c>
       <c r="AG19">
-        <v>36758.15804091799</v>
+        <v>287</v>
       </c>
       <c r="AH19">
-        <v>0.6540848838468949</v>
+        <v>0.6714601769911505</v>
       </c>
       <c r="AI19">
-        <v>0.615264948262829</v>
+        <v>0.5094846399194225</v>
       </c>
       <c r="AJ19">
-        <v>0.6017487474911114</v>
+        <v>0.6590126291618829</v>
       </c>
       <c r="AK19">
-        <v>0.5609974769104715</v>
+        <v>0.4955110497237569</v>
       </c>
       <c r="AL19">
-        <v>622</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>613.22</v>
+        <v>-0.014</v>
       </c>
       <c r="AN19">
-        <v>6.122489086034335</v>
-      </c>
-      <c r="AO19">
-        <v>6.069131832797428</v>
+        <v>10.42955326460481</v>
       </c>
       <c r="AP19">
-        <v>5.159836331351926</v>
+        <v>9.862542955326459</v>
       </c>
       <c r="AQ19">
-        <v>6.1560288314145</v>
+        <v>-2071.428571428572</v>
       </c>
     </row>
     <row r="20">
@@ -2934,7 +2931,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Asax Co., Ltd. (TSE:8772)</t>
+          <t>Marui Group Co., Ltd. (TSE:8252)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2943,112 +2940,124 @@
         </is>
       </c>
       <c r="D20">
-        <v>-0.015</v>
+        <v>-0.0191</v>
       </c>
       <c r="E20">
-        <v>-0.00356</v>
+        <v>-0.0136</v>
+      </c>
+      <c r="F20">
+        <v>0.216</v>
       </c>
       <c r="G20">
-        <v>0.7267441860465116</v>
+        <v>0.2675465313028765</v>
       </c>
       <c r="H20">
-        <v>0.7267441860465116</v>
+        <v>0.2675465313028765</v>
       </c>
       <c r="I20">
-        <v>0.6918604651162791</v>
+        <v>0.1807659072160272</v>
       </c>
       <c r="J20">
-        <v>0.4534883720930233</v>
+        <v>0.1215960065524177</v>
       </c>
       <c r="K20">
-        <v>23.4</v>
+        <v>131.2</v>
       </c>
       <c r="L20">
-        <v>0.4534883720930232</v>
+        <v>0.08879864636209812</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>221.538</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.06865563406470807</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>1.688551829268293</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>74.13800000000001</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.02297570348332714</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0.5650762195121952</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>147.4</v>
+      </c>
+      <c r="T20">
+        <v>0.6653486083651563</v>
       </c>
       <c r="U20">
-        <v>33.9</v>
+        <v>304.1</v>
       </c>
       <c r="V20">
-        <v>0.1674074074074074</v>
+        <v>0.09424197347217057</v>
       </c>
       <c r="W20">
-        <v>0.06474820143884892</v>
+        <v>0.05176971944915755</v>
       </c>
       <c r="X20">
-        <v>0.03467602168174486</v>
+        <v>0.06074352519534205</v>
       </c>
       <c r="Y20">
-        <v>0.03007217975710406</v>
+        <v>-0.008973805746184504</v>
       </c>
       <c r="Z20">
-        <v>0.0781818181818182</v>
+        <v>0.2201940077916522</v>
       </c>
       <c r="AA20">
-        <v>0.03545454545454546</v>
+        <v>0.02677471201423685</v>
       </c>
       <c r="AB20">
-        <v>0.02580915272217724</v>
+        <v>0.05090825343147864</v>
       </c>
       <c r="AC20">
-        <v>0.009645392732368217</v>
+        <v>-0.02413354141724179</v>
       </c>
       <c r="AD20">
-        <v>329</v>
+        <v>3928.8</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>60.59186044159917</v>
       </c>
       <c r="AF20">
-        <v>329</v>
+        <v>3989.391860441599</v>
       </c>
       <c r="AG20">
-        <v>295.1</v>
+        <v>3685.2918604416</v>
       </c>
       <c r="AH20">
-        <v>0.6190028222013171</v>
+        <v>0.5528389402048778</v>
       </c>
       <c r="AI20">
-        <v>0.4775729423718972</v>
+        <v>0.6838654393177936</v>
       </c>
       <c r="AJ20">
-        <v>0.5930466237942122</v>
+        <v>0.5331659264444661</v>
       </c>
       <c r="AK20">
-        <v>0.4505343511450382</v>
+        <v>0.6664792992655355</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>8.94</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>7.159999999999999</v>
       </c>
       <c r="AN20">
-        <v>9.138888888888889</v>
+        <v>11.00812552535724</v>
+      </c>
+      <c r="AO20">
+        <v>29.42953020134228</v>
       </c>
       <c r="AP20">
-        <v>8.197222222222223</v>
+        <v>10.32583877960661</v>
+      </c>
+      <c r="AQ20">
+        <v>36.74581005586593</v>
       </c>
     </row>
     <row r="21">
@@ -3059,7 +3068,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Financial Products Group Co., Ltd. (TSE:7148)</t>
+          <t>ORIX Corporation (TSE:8591)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3068,121 +3077,124 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.0461</v>
+        <v>-0.0234</v>
       </c>
       <c r="E21">
-        <v>-0.174</v>
+        <v>-0.006710000000000001</v>
+      </c>
+      <c r="F21">
+        <v>0.203</v>
       </c>
       <c r="G21">
-        <v>0.3617339312406577</v>
+        <v>0.3418657472019265</v>
       </c>
       <c r="H21">
-        <v>0.3617339312406577</v>
+        <v>0.3418657472019265</v>
       </c>
       <c r="I21">
-        <v>0.352377382445371</v>
+        <v>0.1294766898650864</v>
       </c>
       <c r="J21">
-        <v>0.2294349050319984</v>
+        <v>0.08387806856745735</v>
       </c>
       <c r="K21">
-        <v>26.4</v>
+        <v>1985.2</v>
       </c>
       <c r="L21">
-        <v>0.1973094170403587</v>
+        <v>0.1086500834633172</v>
       </c>
       <c r="M21">
-        <v>14.1764</v>
+        <v>1073.1</v>
       </c>
       <c r="N21">
-        <v>0.02793929838391802</v>
+        <v>0.05708069809624621</v>
       </c>
       <c r="O21">
-        <v>0.5369848484848485</v>
+        <v>0.5405500705218618</v>
       </c>
       <c r="P21">
-        <v>14.1764</v>
+        <v>709.5</v>
       </c>
       <c r="Q21">
-        <v>0.02793929838391802</v>
+        <v>0.03773996393559471</v>
       </c>
       <c r="R21">
-        <v>0.5369848484848485</v>
+        <v>0.3573947209349184</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>363.5999999999999</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>0.3388314229801509</v>
       </c>
       <c r="U21">
-        <v>186.6</v>
+        <v>6399.8</v>
       </c>
       <c r="V21">
-        <v>0.367757193535672</v>
+        <v>0.3404203258562636</v>
       </c>
       <c r="W21">
-        <v>0.1022859356838435</v>
+        <v>0.07102632539302044</v>
       </c>
       <c r="X21">
-        <v>0.03040196103540505</v>
+        <v>0.06809640446843573</v>
       </c>
       <c r="Y21">
-        <v>0.07188397464843842</v>
+        <v>0.002929920924584703</v>
       </c>
       <c r="Z21">
-        <v>0.1482040179952993</v>
+        <v>0.3090817233044552</v>
       </c>
       <c r="AA21">
-        <v>0.03400317479411206</v>
+        <v>0.02592517798027897</v>
       </c>
       <c r="AB21">
-        <v>0.0270569873591638</v>
+        <v>0.05509610090900343</v>
       </c>
       <c r="AC21">
-        <v>0.006946187434948264</v>
+        <v>-0.02917092292872446</v>
       </c>
       <c r="AD21">
-        <v>479.7</v>
+        <v>37411.4</v>
       </c>
       <c r="AE21">
-        <v>5.009531144046796</v>
+        <v>1821.833305650366</v>
       </c>
       <c r="AF21">
-        <v>484.7095311440468</v>
+        <v>39233.23330565037</v>
       </c>
       <c r="AG21">
-        <v>298.1095311440467</v>
+        <v>32833.43330565037</v>
       </c>
       <c r="AH21">
-        <v>0.4885645343867487</v>
+        <v>0.6760511845750597</v>
       </c>
       <c r="AI21">
-        <v>0.6478259243809733</v>
+        <v>0.6218324501665987</v>
       </c>
       <c r="AJ21">
-        <v>0.3700881487034035</v>
+        <v>0.6358985249120511</v>
       </c>
       <c r="AK21">
-        <v>0.5308128060732376</v>
+        <v>0.5791430353414246</v>
       </c>
       <c r="AL21">
-        <v>6.7</v>
+        <v>597</v>
       </c>
       <c r="AM21">
-        <v>-7.600000000000001</v>
+        <v>587.62</v>
       </c>
       <c r="AN21">
-        <v>9.341772151898734</v>
+        <v>7.431301273265399</v>
       </c>
       <c r="AO21">
-        <v>6.746268656716418</v>
+        <v>3.914405360134003</v>
       </c>
       <c r="AP21">
-        <v>5.805443644479976</v>
+        <v>6.521946110809917</v>
       </c>
       <c r="AQ21">
-        <v>-5.947368421052632</v>
+        <v>3.97688982675879</v>
       </c>
     </row>
     <row r="22">
@@ -3202,46 +3214,46 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.07480000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="E22">
-        <v>0.297</v>
+        <v>0.126</v>
       </c>
       <c r="G22">
-        <v>0.1636080332409972</v>
+        <v>0.1268656716417911</v>
       </c>
       <c r="H22">
-        <v>0.1636080332409972</v>
+        <v>0.1268656716417911</v>
       </c>
       <c r="I22">
-        <v>0.1400623268698061</v>
+        <v>0.09775068320369981</v>
       </c>
       <c r="J22">
-        <v>0.1400623268698061</v>
+        <v>0.09775068320369981</v>
       </c>
       <c r="K22">
-        <v>167.4</v>
+        <v>97.2</v>
       </c>
       <c r="L22">
-        <v>0.144909972299169</v>
+        <v>0.1021652301870927</v>
       </c>
       <c r="M22">
-        <v>4.3533</v>
+        <v>3.3859</v>
       </c>
       <c r="N22">
-        <v>0.002910932798395186</v>
+        <v>0.002325161378931465</v>
       </c>
       <c r="O22">
-        <v>0.02600537634408602</v>
+        <v>0.0348343621399177</v>
       </c>
       <c r="P22">
-        <v>4.3533</v>
+        <v>3.3859</v>
       </c>
       <c r="Q22">
-        <v>0.002910932798395186</v>
+        <v>0.002325161378931465</v>
       </c>
       <c r="R22">
-        <v>0.02600537634408602</v>
+        <v>0.0348343621399177</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3250,73 +3262,70 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>332.4</v>
+        <v>374.7</v>
       </c>
       <c r="V22">
-        <v>0.2222668004012036</v>
+        <v>0.2573135558302431</v>
       </c>
       <c r="W22">
-        <v>0.1295465098282</v>
+        <v>0.07134468584850263</v>
       </c>
       <c r="X22">
-        <v>0.04184372293305677</v>
+        <v>0.07171015877974629</v>
       </c>
       <c r="Y22">
-        <v>0.08770278689514319</v>
+        <v>-0.0003654729312436572</v>
       </c>
       <c r="Z22">
-        <v>0.2249352571217166</v>
+        <v>0.1851477056007473</v>
       </c>
       <c r="AA22">
-        <v>0.03150495550752575</v>
+        <v>0.01809831471607052</v>
       </c>
       <c r="AB22">
-        <v>0.02608693545707013</v>
+        <v>0.05115777057832238</v>
       </c>
       <c r="AC22">
-        <v>0.005418020050455621</v>
+        <v>-0.03305945586225185</v>
       </c>
       <c r="AD22">
-        <v>4108.6</v>
+        <v>3647.7</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>4108.6</v>
+        <v>3647.7</v>
       </c>
       <c r="AG22">
-        <v>3776.2</v>
+        <v>3273</v>
       </c>
       <c r="AH22">
-        <v>0.7331418068913831</v>
+        <v>0.7146887674131547</v>
       </c>
       <c r="AI22">
-        <v>0.7482289523046385</v>
+        <v>0.7576959827177931</v>
       </c>
       <c r="AJ22">
-        <v>0.7163154200732211</v>
+        <v>0.6920832276072063</v>
       </c>
       <c r="AK22">
-        <v>0.7320061255742726</v>
+        <v>0.7372451852686114</v>
       </c>
       <c r="AL22">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1.852</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="AN22">
-        <v>21.37669094693029</v>
-      </c>
-      <c r="AO22">
-        <v>8988.888888888891</v>
+        <v>30.99150382327952</v>
       </c>
       <c r="AP22">
-        <v>19.64724245577524</v>
+        <v>27.80798640611725</v>
       </c>
       <c r="AQ22">
-        <v>-87.36501079913607</v>
+        <v>-114.9567367119901</v>
       </c>
     </row>
     <row r="23">
@@ -3327,7 +3336,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Japan Investment Adviser Co., Ltd. (TSE:7172)</t>
+          <t>Kyushu Leasing Service Co., Ltd. (TSE:8596)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3336,46 +3345,46 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.274</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="E23">
-        <v>0.424</v>
+        <v>0.142</v>
       </c>
       <c r="G23">
-        <v>0.5642915642915644</v>
+        <v>0.1499585749792875</v>
       </c>
       <c r="H23">
-        <v>0.5642915642915644</v>
+        <v>0.1499585749792875</v>
       </c>
       <c r="I23">
-        <v>0.334971334971335</v>
+        <v>0.1179350299660256</v>
       </c>
       <c r="J23">
-        <v>0.1963625067073343</v>
+        <v>0.07971301598982969</v>
       </c>
       <c r="K23">
-        <v>24.9</v>
+        <v>31.8</v>
       </c>
       <c r="L23">
-        <v>0.2039312039312039</v>
+        <v>0.1317315658657829</v>
       </c>
       <c r="M23">
-        <v>8.667399999999999</v>
+        <v>3.0645</v>
       </c>
       <c r="N23">
-        <v>0.02543997651893161</v>
+        <v>0.02441832669322709</v>
       </c>
       <c r="O23">
-        <v>0.3480883534136546</v>
+        <v>0.0963679245283019</v>
       </c>
       <c r="P23">
-        <v>8.667399999999999</v>
+        <v>3.0645</v>
       </c>
       <c r="Q23">
-        <v>0.02543997651893161</v>
+        <v>0.02441832669322709</v>
       </c>
       <c r="R23">
-        <v>0.3480883534136546</v>
+        <v>0.0963679245283019</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3384,73 +3393,73 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>96.40000000000001</v>
+        <v>43.5</v>
       </c>
       <c r="V23">
-        <v>0.2829468740827708</v>
+        <v>0.3466135458167331</v>
       </c>
       <c r="W23">
-        <v>0.06867071152785438</v>
+        <v>0.1077600813283633</v>
       </c>
       <c r="X23">
-        <v>0.03132090553770595</v>
+        <v>0.1089081620564333</v>
       </c>
       <c r="Y23">
-        <v>0.03734980599014844</v>
+        <v>-0.001148080728070003</v>
       </c>
       <c r="Z23">
-        <v>0.1618933969769292</v>
+        <v>0.1952438755565027</v>
       </c>
       <c r="AA23">
-        <v>0.03178979324975539</v>
+        <v>0.01556347817415181</v>
       </c>
       <c r="AB23">
-        <v>0.0272546699615548</v>
+        <v>0.05140017671511297</v>
       </c>
       <c r="AC23">
-        <v>0.004535123288200594</v>
+        <v>-0.03583669854096116</v>
       </c>
       <c r="AD23">
-        <v>374.5</v>
+        <v>840.3</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>14.10241883100707</v>
       </c>
       <c r="AF23">
-        <v>374.5</v>
+        <v>854.402418831007</v>
       </c>
       <c r="AG23">
-        <v>278.1</v>
+        <v>810.902418831007</v>
       </c>
       <c r="AH23">
-        <v>0.5236297539149888</v>
+        <v>0.8719260228485632</v>
       </c>
       <c r="AI23">
-        <v>0.5078654732845131</v>
+        <v>0.7751774122734951</v>
       </c>
       <c r="AJ23">
-        <v>0.4494182288299936</v>
+        <v>0.8659764247975004</v>
       </c>
       <c r="AK23">
-        <v>0.4338533541341654</v>
+        <v>0.7659398943533022</v>
       </c>
       <c r="AL23">
-        <v>5.18</v>
+        <v>0.477</v>
       </c>
       <c r="AM23">
-        <v>1.87</v>
+        <v>-0.394</v>
       </c>
       <c r="AN23">
-        <v>8.937947494033413</v>
+        <v>21.06542993231386</v>
       </c>
       <c r="AO23">
-        <v>7.895752895752896</v>
+        <v>56.60377358490566</v>
       </c>
       <c r="AP23">
-        <v>6.637231503579953</v>
+        <v>20.32846374607689</v>
       </c>
       <c r="AQ23">
-        <v>21.8716577540107</v>
+        <v>-68.52791878172589</v>
       </c>
     </row>
     <row r="24">
@@ -3461,7 +3470,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kyushu Leasing Service Co., Ltd. (TSE:8596)</t>
+          <t>Japan Investment Adviser Co., Ltd. (TSE:7172)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3470,46 +3479,46 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.0499</v>
+        <v>0.208</v>
       </c>
       <c r="E24">
-        <v>-0.00825</v>
+        <v>0.232</v>
       </c>
       <c r="G24">
-        <v>0.1887755102040816</v>
+        <v>0.2771618625277162</v>
       </c>
       <c r="H24">
-        <v>0.1887755102040816</v>
+        <v>0.2771618625277162</v>
       </c>
       <c r="I24">
-        <v>0.1316944467786891</v>
+        <v>0.1256467110125647</v>
       </c>
       <c r="J24">
-        <v>0.1023797694428559</v>
+        <v>0.08916863362182009</v>
       </c>
       <c r="K24">
-        <v>16.1</v>
+        <v>46.1</v>
       </c>
       <c r="L24">
-        <v>0.06845238095238096</v>
+        <v>0.3407243163340724</v>
       </c>
       <c r="M24">
-        <v>3.4504</v>
+        <v>6.6742</v>
       </c>
       <c r="N24">
-        <v>0.02961716738197425</v>
+        <v>0.02500636942675159</v>
       </c>
       <c r="O24">
-        <v>0.2143105590062112</v>
+        <v>0.1447765726681128</v>
       </c>
       <c r="P24">
-        <v>3.4504</v>
+        <v>6.6742</v>
       </c>
       <c r="Q24">
-        <v>0.02961716738197425</v>
+        <v>0.02500636942675159</v>
       </c>
       <c r="R24">
-        <v>0.2143105590062112</v>
+        <v>0.1447765726681128</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3518,73 +3527,73 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>42.4</v>
+        <v>128</v>
       </c>
       <c r="V24">
-        <v>0.3639484978540772</v>
+        <v>0.4795803671787187</v>
       </c>
       <c r="W24">
-        <v>0.05466893039049237</v>
+        <v>0.1274536909040641</v>
       </c>
       <c r="X24">
-        <v>0.07854767775776895</v>
+        <v>0.06977428914812933</v>
       </c>
       <c r="Y24">
-        <v>-0.02387874736727659</v>
+        <v>0.05767940175593481</v>
       </c>
       <c r="Z24">
-        <v>0.2014082598105576</v>
+        <v>0.2114723351047202</v>
       </c>
       <c r="AA24">
-        <v>0.0206201312032917</v>
+        <v>0.01885669917010356</v>
       </c>
       <c r="AB24">
-        <v>0.02648010364327176</v>
+        <v>0.05523897401634439</v>
       </c>
       <c r="AC24">
-        <v>-0.005859972439980061</v>
+        <v>-0.03638227484624083</v>
       </c>
       <c r="AD24">
-        <v>969.6</v>
+        <v>608.8</v>
       </c>
       <c r="AE24">
-        <v>20.17733058826166</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>989.7773305882616</v>
+        <v>608.8</v>
       </c>
       <c r="AG24">
-        <v>947.3773305882617</v>
+        <v>480.8</v>
       </c>
       <c r="AH24">
-        <v>0.8946918672390664</v>
+        <v>0.6952152563663355</v>
       </c>
       <c r="AI24">
-        <v>0.7696094994035311</v>
+        <v>0.6467651120790396</v>
       </c>
       <c r="AJ24">
-        <v>0.8904948938656467</v>
+        <v>0.6430386518657215</v>
       </c>
       <c r="AK24">
-        <v>0.7617549241169738</v>
+        <v>0.5911717693348087</v>
       </c>
       <c r="AL24">
-        <v>0.52</v>
+        <v>4.55</v>
       </c>
       <c r="AM24">
-        <v>-0.5900000000000001</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="AN24">
-        <v>21.07367963486199</v>
+        <v>26.4695652173913</v>
       </c>
       <c r="AO24">
-        <v>58.46153846153846</v>
+        <v>3.736263736263736</v>
       </c>
       <c r="AP24">
-        <v>20.5906831251524</v>
+        <v>20.90434782608695</v>
       </c>
       <c r="AQ24">
-        <v>-51.52542372881355</v>
+        <v>424.9999999999996</v>
       </c>
     </row>
     <row r="25">
@@ -3595,7 +3604,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wedge Holdings CO., LTD. (JASDAQ:2388)</t>
+          <t>Orient Corporation (TSE:8585)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3604,115 +3613,115 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.09089999999999999</v>
+        <v>0.011</v>
+      </c>
+      <c r="E25">
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G25">
-        <v>0.1032882011605416</v>
+        <v>0.2798950393602399</v>
       </c>
       <c r="H25">
-        <v>0.1032882011605416</v>
+        <v>0.2798950393602399</v>
       </c>
       <c r="I25">
-        <v>0.03500967117988395</v>
+        <v>0.1320129951268275</v>
       </c>
       <c r="J25">
-        <v>0.03500967117988395</v>
+        <v>0.07725760510263198</v>
       </c>
       <c r="K25">
-        <v>-10.6</v>
+        <v>122.7</v>
       </c>
       <c r="L25">
-        <v>-0.2050290135396518</v>
+        <v>0.07665875296763715</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>183.1419</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.1212619347149573</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.49259902200489</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>35.5419</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.0235330066874131</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>0.2896650366748166</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>147.6</v>
+      </c>
+      <c r="T25">
+        <v>0.8059324491009431</v>
       </c>
       <c r="U25">
-        <v>1.59</v>
+        <v>1512.7</v>
       </c>
       <c r="V25">
-        <v>0.05559440559440559</v>
+        <v>1.00158908826061</v>
       </c>
       <c r="W25">
-        <v>-0.2208333333333333</v>
+        <v>0.0586267857996082</v>
       </c>
       <c r="X25">
-        <v>0.02503714773137234</v>
+        <v>0.1192561118328307</v>
       </c>
       <c r="Y25">
-        <v>-0.2458704810647057</v>
+        <v>-0.06062932603322248</v>
       </c>
       <c r="Z25">
-        <v>0.5159680638722555</v>
+        <v>0.1293278281877459</v>
       </c>
       <c r="AA25">
-        <v>0.01806387225548902</v>
+        <v>0.00999155827890991</v>
       </c>
       <c r="AB25">
-        <v>0.02488428285343156</v>
+        <v>0.05142642338193332</v>
       </c>
       <c r="AC25">
-        <v>-0.006820410597942535</v>
+        <v>-0.04143486510302341</v>
       </c>
       <c r="AD25">
-        <v>3.29</v>
+        <v>12090</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>3.29</v>
+        <v>12090</v>
       </c>
       <c r="AG25">
-        <v>1.7</v>
+        <v>10577.3</v>
       </c>
       <c r="AH25">
-        <v>0.1031671370335528</v>
+        <v>0.8889509790225216</v>
       </c>
       <c r="AI25">
-        <v>0.09218268422527319</v>
+        <v>0.8865716297078494</v>
       </c>
       <c r="AJ25">
-        <v>0.0561056105610561</v>
+        <v>0.8750537741156227</v>
       </c>
       <c r="AK25">
-        <v>0.04985337243401759</v>
+        <v>0.8724193960788843</v>
       </c>
       <c r="AL25">
-        <v>6.72</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="AN25">
-        <v>0.6161048689138577</v>
-      </c>
-      <c r="AO25">
-        <v>0.2693452380952381</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="AP25">
-        <v>0.3183520599250936</v>
-      </c>
-      <c r="AQ25">
-        <v>0.3434535104364327</v>
+        <v>27.03117812420138</v>
       </c>
     </row>
     <row r="26">
@@ -3723,7 +3732,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Showa Holdings Co., Ltd. (TSE:5103)</t>
+          <t>Fuyo General Lease Co., Ltd. (TSE:8424)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3732,115 +3741,121 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.00125</v>
+        <v>0.05230000000000001</v>
+      </c>
+      <c r="E26">
+        <v>0.11</v>
       </c>
       <c r="G26">
-        <v>0.08746441281138789</v>
+        <v>0.1610558303044748</v>
       </c>
       <c r="H26">
-        <v>0.08523131672597864</v>
+        <v>0.1610558303044748</v>
       </c>
       <c r="I26">
-        <v>0.01166626428299419</v>
+        <v>0.06860487243965137</v>
       </c>
       <c r="J26">
-        <v>0.01166626428299419</v>
+        <v>0.04689357310794962</v>
       </c>
       <c r="K26">
-        <v>-10.1</v>
+        <v>249.6</v>
       </c>
       <c r="L26">
-        <v>-0.08985765124555159</v>
+        <v>0.04957397366382649</v>
       </c>
       <c r="M26">
-        <v>-0</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="N26">
-        <v>-0</v>
+        <v>0.0353493594651151</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>0.2774839743589744</v>
       </c>
       <c r="P26">
-        <v>-0</v>
+        <v>64.80000000000001</v>
       </c>
       <c r="Q26">
-        <v>-0</v>
+        <v>0.03307303628847038</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>0.2596153846153847</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>4.459999999999994</v>
+      </c>
+      <c r="T26">
+        <v>0.06439503320820089</v>
       </c>
       <c r="U26">
-        <v>4.19</v>
+        <v>550.7</v>
       </c>
       <c r="V26">
-        <v>0.1351612903225806</v>
+        <v>0.2810697698157505</v>
       </c>
       <c r="W26">
-        <v>-0.2707774798927614</v>
+        <v>0.08554390294057165</v>
       </c>
       <c r="X26">
-        <v>0.02746697601405308</v>
+        <v>0.1233021940180527</v>
       </c>
       <c r="Y26">
-        <v>-0.2982444559068145</v>
+        <v>-0.03775829107748108</v>
       </c>
       <c r="Z26">
-        <v>1.138648029714622</v>
+        <v>0.2129416391266409</v>
       </c>
       <c r="AA26">
-        <v>0.01328376883996141</v>
+        <v>0.00998559432211176</v>
       </c>
       <c r="AB26">
-        <v>0.02617080040910306</v>
+        <v>0.05143488205855009</v>
       </c>
       <c r="AC26">
-        <v>-0.01288703156914165</v>
+        <v>-0.04144928773643833</v>
       </c>
       <c r="AD26">
-        <v>8.449999999999999</v>
+        <v>16591.3</v>
       </c>
       <c r="AE26">
-        <v>6.913559472957265</v>
+        <v>10.00663876799651</v>
       </c>
       <c r="AF26">
-        <v>15.36355947295726</v>
+        <v>16601.306638768</v>
       </c>
       <c r="AG26">
-        <v>11.17355947295726</v>
+        <v>16050.606638768</v>
       </c>
       <c r="AH26">
-        <v>0.3313714401483444</v>
+        <v>0.8944377175739741</v>
       </c>
       <c r="AI26">
-        <v>0.3170126098874382</v>
+        <v>0.8577710521972195</v>
       </c>
       <c r="AJ26">
-        <v>0.2649422911557187</v>
+        <v>0.8912098746929412</v>
       </c>
       <c r="AK26">
-        <v>0.2523754495001059</v>
+        <v>0.8536055358303534</v>
       </c>
       <c r="AL26">
-        <v>6.94</v>
+        <v>6.18</v>
       </c>
       <c r="AM26">
-        <v>5.44</v>
+        <v>-12.22</v>
       </c>
       <c r="AN26">
-        <v>1.240822320117474</v>
+        <v>24.06908257413103</v>
       </c>
       <c r="AO26">
-        <v>0.1201729106628242</v>
+        <v>55.40453074433657</v>
       </c>
       <c r="AP26">
-        <v>1.640757631858629</v>
+        <v>23.28469598846399</v>
       </c>
       <c r="AQ26">
-        <v>0.1533088235294117</v>
+        <v>-28.01963993453355</v>
       </c>
     </row>
     <row r="27">
@@ -3851,7 +3866,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Orient Corporation (TSE:8585)</t>
+          <t>Daikokuya Holdings Co.,Ltd. (TSE:6993)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3860,115 +3875,115 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.0132</v>
-      </c>
-      <c r="E27">
-        <v>-0.0564</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="G27">
-        <v>0.1965101584524157</v>
+        <v>0.0108974358974359</v>
       </c>
       <c r="H27">
-        <v>0.1965101584524157</v>
+        <v>0.0108974358974359</v>
       </c>
       <c r="I27">
-        <v>0.1043550111791581</v>
+        <v>0.004828497663326632</v>
       </c>
       <c r="J27">
-        <v>0.08599369621483235</v>
+        <v>0.004828497663326632</v>
       </c>
       <c r="K27">
-        <v>186.1</v>
+        <v>-2.21</v>
       </c>
       <c r="L27">
-        <v>0.09045397103139885</v>
+        <v>-0.02023809523809524</v>
       </c>
       <c r="M27">
-        <v>191.3428</v>
+        <v>-0</v>
       </c>
       <c r="N27">
-        <v>0.1026847697756789</v>
+        <v>-0</v>
       </c>
       <c r="O27">
-        <v>1.028171950564213</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>46.3428</v>
+        <v>-0</v>
       </c>
       <c r="Q27">
-        <v>0.02487002253944403</v>
+        <v>-0</v>
       </c>
       <c r="R27">
-        <v>0.2490209564750135</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>145</v>
-      </c>
-      <c r="T27">
-        <v>0.7578022272068768</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>3427.9</v>
+        <v>5.46</v>
       </c>
       <c r="V27">
-        <v>1.839594290007513</v>
+        <v>0.1062256809338521</v>
       </c>
       <c r="W27">
-        <v>0.07701539480218507</v>
+        <v>-0.2450110864745011</v>
       </c>
       <c r="X27">
-        <v>0.07132907765222153</v>
+        <v>0.05578319121030474</v>
       </c>
       <c r="Y27">
-        <v>0.005686317149963538</v>
+        <v>-0.3007942776848059</v>
       </c>
       <c r="Z27">
-        <v>0.1497630607743654</v>
+        <v>2.333151852216228</v>
       </c>
       <c r="AA27">
-        <v>0.01287867915243426</v>
+        <v>0.01126561826661226</v>
       </c>
       <c r="AB27">
-        <v>0.02644546557660496</v>
+        <v>0.05418991177055109</v>
       </c>
       <c r="AC27">
-        <v>-0.0135667864241707</v>
+        <v>-0.04292429350393883</v>
       </c>
       <c r="AD27">
-        <v>13724.6</v>
+        <v>33.9</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>0.1536402758236592</v>
       </c>
       <c r="AF27">
-        <v>13724.6</v>
+        <v>34.05364027582366</v>
       </c>
       <c r="AG27">
-        <v>10296.7</v>
+        <v>28.59364027582366</v>
       </c>
       <c r="AH27">
-        <v>0.8804593276879651</v>
+        <v>0.3985042669441203</v>
       </c>
       <c r="AI27">
-        <v>0.8667091877008961</v>
+        <v>0.7942791901210783</v>
       </c>
       <c r="AJ27">
-        <v>0.8467611286091398</v>
+        <v>0.3574489194044776</v>
       </c>
       <c r="AK27">
-        <v>0.8298837790350919</v>
+        <v>0.7642571015550337</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>0.829</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AN27">
-        <v>31.47122219674387</v>
+        <v>31.50557620817844</v>
+      </c>
+      <c r="AO27">
+        <v>0.4752714113389627</v>
       </c>
       <c r="AP27">
-        <v>23.61086906672782</v>
+        <v>26.57401512623017</v>
+      </c>
+      <c r="AQ27">
+        <v>0.4834355828220859</v>
       </c>
     </row>
     <row r="28">
@@ -3979,7 +3994,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fuyo General Lease Co., Ltd. (TSE:8424)</t>
+          <t>Credit Saison Co., Ltd. (TSE:8253)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3988,46 +4003,46 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.064</v>
+        <v>0.0473</v>
       </c>
       <c r="E28">
-        <v>0.14</v>
+        <v>-0.0213</v>
       </c>
       <c r="G28">
-        <v>0.1388800801134941</v>
+        <v>0.2314585166813345</v>
       </c>
       <c r="H28">
-        <v>0.1388800801134941</v>
+        <v>0.2314585166813345</v>
       </c>
       <c r="I28">
-        <v>0.07084091938054494</v>
+        <v>0.1104088327066165</v>
       </c>
       <c r="J28">
-        <v>0.04941797862958133</v>
+        <v>0.08088187284867847</v>
       </c>
       <c r="K28">
-        <v>302.8</v>
+        <v>285.6</v>
       </c>
       <c r="L28">
-        <v>0.05053826253859635</v>
+        <v>0.1142491399311945</v>
       </c>
       <c r="M28">
-        <v>69.90000000000001</v>
+        <v>59.39400000000001</v>
       </c>
       <c r="N28">
-        <v>0.0336575500770416</v>
+        <v>0.02945546518547907</v>
       </c>
       <c r="O28">
-        <v>0.2308454425363276</v>
+        <v>0.2079621848739496</v>
       </c>
       <c r="P28">
-        <v>69.90000000000001</v>
+        <v>59.39400000000001</v>
       </c>
       <c r="Q28">
-        <v>0.0336575500770416</v>
+        <v>0.02945546518547907</v>
       </c>
       <c r="R28">
-        <v>0.2308454425363276</v>
+        <v>0.2079621848739496</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -4036,73 +4051,70 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>625.7</v>
+        <v>668</v>
       </c>
       <c r="V28">
-        <v>0.3012808166409861</v>
+        <v>0.3312834755008927</v>
       </c>
       <c r="W28">
-        <v>0.1124438337851387</v>
+        <v>0.05805940110995914</v>
       </c>
       <c r="X28">
-        <v>0.09051631017074727</v>
+        <v>0.1283896544429309</v>
       </c>
       <c r="Y28">
-        <v>0.02192752361439143</v>
+        <v>-0.07033025333297174</v>
       </c>
       <c r="Z28">
-        <v>0.2394786365287616</v>
+        <v>0.09575869941620828</v>
       </c>
       <c r="AA28">
-        <v>0.01183455014221961</v>
+        <v>0.007745142950336579</v>
       </c>
       <c r="AB28">
-        <v>0.02652235594021008</v>
+        <v>0.05144440096815943</v>
       </c>
       <c r="AC28">
-        <v>-0.01468780579799047</v>
+        <v>-0.04369925801782285</v>
       </c>
       <c r="AD28">
-        <v>21522.3</v>
+        <v>18271.8</v>
       </c>
       <c r="AE28">
-        <v>15.13315765732494</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>21537.43315765732</v>
+        <v>18271.8</v>
       </c>
       <c r="AG28">
-        <v>20911.73315765732</v>
+        <v>17603.8</v>
       </c>
       <c r="AH28">
-        <v>0.9120530408023619</v>
+        <v>0.9006121785077039</v>
       </c>
       <c r="AI28">
-        <v>0.8680691949246263</v>
+        <v>0.8178924892905582</v>
       </c>
       <c r="AJ28">
-        <v>0.9096593077184556</v>
+        <v>0.8972283666833161</v>
       </c>
       <c r="AK28">
-        <v>0.8646559639318242</v>
+        <v>0.8122793822472211</v>
       </c>
       <c r="AL28">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>-17.15</v>
+        <v>-8.34</v>
       </c>
       <c r="AN28">
-        <v>24.74766290661975</v>
-      </c>
-      <c r="AO28">
-        <v>63.53383458646616</v>
+        <v>37.43454210202827</v>
       </c>
       <c r="AP28">
-        <v>24.04559563703166</v>
+        <v>36.0659700880967</v>
       </c>
       <c r="AQ28">
-        <v>-24.63556851311954</v>
+        <v>-33.09352517985612</v>
       </c>
     </row>
     <row r="29">
@@ -4113,7 +4125,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Credit Saison Co., Ltd. (TSE:8253)</t>
+          <t>NEC Capital Solutions Limited (TSE:8793)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4122,49 +4134,46 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.0522</v>
+        <v>0.0228</v>
       </c>
       <c r="E29">
-        <v>0.0351</v>
-      </c>
-      <c r="F29">
-        <v>-0.004269999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="G29">
-        <v>0.1888242955621208</v>
+        <v>0.1148550319041755</v>
       </c>
       <c r="H29">
-        <v>0.1888242955621208</v>
+        <v>0.1148550319041755</v>
       </c>
       <c r="I29">
-        <v>0.1245909971727183</v>
+        <v>0.04072133168978571</v>
       </c>
       <c r="J29">
-        <v>0.0851971377575949</v>
+        <v>0.0289543029648647</v>
       </c>
       <c r="K29">
-        <v>334.3</v>
+        <v>54.4</v>
       </c>
       <c r="L29">
-        <v>0.10619778264875</v>
+        <v>0.03044889734691593</v>
       </c>
       <c r="M29">
-        <v>62.98890000000001</v>
+        <v>11.739</v>
       </c>
       <c r="N29">
-        <v>0.03838212174760832</v>
+        <v>0.03351127604910077</v>
       </c>
       <c r="O29">
-        <v>0.1884202811845648</v>
+        <v>0.2157904411764706</v>
       </c>
       <c r="P29">
-        <v>62.98890000000001</v>
+        <v>11.739</v>
       </c>
       <c r="Q29">
-        <v>0.03838212174760832</v>
+        <v>0.03351127604910077</v>
       </c>
       <c r="R29">
-        <v>0.1884202811845648</v>
+        <v>0.2157904411764706</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4173,70 +4182,73 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>976.9</v>
+        <v>165.5</v>
       </c>
       <c r="V29">
-        <v>0.5952714642617757</v>
+        <v>0.4724521838424208</v>
       </c>
       <c r="W29">
-        <v>0.07034340543725276</v>
+        <v>0.06098654708520179</v>
       </c>
       <c r="X29">
-        <v>0.1105293562870998</v>
+        <v>0.187975312505038</v>
       </c>
       <c r="Y29">
-        <v>-0.04018595084984702</v>
+        <v>-0.1269887654198362</v>
       </c>
       <c r="Z29">
-        <v>0.1186955144641187</v>
+        <v>0.2246126949212122</v>
       </c>
       <c r="AA29">
-        <v>0.01011251809700812</v>
+        <v>0.006503504018503505</v>
       </c>
       <c r="AB29">
-        <v>0.02656860898824271</v>
+        <v>0.05150669349802113</v>
       </c>
       <c r="AC29">
-        <v>-0.01645609089123459</v>
+        <v>-0.04500318947951763</v>
       </c>
       <c r="AD29">
-        <v>22163</v>
+        <v>5509.6</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>79.23634401514434</v>
       </c>
       <c r="AF29">
-        <v>22163</v>
+        <v>5588.836344015144</v>
       </c>
       <c r="AG29">
-        <v>21186.1</v>
+        <v>5423.336344015144</v>
       </c>
       <c r="AH29">
-        <v>0.9310580950340488</v>
+        <v>0.9410183602952646</v>
       </c>
       <c r="AI29">
-        <v>0.8180311592250425</v>
+        <v>0.8622836123625263</v>
       </c>
       <c r="AJ29">
-        <v>0.9281076960818673</v>
+        <v>0.9393276647284661</v>
       </c>
       <c r="AK29">
-        <v>0.8112244507240717</v>
+        <v>0.8586749531055977</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>0.166</v>
       </c>
       <c r="AM29">
-        <v>-10.7</v>
+        <v>-7.274</v>
       </c>
       <c r="AN29">
-        <v>33.88319828772359</v>
+        <v>28.56194919647486</v>
+      </c>
+      <c r="AO29">
+        <v>456.0240963855422</v>
       </c>
       <c r="AP29">
-        <v>32.38969576517352</v>
+        <v>28.11475554180997</v>
       </c>
       <c r="AQ29">
-        <v>-36.65420560747663</v>
+        <v>-10.40692878746219</v>
       </c>
     </row>
     <row r="30">
@@ -4247,7 +4259,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ricoh Leasing Company, Ltd. (TSE:8566)</t>
+          <t>JACCS Co., Ltd. (TSE:8584)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4256,121 +4268,115 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.015</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="E30">
-        <v>0.0373</v>
+        <v>0.184</v>
       </c>
       <c r="G30">
-        <v>0.1131697728596389</v>
+        <v>0.2657342657342657</v>
       </c>
       <c r="H30">
-        <v>0.1131697728596389</v>
+        <v>0.2657342657342657</v>
       </c>
       <c r="I30">
-        <v>0.06515423643905609</v>
+        <v>0.1742208408875076</v>
       </c>
       <c r="J30">
-        <v>0.04447035185522876</v>
+        <v>0.1204746202262348</v>
       </c>
       <c r="K30">
-        <v>124.7</v>
+        <v>136.3</v>
       </c>
       <c r="L30">
-        <v>0.04539167152009319</v>
+        <v>0.1176724510057844</v>
       </c>
       <c r="M30">
-        <v>30.3688</v>
+        <v>43.035</v>
       </c>
       <c r="N30">
-        <v>0.02938726533772015</v>
+        <v>0.03968188105117566</v>
       </c>
       <c r="O30">
-        <v>0.2435348837209302</v>
+        <v>0.3157373440939105</v>
       </c>
       <c r="P30">
-        <v>30.3688</v>
+        <v>43.02800000000001</v>
       </c>
       <c r="Q30">
-        <v>0.02938726533772015</v>
+        <v>0.03967542646380821</v>
       </c>
       <c r="R30">
-        <v>0.2435348837209302</v>
+        <v>0.3156859867938371</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>0.006999999999997897</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>0.0001626583013825467</v>
       </c>
       <c r="U30">
-        <v>152.8</v>
+        <v>1041.1</v>
       </c>
       <c r="V30">
-        <v>0.1478614282949487</v>
+        <v>0.9599815583218072</v>
       </c>
       <c r="W30">
-        <v>0.07053965380699175</v>
+        <v>0.0849009592624891</v>
       </c>
       <c r="X30">
-        <v>0.07225884176104273</v>
+        <v>0.19308890423095</v>
       </c>
       <c r="Y30">
-        <v>-0.001719187954050988</v>
+        <v>-0.1081879449684609</v>
       </c>
       <c r="Z30">
-        <v>0.2843732958535165</v>
+        <v>0.05302520150537919</v>
       </c>
       <c r="AA30">
-        <v>0.01264618052483694</v>
+        <v>0.006388191013780129</v>
       </c>
       <c r="AB30">
-        <v>0.02997344335275699</v>
+        <v>0.05150975905807103</v>
       </c>
       <c r="AC30">
-        <v>-0.01732726282792005</v>
+        <v>-0.0451215680442909</v>
       </c>
       <c r="AD30">
-        <v>7696.8</v>
+        <v>17944.1</v>
       </c>
       <c r="AE30">
-        <v>65.04140827312567</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>7761.841408273126</v>
+        <v>17944.1</v>
       </c>
       <c r="AG30">
-        <v>7609.041408273126</v>
+        <v>16903</v>
       </c>
       <c r="AH30">
-        <v>0.8825046463161379</v>
+        <v>0.9430068423320686</v>
       </c>
       <c r="AI30">
-        <v>0.8138540759750095</v>
+        <v>0.9272478296816866</v>
       </c>
       <c r="AJ30">
-        <v>0.8804273062226653</v>
+        <v>0.9397081306462821</v>
       </c>
       <c r="AK30">
-        <v>0.8108231656581766</v>
+        <v>0.9231113708228431</v>
       </c>
       <c r="AL30">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1.21</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>21.96575342465754</v>
-      </c>
-      <c r="AO30">
-        <v>80.13333333333334</v>
+        <v>65.63313825896122</v>
       </c>
       <c r="AP30">
-        <v>21.71530082269728</v>
-      </c>
-      <c r="AQ30">
-        <v>-149.0082644628099</v>
+        <v>61.82516459400147</v>
       </c>
     </row>
     <row r="31">
@@ -4381,7 +4387,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mitsubishi HC Capital Inc. (TSE:8593)</t>
+          <t>Showa Holdings Co., Ltd. (TSE:5103)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4390,121 +4396,115 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.0949</v>
-      </c>
-      <c r="E31">
-        <v>0.108</v>
+        <v>-0.103</v>
       </c>
       <c r="G31">
-        <v>0.16625322953057</v>
+        <v>0.02693032015065913</v>
       </c>
       <c r="H31">
-        <v>0.16625322953057</v>
+        <v>0.02354048964218456</v>
       </c>
       <c r="I31">
-        <v>0.06946598328866777</v>
+        <v>0.005969514708465569</v>
       </c>
       <c r="J31">
-        <v>0.04916399327169416</v>
+        <v>0.002984757354232784</v>
       </c>
       <c r="K31">
-        <v>820.7</v>
+        <v>-0.104</v>
       </c>
       <c r="L31">
-        <v>0.07044453790889506</v>
+        <v>-0.001958568738229755</v>
       </c>
       <c r="M31">
-        <v>331.6467</v>
+        <v>-0</v>
       </c>
       <c r="N31">
-        <v>0.04674503861983424</v>
+        <v>-0</v>
       </c>
       <c r="O31">
-        <v>0.404102229803826</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>331.6467</v>
+        <v>-0</v>
       </c>
       <c r="Q31">
-        <v>0.04674503861983424</v>
+        <v>-0</v>
       </c>
       <c r="R31">
-        <v>0.404102229803826</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
       </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
       <c r="U31">
-        <v>3639.1</v>
+        <v>2.35</v>
       </c>
       <c r="V31">
-        <v>0.5129249591249929</v>
+        <v>0.08867924528301888</v>
       </c>
       <c r="W31">
-        <v>0.1110419570011771</v>
+        <v>-0.004333333333333333</v>
       </c>
       <c r="X31">
-        <v>0.08419381839803006</v>
+        <v>0.05380741711722725</v>
       </c>
       <c r="Y31">
-        <v>0.02684813860314708</v>
+        <v>-0.05814075045056058</v>
       </c>
       <c r="Z31">
-        <v>0.2387351553994028</v>
+        <v>1.75478636226851</v>
       </c>
       <c r="AA31">
-        <v>0.0117371735737731</v>
+        <v>0.00523761149988833</v>
       </c>
       <c r="AB31">
-        <v>0.02939713489148119</v>
+        <v>0.05052252180448812</v>
       </c>
       <c r="AC31">
-        <v>-0.01765996131770809</v>
+        <v>-0.04528491030459979</v>
       </c>
       <c r="AD31">
-        <v>66496</v>
+        <v>5.32</v>
       </c>
       <c r="AE31">
-        <v>55.00227446016967</v>
+        <v>6.180093844902393</v>
       </c>
       <c r="AF31">
-        <v>66551.00227446017</v>
+        <v>11.50009384490239</v>
       </c>
       <c r="AG31">
-        <v>62911.90227446018</v>
+        <v>9.150093844902393</v>
       </c>
       <c r="AH31">
-        <v>0.9036632125540653</v>
+        <v>0.3026333011660469</v>
       </c>
       <c r="AI31">
-        <v>0.8556411726072737</v>
+        <v>0.3616371039969707</v>
       </c>
       <c r="AJ31">
-        <v>0.8986554177029373</v>
+        <v>0.2566639483393889</v>
       </c>
       <c r="AK31">
-        <v>0.848555440308263</v>
+        <v>0.31069829159428</v>
       </c>
       <c r="AL31">
-        <v>42.5</v>
+        <v>0.09</v>
       </c>
       <c r="AM31">
-        <v>14</v>
+        <v>-0.05499999999999999</v>
       </c>
       <c r="AN31">
-        <v>22.52421922633968</v>
+        <v>2.568807339449541</v>
       </c>
       <c r="AO31">
-        <v>18.69411764705882</v>
+        <v>-3.3</v>
       </c>
       <c r="AP31">
-        <v>21.31017623279594</v>
+        <v>4.418200794255139</v>
       </c>
       <c r="AQ31">
-        <v>56.75</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="32">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NEC Capital Solutions Limited (TSE:8793)</t>
+          <t>Wedge Holdings CO.,LTD. (TSE:2388)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4524,121 +4524,115 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.0393</v>
-      </c>
-      <c r="E32">
-        <v>0.07190000000000001</v>
+        <v>-0.416</v>
       </c>
       <c r="G32">
-        <v>0.09141955543180658</v>
+        <v>0.6539278131634819</v>
       </c>
       <c r="H32">
-        <v>0.09141955543180658</v>
+        <v>0.6539278131634819</v>
       </c>
       <c r="I32">
-        <v>0.04301851860382249</v>
+        <v>0.0762208067940552</v>
       </c>
       <c r="J32">
-        <v>0.03234758256882761</v>
+        <v>0.0381104033970276</v>
       </c>
       <c r="K32">
-        <v>56.8</v>
+        <v>0.38</v>
       </c>
       <c r="L32">
-        <v>0.0263585317184092</v>
+        <v>0.08067940552016985</v>
       </c>
       <c r="M32">
-        <v>12.483</v>
+        <v>-0</v>
       </c>
       <c r="N32">
-        <v>0.03321713677488026</v>
+        <v>-0</v>
       </c>
       <c r="O32">
-        <v>0.2197711267605634</v>
+        <v>-0</v>
       </c>
       <c r="P32">
-        <v>11.954</v>
+        <v>-0</v>
       </c>
       <c r="Q32">
-        <v>0.03180947312400213</v>
+        <v>-0</v>
       </c>
       <c r="R32">
-        <v>0.2104577464788732</v>
+        <v>-0</v>
       </c>
       <c r="S32">
-        <v>0.5289999999999999</v>
-      </c>
-      <c r="T32">
-        <v>0.04237763358167106</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>302.2</v>
+        <v>1.62</v>
       </c>
       <c r="V32">
-        <v>0.8041511442256519</v>
+        <v>0.04122137404580153</v>
       </c>
       <c r="W32">
-        <v>0.06438449331217411</v>
+        <v>0.0117283950617284</v>
       </c>
       <c r="X32">
-        <v>0.1499753821469331</v>
+        <v>0.05072025557612126</v>
       </c>
       <c r="Y32">
-        <v>-0.08559088883475902</v>
+        <v>-0.03899186051439286</v>
       </c>
       <c r="Z32">
-        <v>0.2640476508137206</v>
+        <v>0.1381231671554252</v>
       </c>
       <c r="AA32">
-        <v>0.008541303186801788</v>
+        <v>0.005263929618768329</v>
       </c>
       <c r="AB32">
-        <v>0.02661872709163323</v>
+        <v>0.05079623987691652</v>
       </c>
       <c r="AC32">
-        <v>-0.01807742390483144</v>
+        <v>-0.04553231025814819</v>
       </c>
       <c r="AD32">
-        <v>7299.4</v>
+        <v>3.02</v>
       </c>
       <c r="AE32">
-        <v>97.49697130311449</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>7396.896971303114</v>
+        <v>3.02</v>
       </c>
       <c r="AG32">
-        <v>7094.696971303114</v>
+        <v>1.4</v>
       </c>
       <c r="AH32">
-        <v>0.9516512735042344</v>
+        <v>0.07136105860113422</v>
       </c>
       <c r="AI32">
-        <v>0.8733985448940935</v>
+        <v>0.1306228373702422</v>
       </c>
       <c r="AJ32">
-        <v>0.9496954484496033</v>
+        <v>0.0343980343980344</v>
       </c>
       <c r="AK32">
-        <v>0.8687139064240064</v>
+        <v>0.06511627906976744</v>
       </c>
       <c r="AL32">
-        <v>0.188</v>
+        <v>0.083</v>
       </c>
       <c r="AM32">
-        <v>-4.172000000000001</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="AN32">
-        <v>28.30321830166731</v>
+        <v>0.9805194805194805</v>
       </c>
       <c r="AO32">
-        <v>529.7872340425531</v>
+        <v>4.325301204819277</v>
       </c>
       <c r="AP32">
-        <v>27.50948806243937</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AQ32">
-        <v>-23.87344199424736</v>
+        <v>-8.756097560975611</v>
       </c>
     </row>
     <row r="33">
@@ -4658,46 +4652,46 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.0688</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="E33">
-        <v>0.067</v>
+        <v>0.126</v>
       </c>
       <c r="G33">
-        <v>0.07960534637601721</v>
+        <v>0.07984748853401116</v>
       </c>
       <c r="H33">
-        <v>0.07960534637601721</v>
+        <v>0.07984748853401116</v>
       </c>
       <c r="I33">
-        <v>0.05292144190892882</v>
+        <v>0.04200475396314884</v>
       </c>
       <c r="J33">
-        <v>0.03769686008210128</v>
+        <v>0.03266796830296227</v>
       </c>
       <c r="K33">
-        <v>163.8</v>
+        <v>145.1</v>
       </c>
       <c r="L33">
-        <v>0.03453219209849476</v>
+        <v>0.04008951759960214</v>
       </c>
       <c r="M33">
-        <v>46.4156</v>
+        <v>40.1236</v>
       </c>
       <c r="N33">
-        <v>0.03463075430873685</v>
+        <v>0.03277268643306379</v>
       </c>
       <c r="O33">
-        <v>0.2833675213675214</v>
+        <v>0.2765237767057202</v>
       </c>
       <c r="P33">
-        <v>46.4156</v>
+        <v>40.1236</v>
       </c>
       <c r="Q33">
-        <v>0.03463075430873685</v>
+        <v>0.03277268643306379</v>
       </c>
       <c r="R33">
-        <v>0.2833675213675214</v>
+        <v>0.2765237767057202</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -4706,73 +4700,73 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>168.6</v>
+        <v>179.9</v>
       </c>
       <c r="V33">
-        <v>0.1257927329702306</v>
+        <v>0.1469411092052602</v>
       </c>
       <c r="W33">
-        <v>0.08943000655164884</v>
+        <v>0.07608011744966442</v>
       </c>
       <c r="X33">
-        <v>0.1222134546883389</v>
+        <v>0.1672374835565439</v>
       </c>
       <c r="Y33">
-        <v>-0.03278344813669004</v>
+        <v>-0.09115736610687949</v>
       </c>
       <c r="Z33">
-        <v>0.2086194281869745</v>
+        <v>0.1623640101726762</v>
       </c>
       <c r="AA33">
-        <v>0.007864297394772355</v>
+        <v>0.005304102337862828</v>
       </c>
       <c r="AB33">
-        <v>0.02658740578112181</v>
+        <v>0.05149170709006926</v>
       </c>
       <c r="AC33">
-        <v>-0.01872310838634945</v>
+        <v>-0.04618760475220643</v>
       </c>
       <c r="AD33">
-        <v>20553.3</v>
+        <v>16595.9</v>
       </c>
       <c r="AE33">
-        <v>0.1321622459353829</v>
+        <v>0.08496752889553838</v>
       </c>
       <c r="AF33">
-        <v>20553.43216224594</v>
+        <v>16595.9849675289</v>
       </c>
       <c r="AG33">
-        <v>20384.83216224594</v>
+        <v>16416.0849675289</v>
       </c>
       <c r="AH33">
-        <v>0.9387815658807024</v>
+        <v>0.9312973949501454</v>
       </c>
       <c r="AI33">
-        <v>0.9111479830692145</v>
+        <v>0.9002879718066962</v>
       </c>
       <c r="AJ33">
-        <v>0.938306474271803</v>
+        <v>0.9305967527208958</v>
       </c>
       <c r="AK33">
-        <v>0.9104788883519217</v>
+        <v>0.8993052824177213</v>
       </c>
       <c r="AL33">
-        <v>13.2</v>
+        <v>9.81</v>
       </c>
       <c r="AM33">
-        <v>8.969999999999999</v>
+        <v>4.180000000000001</v>
       </c>
       <c r="AN33">
-        <v>51.53088598835664</v>
+        <v>61.25101033773885</v>
       </c>
       <c r="AO33">
-        <v>19.01515151515152</v>
+        <v>15.49439347604485</v>
       </c>
       <c r="AP33">
-        <v>51.10850627609586</v>
+        <v>60.58736133932548</v>
       </c>
       <c r="AQ33">
-        <v>27.98216276477146</v>
+        <v>36.36363636363636</v>
       </c>
     </row>
     <row r="34">
@@ -4783,7 +4777,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tokyo Century Corporation (TSE:8439)</t>
+          <t>Ricoh Leasing Company, Ltd. (TSE:8566)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4792,121 +4786,121 @@
         </is>
       </c>
       <c r="D34">
-        <v>0.0542</v>
+        <v>0.00119</v>
       </c>
       <c r="E34">
-        <v>0.07240000000000001</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="G34">
-        <v>0.2234992453036062</v>
+        <v>0.1497654625465448</v>
       </c>
       <c r="H34">
-        <v>0.2234992453036062</v>
+        <v>0.1497654625465448</v>
       </c>
       <c r="I34">
-        <v>0.069914928076157</v>
+        <v>0.06742650564888246</v>
       </c>
       <c r="J34">
-        <v>0.04810675734566401</v>
+        <v>0.04660219969598225</v>
       </c>
       <c r="K34">
-        <v>491.4</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="L34">
-        <v>0.04468166360544836</v>
+        <v>0.04685913245321341</v>
       </c>
       <c r="M34">
-        <v>154.026</v>
+        <v>27.5686</v>
       </c>
       <c r="N34">
-        <v>0.02600824018101381</v>
+        <v>0.03109474396571171</v>
       </c>
       <c r="O34">
-        <v>0.3134432234432235</v>
+        <v>0.2845056759545924</v>
       </c>
       <c r="P34">
-        <v>153.972</v>
+        <v>27.5686</v>
       </c>
       <c r="Q34">
-        <v>0.02599912194792476</v>
+        <v>0.03109474396571171</v>
       </c>
       <c r="R34">
-        <v>0.3133333333333334</v>
+        <v>0.2845056759545924</v>
       </c>
       <c r="S34">
-        <v>0.05400000000000205</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>0.000350590160102853</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>1600.2</v>
+        <v>43.3</v>
       </c>
       <c r="V34">
-        <v>0.2702036405389889</v>
+        <v>0.04883825851567786</v>
       </c>
       <c r="W34">
-        <v>0.09102359871077685</v>
+        <v>0.05458232411423422</v>
       </c>
       <c r="X34">
-        <v>0.06615094548523949</v>
+        <v>0.1098771625787391</v>
       </c>
       <c r="Y34">
-        <v>0.02487265322553736</v>
+        <v>-0.05529483846450484</v>
       </c>
       <c r="Z34">
-        <v>0.2504654577981857</v>
+        <v>0.2208789010772109</v>
       </c>
       <c r="AA34">
-        <v>0.01204908100176797</v>
+        <v>0.01029344265662929</v>
       </c>
       <c r="AB34">
-        <v>0.03102797320944552</v>
+        <v>0.05784487159264122</v>
       </c>
       <c r="AC34">
-        <v>-0.01897889220767755</v>
+        <v>-0.04755142893601193</v>
       </c>
       <c r="AD34">
-        <v>38741.7</v>
+        <v>6092.5</v>
       </c>
       <c r="AE34">
-        <v>74.44802002020333</v>
+        <v>42.84364484337987</v>
       </c>
       <c r="AF34">
-        <v>38816.1480200202</v>
+        <v>6135.343644843379</v>
       </c>
       <c r="AG34">
-        <v>37215.9480200202</v>
+        <v>6092.043644843379</v>
       </c>
       <c r="AH34">
-        <v>0.8676258676929725</v>
+        <v>0.873738661994093</v>
       </c>
       <c r="AI34">
-        <v>0.8505235161535428</v>
+        <v>0.8117312381038893</v>
       </c>
       <c r="AJ34">
-        <v>0.8627154787161578</v>
+        <v>0.8729552553302931</v>
       </c>
       <c r="AK34">
-        <v>0.8450919879713488</v>
+        <v>0.8106464756227432</v>
       </c>
       <c r="AL34">
-        <v>27.2</v>
+        <v>0.27</v>
       </c>
       <c r="AM34">
-        <v>16.8</v>
+        <v>-2.76</v>
       </c>
       <c r="AN34">
-        <v>15.37064074588375</v>
+        <v>22.13844476744186</v>
       </c>
       <c r="AO34">
-        <v>27.9375</v>
+        <v>508.5185185185185</v>
       </c>
       <c r="AP34">
-        <v>14.76530371752438</v>
+        <v>22.13678650015763</v>
       </c>
       <c r="AQ34">
-        <v>45.23214285714286</v>
+        <v>-49.74637681159421</v>
       </c>
     </row>
     <row r="35">
@@ -4917,7 +4911,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JACCS Co., Ltd. (TSE:8584)</t>
+          <t>Mitsubishi HC Capital Inc. (TSE:8593)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4926,115 +4920,121 @@
         </is>
       </c>
       <c r="D35">
-        <v>0.06849999999999999</v>
+        <v>0.167</v>
       </c>
       <c r="E35">
-        <v>0.149</v>
+        <v>0.129</v>
       </c>
       <c r="G35">
-        <v>0.163153196456774</v>
+        <v>0.2810813727606303</v>
       </c>
       <c r="H35">
-        <v>0.163153196456774</v>
+        <v>0.2810813727606303</v>
       </c>
       <c r="I35">
-        <v>0.15347112545492</v>
+        <v>0.07077876453645143</v>
       </c>
       <c r="J35">
-        <v>0.1060545004258252</v>
+        <v>0.05059545517802989</v>
       </c>
       <c r="K35">
-        <v>150.4</v>
+        <v>705.6</v>
       </c>
       <c r="L35">
-        <v>0.1032754240197762</v>
+        <v>0.05439240233110296</v>
       </c>
       <c r="M35">
-        <v>41.875</v>
+        <v>297.252</v>
       </c>
       <c r="N35">
-        <v>0.04699248120300752</v>
+        <v>0.04206019271857711</v>
       </c>
       <c r="O35">
-        <v>0.2784242021276596</v>
+        <v>0.4212755102040817</v>
       </c>
       <c r="P35">
-        <v>41.866</v>
+        <v>297.252</v>
       </c>
       <c r="Q35">
-        <v>0.04698238132645045</v>
+        <v>0.04206019271857711</v>
       </c>
       <c r="R35">
-        <v>0.2783643617021276</v>
+        <v>0.4212755102040817</v>
       </c>
       <c r="S35">
-        <v>0.009000000000000341</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>0.0002149253731343365</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>1319</v>
+        <v>4689.1</v>
       </c>
       <c r="V35">
-        <v>1.480193019863091</v>
+        <v>0.6634924228488956</v>
       </c>
       <c r="W35">
-        <v>0.09839068428627504</v>
+        <v>0.0639049395909939</v>
       </c>
       <c r="X35">
-        <v>0.1788107062158209</v>
+        <v>0.1236405817852306</v>
       </c>
       <c r="Y35">
-        <v>-0.08042002192954589</v>
+        <v>-0.05973564219423669</v>
       </c>
       <c r="Z35">
-        <v>0.06828465459115014</v>
+        <v>0.1765707965236033</v>
       </c>
       <c r="AA35">
-        <v>0.007241894929414463</v>
+        <v>0.008933679821259005</v>
       </c>
       <c r="AB35">
-        <v>0.02663981552802444</v>
+        <v>0.05672746756579027</v>
       </c>
       <c r="AC35">
-        <v>-0.01939792059860998</v>
+        <v>-0.04779378774453126</v>
       </c>
       <c r="AD35">
-        <v>21564</v>
+        <v>60070.3</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>88.14777463668747</v>
       </c>
       <c r="AF35">
-        <v>21564</v>
+        <v>60158.44777463669</v>
       </c>
       <c r="AG35">
-        <v>20245</v>
+        <v>55469.34777463669</v>
       </c>
       <c r="AH35">
-        <v>0.9603163646565814</v>
+        <v>0.894872125131401</v>
       </c>
       <c r="AI35">
-        <v>0.9289382086363167</v>
+        <v>0.8481090059907328</v>
       </c>
       <c r="AJ35">
-        <v>0.9578399042396658</v>
+        <v>0.8869894653536846</v>
       </c>
       <c r="AK35">
-        <v>0.9246572214153262</v>
+        <v>0.8373572537931852</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>45.4</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="AN35">
-        <v>67.87535410764873</v>
+        <v>18.18603735884472</v>
+      </c>
+      <c r="AO35">
+        <v>19.80396475770925</v>
       </c>
       <c r="AP35">
-        <v>63.72363865281712</v>
+        <v>16.7931179118515</v>
+      </c>
+      <c r="AQ35">
+        <v>36.40080971659919</v>
       </c>
     </row>
     <row r="36">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Japan Securities Finance Co., Ltd. (TSE:8511)</t>
+          <t>AEON Financial Service Co., Ltd. (TSE:8570)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5053,47 +5053,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D36">
-        <v>0.0765</v>
-      </c>
-      <c r="E36">
-        <v>0.113</v>
-      </c>
       <c r="G36">
-        <v>0.2017448200654307</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>0.2017448200654307</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>0.178117048346056</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>0.1253301934636026</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>40.6</v>
+        <v>218.3</v>
       </c>
       <c r="L36">
-        <v>0.1475826972010178</v>
+        <v>0.06955995284070994</v>
       </c>
       <c r="M36">
-        <v>24.6942</v>
+        <v>76.17740000000001</v>
       </c>
       <c r="N36">
-        <v>0.03225891574134553</v>
+        <v>0.03324346497927122</v>
       </c>
       <c r="O36">
-        <v>0.6082315270935961</v>
+        <v>0.3489573980760421</v>
       </c>
       <c r="P36">
-        <v>24.6942</v>
+        <v>76.17740000000001</v>
       </c>
       <c r="Q36">
-        <v>0.03225891574134553</v>
+        <v>0.03324346497927122</v>
       </c>
       <c r="R36">
-        <v>0.6082315270935961</v>
+        <v>0.3489573980760421</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -5102,70 +5096,61 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>11262.2</v>
+        <v>4972.9</v>
       </c>
       <c r="V36">
-        <v>14.71221423905944</v>
+        <v>2.170150556404102</v>
       </c>
       <c r="W36">
-        <v>0.03314826910516003</v>
+        <v>0.05696466781483222</v>
       </c>
       <c r="X36">
-        <v>0.2185110873055296</v>
+        <v>0.08175854546456482</v>
       </c>
       <c r="Y36">
-        <v>-0.1853628182003696</v>
+        <v>-0.0247938776497326</v>
       </c>
       <c r="Z36">
-        <v>0.04348582087192945</v>
+        <v>0.4604448487338244</v>
       </c>
       <c r="AA36">
-        <v>0.005450086342802488</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>0.0287637692005123</v>
+        <v>0.0512673150276395</v>
       </c>
       <c r="AC36">
-        <v>-0.02331368285770981</v>
+        <v>-0.0512673150276395</v>
       </c>
       <c r="AD36">
-        <v>23284.4</v>
+        <v>8403.700000000001</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>23284.4</v>
+        <v>8403.700000000001</v>
       </c>
       <c r="AG36">
-        <v>12022.2</v>
+        <v>3430.800000000001</v>
       </c>
       <c r="AH36">
-        <v>0.9681703458226437</v>
+        <v>0.7857450071059915</v>
       </c>
       <c r="AI36">
-        <v>0.9498331579247946</v>
+        <v>0.6840952753085213</v>
       </c>
       <c r="AJ36">
-        <v>0.9401377886562869</v>
+        <v>0.5995491323418906</v>
       </c>
       <c r="AK36">
-        <v>0.9071989133715667</v>
+        <v>0.4692333994392396</v>
       </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-4.12</v>
-      </c>
-      <c r="AN36">
-        <v>379.8433931484503</v>
-      </c>
-      <c r="AP36">
-        <v>196.120717781403</v>
-      </c>
-      <c r="AQ36">
-        <v>-11.89320388349515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -5176,7 +5161,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AEON Financial Service Co., Ltd. (TSE:8570)</t>
+          <t>Tokyo Century Corporation (TSE:8439)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5184,107 +5169,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="F37">
-        <v>0.347</v>
+      <c r="D37">
+        <v>0.0509</v>
+      </c>
+      <c r="E37">
+        <v>-0.25</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>0.2652119602525292</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>0.2652119602525292</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>0.06523749807327736</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>0.03261874903663868</v>
       </c>
       <c r="K37">
-        <v>312.5</v>
+        <v>74.8</v>
       </c>
       <c r="L37">
-        <v>0.0724100377690757</v>
+        <v>0.008417641034874692</v>
       </c>
       <c r="M37">
-        <v>78.55120000000001</v>
+        <v>60.9124</v>
       </c>
       <c r="N37">
-        <v>0.03373902585688515</v>
+        <v>0.01466673087573138</v>
       </c>
       <c r="O37">
-        <v>0.25136384</v>
+        <v>0.8143368983957219</v>
       </c>
       <c r="P37">
-        <v>78.55120000000001</v>
+        <v>60.9054</v>
       </c>
       <c r="Q37">
-        <v>0.03373902585688515</v>
+        <v>0.01466504538778262</v>
       </c>
       <c r="R37">
-        <v>0.25136384</v>
+        <v>0.8142433155080214</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>0.006999999999997897</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>0.0001149191297666468</v>
       </c>
       <c r="U37">
-        <v>6573.8</v>
+        <v>1337.3</v>
       </c>
       <c r="V37">
-        <v>2.823554677433211</v>
+        <v>0.3220004334111868</v>
       </c>
       <c r="W37">
-        <v>0.08931888987338155</v>
+        <v>0.0129883660357701</v>
       </c>
       <c r="X37">
-        <v>0.0509081614853624</v>
+        <v>0.1151648996172618</v>
       </c>
       <c r="Y37">
-        <v>0.03841072838801915</v>
+        <v>-0.1021765335814917</v>
       </c>
       <c r="Z37">
-        <v>0.7200273616069941</v>
+        <v>0.2091267017625525</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>0.006821451401652685</v>
       </c>
       <c r="AB37">
-        <v>0.02626538127821135</v>
+        <v>0.05921373620710002</v>
       </c>
       <c r="AC37">
-        <v>-0.02626538127821135</v>
+        <v>-0.05239228480544734</v>
       </c>
       <c r="AD37">
-        <v>9701.6</v>
+        <v>31222.7</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>57.46534185524983</v>
       </c>
       <c r="AF37">
-        <v>9701.6</v>
+        <v>31280.16534185525</v>
       </c>
       <c r="AG37">
-        <v>3127.8</v>
+        <v>29942.86534185525</v>
       </c>
       <c r="AH37">
-        <v>0.8064639478628074</v>
+        <v>0.8827909321951714</v>
       </c>
       <c r="AI37">
-        <v>0.6814835627985389</v>
+        <v>0.8317983850884599</v>
       </c>
       <c r="AJ37">
-        <v>0.5732771260997068</v>
+        <v>0.878193799226392</v>
       </c>
       <c r="AK37">
-        <v>0.4082117407533085</v>
+        <v>0.8255963614266341</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>29.2</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>17.3</v>
+      </c>
+      <c r="AN37">
+        <v>15.12288094546159</v>
+      </c>
+      <c r="AO37">
+        <v>19.46575342465754</v>
+      </c>
+      <c r="AP37">
+        <v>14.50298621614611</v>
+      </c>
+      <c r="AQ37">
+        <v>32.85549132947978</v>
       </c>
     </row>
     <row r="38">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bank of Japan (TSE:8301)</t>
+          <t>Japan Securities Finance Co., Ltd. (TSE:8511)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5303,107 +5303,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D38">
+        <v>0.0741</v>
+      </c>
+      <c r="E38">
+        <v>0.129</v>
+      </c>
       <c r="G38">
-        <v>0</v>
+        <v>0.2460024009603842</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.2448979591836735</v>
       </c>
       <c r="I38">
-        <v>3.357395849918432e-05</v>
+        <v>0.2024809923969588</v>
       </c>
       <c r="J38">
-        <v>2.814000410916768e-05</v>
+        <v>0.1459671587933419</v>
       </c>
       <c r="K38">
-        <v>12042.2</v>
+        <v>45.2</v>
       </c>
       <c r="L38">
-        <v>0.5811087304804371</v>
+        <v>0.1808723489395758</v>
       </c>
       <c r="M38">
-        <v>-0</v>
+        <v>40.5394</v>
       </c>
       <c r="N38">
-        <v>-0</v>
+        <v>0.05315945449777078</v>
       </c>
       <c r="O38">
-        <v>-0</v>
+        <v>0.8968893805309734</v>
       </c>
       <c r="P38">
-        <v>-0</v>
+        <v>18.6394</v>
       </c>
       <c r="Q38">
-        <v>-0</v>
+        <v>0.02444190925780225</v>
       </c>
       <c r="R38">
-        <v>-0</v>
+        <v>0.4123761061946902</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>21.9</v>
+      </c>
+      <c r="T38">
+        <v>0.5402151980542387</v>
       </c>
       <c r="U38">
-        <v>2375.1</v>
+        <v>11624.4</v>
       </c>
       <c r="V38">
-        <v>10.5606936416185</v>
+        <v>15.24311565696302</v>
       </c>
       <c r="W38">
-        <v>0.2991531339509071</v>
+        <v>0.03675394373068792</v>
       </c>
       <c r="X38">
-        <v>29.78301161762492</v>
+        <v>0.2811392358757733</v>
       </c>
       <c r="Y38">
-        <v>-29.48385848367401</v>
+        <v>-0.2443852921450854</v>
       </c>
       <c r="Z38">
-        <v>0.0184799409211997</v>
+        <v>0.01885753093872623</v>
       </c>
       <c r="AA38">
-        <v>5.200256134597353e-07</v>
+        <v>0.00275258021298341</v>
       </c>
       <c r="AB38">
-        <v>0.02993903090280015</v>
+        <v>0.05576177471661138</v>
       </c>
       <c r="AC38">
-        <v>-0.02993851087718669</v>
+        <v>-0.05300919450362797</v>
       </c>
       <c r="AD38">
-        <v>1048222.5</v>
+        <v>20385.5</v>
       </c>
       <c r="AE38">
-        <v>4.521267864065516</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1048227.021267864</v>
+        <v>20385.5</v>
       </c>
       <c r="AG38">
-        <v>1045851.921267864</v>
+        <v>8761.1</v>
       </c>
       <c r="AH38">
-        <v>0.999785493263508</v>
+        <v>0.963940022980788</v>
       </c>
       <c r="AI38">
-        <v>0.9634887438483043</v>
+        <v>0.9554732722457875</v>
       </c>
       <c r="AJ38">
-        <v>0.9997850062295354</v>
+        <v>0.9199260791499102</v>
       </c>
       <c r="AK38">
-        <v>0.9634088618146316</v>
+        <v>0.9021738011141889</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>-4.37</v>
       </c>
       <c r="AN38">
-        <v>655139.0625</v>
+        <v>364.0267857142857</v>
       </c>
       <c r="AP38">
-        <v>653657.450792415</v>
+        <v>156.4482142857143</v>
+      </c>
+      <c r="AQ38">
+        <v>-11.57894736842105</v>
       </c>
     </row>
     <row r="39">
@@ -5414,7 +5426,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Daikokuya Holdings Co.,Ltd. (TSE:6993)</t>
+          <t>Bank of Japan (TSE:8301)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5422,26 +5434,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D39">
-        <v>-0.066</v>
-      </c>
       <c r="G39">
-        <v>-0.01685796269727403</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>-0.01685796269727403</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>-0.00833772607646111</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>-0.00833772607646111</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>-5.5</v>
+        <v>12884.2</v>
       </c>
       <c r="L39">
-        <v>-0.03945480631276901</v>
+        <v>0.4036567905334491</v>
       </c>
       <c r="M39">
         <v>-0</v>
@@ -5450,7 +5459,7 @@
         <v>-0</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P39">
         <v>-0</v>
@@ -5459,207 +5468,67 @@
         <v>-0</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S39">
         <v>0</v>
       </c>
       <c r="U39">
-        <v>6.22</v>
+        <v>2597.8</v>
       </c>
       <c r="V39">
-        <v>0.1132969034608379</v>
+        <v>14.09549647314162</v>
       </c>
       <c r="W39">
-        <v>-0.3503184713375797</v>
+        <v>0.3243560308541277</v>
       </c>
       <c r="X39">
-        <v>0.0299415884924406</v>
+        <v>39.8966439133965</v>
       </c>
       <c r="Y39">
-        <v>-0.3802600598300203</v>
+        <v>-39.57228788254237</v>
       </c>
       <c r="Z39">
-        <v>3.023441754063721</v>
+        <v>0.02940271551400933</v>
       </c>
       <c r="AA39">
-        <v>-0.02520862915351841</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>0.02694659146941234</v>
+        <v>0.06042737299721482</v>
       </c>
       <c r="AC39">
-        <v>-0.05215522062293075</v>
+        <v>-0.06042737299721482</v>
       </c>
       <c r="AD39">
-        <v>47.5</v>
+        <v>849517.9</v>
       </c>
       <c r="AE39">
-        <v>0.9863950752933937</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>48.48639507529339</v>
+        <v>849517.9</v>
       </c>
       <c r="AG39">
-        <v>42.2663950752934</v>
+        <v>846920.1</v>
       </c>
       <c r="AH39">
-        <v>0.4689823553667977</v>
+        <v>0.9997831004792032</v>
       </c>
       <c r="AI39">
-        <v>0.7734755686151006</v>
+        <v>0.9606367728531464</v>
       </c>
       <c r="AJ39">
-        <v>0.4349898444059959</v>
+        <v>0.9997824353172997</v>
       </c>
       <c r="AK39">
-        <v>0.7485229935244593</v>
+        <v>0.9605207988249466</v>
       </c>
       <c r="AL39">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AM39">
-        <v>1.134</v>
-      </c>
-      <c r="AN39">
-        <v>-243.5897435897435</v>
-      </c>
-      <c r="AO39">
-        <v>-1.572649572649573</v>
-      </c>
-      <c r="AP39">
-        <v>-216.7507439758635</v>
-      </c>
-      <c r="AQ39">
-        <v>-1.622574955908289</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>GFA Co., Ltd. (JASDAQ:8783)</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>0.3779999999999999</v>
-      </c>
-      <c r="G40">
-        <v>-0.4075396825396826</v>
-      </c>
-      <c r="H40">
-        <v>-0.4880952380952381</v>
-      </c>
-      <c r="I40">
-        <v>-0.4563492063492063</v>
-      </c>
-      <c r="J40">
-        <v>-0.4563492063492063</v>
-      </c>
-      <c r="K40">
-        <v>-13.1</v>
-      </c>
-      <c r="L40">
-        <v>-0.5198412698412699</v>
-      </c>
-      <c r="M40">
-        <v>-0</v>
-      </c>
-      <c r="N40">
-        <v>-0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>-0</v>
-      </c>
-      <c r="Q40">
-        <v>-0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>1.69</v>
-      </c>
-      <c r="V40">
-        <v>0.05767918088737201</v>
-      </c>
-      <c r="W40">
-        <v>-1.247619047619048</v>
-      </c>
-      <c r="X40">
-        <v>0.02604596466259863</v>
-      </c>
-      <c r="Y40">
-        <v>-1.273665012281646</v>
-      </c>
-      <c r="Z40">
-        <v>1.365113759479957</v>
-      </c>
-      <c r="AA40">
-        <v>-0.6229685807150596</v>
-      </c>
-      <c r="AB40">
-        <v>0.02551180110506276</v>
-      </c>
-      <c r="AC40">
-        <v>-0.6484803818201224</v>
-      </c>
-      <c r="AD40">
-        <v>8</v>
-      </c>
-      <c r="AE40">
-        <v>0</v>
-      </c>
-      <c r="AF40">
-        <v>8</v>
-      </c>
-      <c r="AG40">
-        <v>6.31</v>
-      </c>
-      <c r="AH40">
-        <v>0.2144772117962467</v>
-      </c>
-      <c r="AI40">
-        <v>0.6294256490952006</v>
-      </c>
-      <c r="AJ40">
-        <v>0.1771974164560517</v>
-      </c>
-      <c r="AK40">
-        <v>0.5725952813067151</v>
-      </c>
-      <c r="AL40">
-        <v>0.251</v>
-      </c>
-      <c r="AM40">
-        <v>0.224</v>
-      </c>
-      <c r="AN40">
-        <v>-0.7339449541284403</v>
-      </c>
-      <c r="AO40">
-        <v>-45.81673306772908</v>
-      </c>
-      <c r="AP40">
-        <v>-0.5788990825688074</v>
-      </c>
-      <c r="AQ40">
-        <v>-51.33928571428572</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0445</v>
+        <v>0.04405000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0799</v>
+        <v>0.08825</v>
       </c>
       <c r="F2">
-        <v>0.09080000000000001</v>
+        <v>0.1434</v>
       </c>
       <c r="G2">
-        <v>0.2594673849548906</v>
+        <v>0.1617902054925632</v>
       </c>
       <c r="H2">
-        <v>0.2594664762770169</v>
+        <v>0.1617868274408355</v>
       </c>
       <c r="I2">
-        <v>0.1298855797085727</v>
+        <v>0.09668771150835939</v>
       </c>
       <c r="J2">
-        <v>0.09251674514290111</v>
+        <v>0.07096983562990473</v>
       </c>
       <c r="K2">
-        <v>4447.8</v>
+        <v>23020.888</v>
       </c>
       <c r="L2">
-        <v>0.09622898682417083</v>
+        <v>0.2142307175828709</v>
       </c>
       <c r="M2">
-        <v>1872.7705</v>
+        <v>3232.61125</v>
       </c>
       <c r="N2">
-        <v>0.04535332950700968</v>
+        <v>0.03755565044670807</v>
       </c>
       <c r="O2">
-        <v>0.4210554656234543</v>
+        <v>0.1404207887202266</v>
       </c>
       <c r="P2">
-        <v>1447.9705</v>
+        <v>2517.67625</v>
       </c>
       <c r="Q2">
-        <v>0.03506584667097733</v>
+        <v>0.02924971853110355</v>
       </c>
       <c r="R2">
-        <v>0.3255475740815684</v>
+        <v>0.1093648624675121</v>
       </c>
       <c r="S2">
-        <v>424.8000000000001</v>
+        <v>714.9350000000002</v>
       </c>
       <c r="T2">
-        <v>0.2268297156538936</v>
+        <v>0.2211633087647023</v>
       </c>
       <c r="U2">
-        <v>25419.4</v>
+        <v>41821.31</v>
       </c>
       <c r="V2">
-        <v>0.6155876676135607</v>
+        <v>0.4858692796987008</v>
       </c>
       <c r="W2">
-        <v>0.08325550486727253</v>
+        <v>0.09531646437632861</v>
       </c>
       <c r="X2">
-        <v>0.1179039385599455</v>
+        <v>0.0691220742751965</v>
       </c>
       <c r="Y2">
-        <v>-0.03464843369267299</v>
+        <v>0.02619439010113211</v>
       </c>
       <c r="Z2">
-        <v>0.2652530197837112</v>
+        <v>0.09079768030775527</v>
       </c>
       <c r="AA2">
-        <v>0.01440385405790217</v>
+        <v>0.0376026255515813</v>
       </c>
       <c r="AB2">
-        <v>0.05429274308726709</v>
+        <v>0.05502690275621884</v>
       </c>
       <c r="AC2">
-        <v>-0.03911764292550152</v>
+        <v>-0.0161272686382774</v>
       </c>
       <c r="AD2">
-        <v>165331.1</v>
+        <v>1280671.376</v>
       </c>
       <c r="AE2">
-        <v>1496.793101450304</v>
+        <v>3749.720942636133</v>
       </c>
       <c r="AF2">
-        <v>166827.8931014503</v>
+        <v>1284421.096942636</v>
       </c>
       <c r="AG2">
-        <v>141408.4931014503</v>
+        <v>1242599.786942636</v>
       </c>
       <c r="AH2">
-        <v>0.8015916651832505</v>
+        <v>0.9371941184315171</v>
       </c>
       <c r="AI2">
-        <v>0.7668781437288191</v>
+        <v>0.9112171992123629</v>
       </c>
       <c r="AJ2">
-        <v>0.7739869450416784</v>
+        <v>0.9352172435679084</v>
       </c>
       <c r="AK2">
-        <v>0.736034139620608</v>
+        <v>0.9085025024380743</v>
       </c>
       <c r="AL2">
-        <v>1392.68</v>
+        <v>1521.79</v>
       </c>
       <c r="AM2">
-        <v>1332.84</v>
+        <v>1356.999</v>
       </c>
       <c r="AN2">
-        <v>12.13385832550493</v>
+        <v>63.83102656959203</v>
       </c>
       <c r="AO2">
-        <v>4.259628916908407</v>
+        <v>6.724333843697224</v>
       </c>
       <c r="AP2">
-        <v>10.37814797891104</v>
+        <v>61.93346825899918</v>
       </c>
       <c r="AQ2">
-        <v>4.450871822574352</v>
+        <v>7.540922285130643</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORIX Corporation (TSE:8591)</t>
+          <t>Entrust Inc. (TSE:7191)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0445</v>
+        <v>0.222</v>
       </c>
       <c r="E3">
-        <v>0.0411</v>
-      </c>
-      <c r="F3">
-        <v>0.09080000000000001</v>
+        <v>0.184</v>
       </c>
       <c r="G3">
-        <v>0.3036868091932128</v>
+        <v>0.2117647058823529</v>
       </c>
       <c r="H3">
-        <v>0.3036868091932128</v>
+        <v>0.2117647058823529</v>
       </c>
       <c r="I3">
-        <v>0.1872821215543639</v>
+        <v>0.225</v>
       </c>
       <c r="J3">
-        <v>0.1346638921932612</v>
+        <v>0.1323529411764706</v>
       </c>
       <c r="K3">
-        <v>2798.9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L3">
-        <v>0.1402992556204416</v>
+        <v>0.1327941176470588</v>
       </c>
       <c r="M3">
-        <v>1172.9</v>
+        <v>1.4112</v>
       </c>
       <c r="N3">
-        <v>0.04750333118679351</v>
+        <v>0.012134135855546</v>
       </c>
       <c r="O3">
-        <v>0.4190574868698417</v>
+        <v>0.1562790697674419</v>
       </c>
       <c r="P3">
-        <v>796.4</v>
+        <v>1.4112</v>
       </c>
       <c r="Q3">
-        <v>0.03225479832650895</v>
+        <v>0.012134135855546</v>
       </c>
       <c r="R3">
-        <v>0.2845403551395191</v>
+        <v>0.1562790697674419</v>
       </c>
       <c r="S3">
-        <v>376.5000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.320999232671157</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>8159.4</v>
+        <v>41.7</v>
       </c>
       <c r="V3">
-        <v>0.3304618300669477</v>
+        <v>0.358555460017197</v>
       </c>
       <c r="W3">
-        <v>0.1111508234350366</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="X3">
-        <v>0.07439121305479765</v>
+        <v>0.05842561509745306</v>
       </c>
       <c r="Y3">
-        <v>0.03675961038023895</v>
+        <v>0.1804632737914358</v>
       </c>
       <c r="Z3">
-        <v>0.3533606985133169</v>
+        <v>24.28571428571431</v>
       </c>
       <c r="AA3">
-        <v>0.04758492700993277</v>
+        <v>3.214285714285718</v>
       </c>
       <c r="AB3">
-        <v>0.05475699131576835</v>
+        <v>0.05842561509745306</v>
       </c>
       <c r="AC3">
-        <v>-0.007172064305835585</v>
+        <v>3.155860099188264</v>
       </c>
       <c r="AD3">
-        <v>43574.2</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1392.576580256081</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>44966.77658025608</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>36807.37658025607</v>
+        <v>-41.7</v>
       </c>
       <c r="AH3">
-        <v>0.6455394263466082</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.6180365055769202</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.5985107002506315</v>
+        <v>-0.5589812332439679</v>
       </c>
       <c r="AK3">
-        <v>0.5697905963891496</v>
+        <v>-10.6923076923077</v>
       </c>
       <c r="AL3">
-        <v>1263.9</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1254.43</v>
+        <v>-0.049</v>
       </c>
       <c r="AN3">
-        <v>6.491307521563603</v>
-      </c>
-      <c r="AO3">
-        <v>2.911780995331909</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>5.48324468250571</v>
+        <v>-2.60625</v>
       </c>
       <c r="AQ3">
-        <v>2.933762744832314</v>
+        <v>-312.2448979591837</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mitsubishi HC Capital Inc. (TSE:8593)</t>
+          <t>GMO Payment Gateway, Inc. (TSE:3769)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,121 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.179</v>
+        <v>0.181</v>
       </c>
       <c r="E4">
-        <v>0.123</v>
+        <v>0.288</v>
+      </c>
+      <c r="F4">
+        <v>0.196</v>
       </c>
       <c r="G4">
-        <v>0.2258883073719341</v>
+        <v>0.3871844660194175</v>
       </c>
       <c r="H4">
-        <v>0.2258883073719341</v>
+        <v>0.3871844660194175</v>
       </c>
       <c r="I4">
-        <v>0.08944001257439513</v>
+        <v>0.341747572815534</v>
       </c>
       <c r="J4">
-        <v>0.06451592389803058</v>
+        <v>0.2390453074433657</v>
       </c>
       <c r="K4">
-        <v>927.1</v>
+        <v>130.6</v>
       </c>
       <c r="L4">
-        <v>0.06392779076422361</v>
+        <v>0.2535922330097087</v>
       </c>
       <c r="M4">
-        <v>390.3472</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04103647946847206</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.4210410958904109</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>390.3472</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04103647946847206</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.4210410958904109</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>2668.5</v>
+        <v>1214.9</v>
       </c>
       <c r="V4">
-        <v>0.2805344715207838</v>
+        <v>0.3159112775307487</v>
       </c>
       <c r="W4">
-        <v>0.08325550486727253</v>
+        <v>0.2113952735513111</v>
       </c>
       <c r="X4">
-        <v>0.113509085706502</v>
+        <v>0.05926998748880834</v>
       </c>
       <c r="Y4">
-        <v>-0.03025358083922945</v>
+        <v>0.1521252860625028</v>
       </c>
       <c r="Z4">
-        <v>0.2232604477720556</v>
+        <v>11.89651189651191</v>
       </c>
       <c r="AA4">
-        <v>0.01440385405790217</v>
+        <v>2.843805343805348</v>
       </c>
       <c r="AB4">
-        <v>0.05286239589968585</v>
+        <v>0.0578582633987663</v>
       </c>
       <c r="AC4">
-        <v>-0.03845854184178368</v>
+        <v>2.785947080406582</v>
       </c>
       <c r="AD4">
-        <v>59730.7</v>
+        <v>370.7</v>
       </c>
       <c r="AE4">
-        <v>52.57052821174747</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>59783.27052821175</v>
+        <v>370.7</v>
       </c>
       <c r="AG4">
-        <v>57114.77052821175</v>
+        <v>-844.2</v>
       </c>
       <c r="AH4">
-        <v>0.8627298447143472</v>
+        <v>0.08791860354805048</v>
       </c>
       <c r="AI4">
-        <v>0.8310102796000964</v>
+        <v>0.3341747047687731</v>
       </c>
       <c r="AJ4">
-        <v>0.8572319899195736</v>
+        <v>-0.2812593703148426</v>
       </c>
       <c r="AK4">
-        <v>0.8245004450241695</v>
+        <v>7.994318181818181</v>
       </c>
       <c r="AL4">
-        <v>66.2</v>
+        <v>2.01</v>
       </c>
       <c r="AM4">
-        <v>41.6</v>
+        <v>-5.84</v>
       </c>
       <c r="AN4">
-        <v>15.04172752455301</v>
+        <v>1.859077231695085</v>
       </c>
       <c r="AO4">
-        <v>19.40030211480362</v>
+        <v>87.56218905472637</v>
       </c>
       <c r="AP4">
-        <v>14.38296915845171</v>
+        <v>-4.23370110330993</v>
       </c>
       <c r="AQ4">
-        <v>30.87259615384615</v>
+        <v>-30.13698630136986</v>
       </c>
     </row>
     <row r="5">
@@ -987,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tokyo Century Corporation (TSE:8439)</t>
+          <t>eGuarantee, Inc. (TSE:8771)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -996,121 +990,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0375</v>
+        <v>0.106</v>
       </c>
       <c r="E5">
-        <v>0.0799</v>
+        <v>0.1</v>
       </c>
       <c r="G5">
-        <v>0.250588591053416</v>
+        <v>0.4894894894894896</v>
       </c>
       <c r="H5">
-        <v>0.250588591053416</v>
+        <v>0.4894894894894896</v>
       </c>
       <c r="I5">
-        <v>0.08098796898287146</v>
+        <v>0.5120120120120121</v>
       </c>
       <c r="J5">
-        <v>0.05716958485030352</v>
+        <v>0.3526538065442965</v>
       </c>
       <c r="K5">
-        <v>556</v>
+        <v>23.3</v>
       </c>
       <c r="L5">
-        <v>0.06004708728427328</v>
+        <v>0.3498498498498499</v>
       </c>
       <c r="M5">
-        <v>212.2689</v>
+        <v>11.6388</v>
       </c>
       <c r="N5">
-        <v>0.04266883090777519</v>
+        <v>0.02151349353049908</v>
       </c>
       <c r="O5">
-        <v>0.3817785971223022</v>
+        <v>0.499519313304721</v>
       </c>
       <c r="P5">
-        <v>190.7689</v>
+        <v>11.6388</v>
       </c>
       <c r="Q5">
-        <v>0.03834704912760312</v>
+        <v>0.02151349353049908</v>
       </c>
       <c r="R5">
-        <v>0.3431095323741007</v>
+        <v>0.499519313304721</v>
       </c>
       <c r="S5">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.1012866227695155</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1233.7</v>
+        <v>90.2</v>
       </c>
       <c r="V5">
-        <v>0.2479898689394548</v>
+        <v>0.166728280961183</v>
       </c>
       <c r="W5">
-        <v>0.09531646437632861</v>
+        <v>0.1693313953488372</v>
       </c>
       <c r="X5">
-        <v>0.1207563351409322</v>
+        <v>0.05842561509745306</v>
       </c>
       <c r="Y5">
-        <v>-0.02543987076460356</v>
+        <v>0.1109057802513842</v>
       </c>
       <c r="Z5">
-        <v>0.2654400972387854</v>
+        <v>2.457564575645757</v>
       </c>
       <c r="AA5">
-        <v>0.01517510016176556</v>
+        <v>0.8666695024298948</v>
       </c>
       <c r="AB5">
-        <v>0.05429274308726709</v>
+        <v>0.05842561509745306</v>
       </c>
       <c r="AC5">
-        <v>-0.03911764292550152</v>
+        <v>0.8082438873324418</v>
       </c>
       <c r="AD5">
-        <v>35380.2</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>35380.2</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>34146.5</v>
+        <v>-90.2</v>
       </c>
       <c r="AH5">
-        <v>0.8767240738446288</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.8119044996420114</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.8728365366181593</v>
+        <v>-0.2000887311446318</v>
       </c>
       <c r="AK5">
-        <v>0.8064241871757146</v>
+        <v>-1.134591194968554</v>
       </c>
       <c r="AL5">
-        <v>60.6</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>44.3</v>
+        <v>-0.537</v>
       </c>
       <c r="AN5">
-        <v>13.81014091104258</v>
-      </c>
-      <c r="AO5">
-        <v>12.37458745874587</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>13.32858425387408</v>
+        <v>-2.599423631123919</v>
       </c>
       <c r="AQ5">
-        <v>16.92776523702032</v>
+        <v>-63.50093109869646</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ricoh Leasing Company, Ltd. (TSE:8566)</t>
+          <t>Coincheck Group N.V. (NasdaqGM:CNCK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,122 +1120,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.0111</v>
-      </c>
-      <c r="E6">
-        <v>0.0306</v>
-      </c>
       <c r="G6">
-        <v>0.1253561253561254</v>
+        <v>0.008048289738430584</v>
       </c>
       <c r="H6">
-        <v>0.1253561253561254</v>
+        <v>0.008048289738430584</v>
       </c>
       <c r="I6">
-        <v>0.06943664537083973</v>
+        <v>0.01197884984324552</v>
       </c>
       <c r="J6">
-        <v>0.04790402711995215</v>
+        <v>0.008258210616315199</v>
       </c>
       <c r="K6">
-        <v>99</v>
+        <v>19.6</v>
       </c>
       <c r="L6">
-        <v>0.04623791509037411</v>
+        <v>0.009171306911234852</v>
       </c>
       <c r="M6">
-        <v>33.264</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03237687366167023</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.336</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>33.264</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.03237687366167023</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.336</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>25.4</v>
+        <v>74.2</v>
       </c>
       <c r="V6">
-        <v>0.02472260073973136</v>
+        <v>0.06434827855346457</v>
       </c>
       <c r="W6">
-        <v>0.06804591380850918</v>
+        <v>0.2552083333333334</v>
       </c>
       <c r="X6">
-        <v>0.1179039385599455</v>
+        <v>0.05842561509745306</v>
       </c>
       <c r="Y6">
-        <v>-0.04985802475143634</v>
+        <v>0.1967827182358803</v>
       </c>
       <c r="Z6">
-        <v>0.2878230332657079</v>
+        <v>95.40625</v>
       </c>
       <c r="AA6">
-        <v>0.01378788239130736</v>
+        <v>0.787884906612822</v>
       </c>
       <c r="AB6">
-        <v>0.05431706779159121</v>
+        <v>0.05842561509745306</v>
       </c>
       <c r="AC6">
-        <v>-0.04052918540028384</v>
+        <v>0.7294592915153689</v>
       </c>
       <c r="AD6">
-        <v>6920.7</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>51.64599298247533</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>6972.345992982475</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>6946.945992982475</v>
+        <v>-74.2</v>
       </c>
       <c r="AH6">
-        <v>0.8715709222641251</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.8143888308934576</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0.8711618481435186</v>
+        <v>-0.06877375104272872</v>
       </c>
       <c r="AK6">
-        <v>0.813836523220891</v>
+        <v>-4.696202531645571</v>
       </c>
       <c r="AL6">
-        <v>1.98</v>
+        <v>0.496</v>
       </c>
       <c r="AM6">
-        <v>-4.289999999999999</v>
+        <v>0.496</v>
       </c>
       <c r="AN6">
-        <v>22.72807881773399</v>
+        <v>0</v>
       </c>
       <c r="AO6">
-        <v>73.8888888888889</v>
+        <v>51.61290322580646</v>
       </c>
       <c r="AP6">
-        <v>22.81427255495066</v>
+        <v>-2.821292775665399</v>
       </c>
       <c r="AQ6">
-        <v>-34.10256410256411</v>
+        <v>51.61290322580646</v>
       </c>
     </row>
     <row r="7">
@@ -1255,127 +1237,5096 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>J-Lease Co.,Ltd. (TSE:7187)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.182</v>
+      </c>
+      <c r="E7">
+        <v>0.903</v>
+      </c>
+      <c r="G7">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="H7">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="I7">
+        <v>0.1969111969111969</v>
+      </c>
+      <c r="J7">
+        <v>0.134572476281019</v>
+      </c>
+      <c r="K7">
+        <v>13.6</v>
+      </c>
+      <c r="L7">
+        <v>0.1312741312741313</v>
+      </c>
+      <c r="M7">
+        <v>5.5962</v>
+      </c>
+      <c r="N7">
+        <v>0.03883553088133241</v>
+      </c>
+      <c r="O7">
+        <v>0.4114852941176471</v>
+      </c>
+      <c r="P7">
+        <v>5.5892</v>
+      </c>
+      <c r="Q7">
+        <v>0.03878695350451076</v>
+      </c>
+      <c r="R7">
+        <v>0.4109705882352941</v>
+      </c>
+      <c r="S7">
+        <v>0.006999999999999673</v>
+      </c>
+      <c r="T7">
+        <v>0.001250848790250469</v>
+      </c>
+      <c r="U7">
+        <v>11.9</v>
+      </c>
+      <c r="V7">
+        <v>0.08258154059680778</v>
+      </c>
+      <c r="W7">
+        <v>0.5190839694656488</v>
+      </c>
+      <c r="X7">
+        <v>0.05933744560626079</v>
+      </c>
+      <c r="Y7">
+        <v>0.459746523859388</v>
+      </c>
+      <c r="Z7">
+        <v>4.059561128526646</v>
+      </c>
+      <c r="AA7">
+        <v>0.5463051936799987</v>
+      </c>
+      <c r="AB7">
+        <v>0.05781721026132174</v>
+      </c>
+      <c r="AC7">
+        <v>0.488487983418677</v>
+      </c>
+      <c r="AD7">
+        <v>15</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>15</v>
+      </c>
+      <c r="AG7">
+        <v>3.1</v>
+      </c>
+      <c r="AH7">
+        <v>0.09428032683846638</v>
+      </c>
+      <c r="AI7">
+        <v>0.2946954813359529</v>
+      </c>
+      <c r="AJ7">
+        <v>0.02105978260869565</v>
+      </c>
+      <c r="AK7">
+        <v>0.07948717948717948</v>
+      </c>
+      <c r="AL7">
+        <v>0.133</v>
+      </c>
+      <c r="AM7">
+        <v>0.133</v>
+      </c>
+      <c r="AN7">
+        <v>0.6849315068493151</v>
+      </c>
+      <c r="AO7">
+        <v>153.3834586466165</v>
+      </c>
+      <c r="AP7">
+        <v>0.1415525114155251</v>
+      </c>
+      <c r="AQ7">
+        <v>153.3834586466165</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GMO Financial Gate, Inc. (TSE:4051)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.51</v>
+      </c>
+      <c r="E8">
+        <v>0.499</v>
+      </c>
+      <c r="G8">
+        <v>0.110260336906585</v>
+      </c>
+      <c r="H8">
+        <v>0.110260336906585</v>
+      </c>
+      <c r="I8">
+        <v>0.08192955589586523</v>
+      </c>
+      <c r="J8">
+        <v>0.05813097061182819</v>
+      </c>
+      <c r="K8">
+        <v>7.07</v>
+      </c>
+      <c r="L8">
+        <v>0.05413476263399694</v>
+      </c>
+      <c r="M8">
+        <v>3.57225</v>
+      </c>
+      <c r="N8">
+        <v>0.009569381194749531</v>
+      </c>
+      <c r="O8">
+        <v>0.5052687411598302</v>
+      </c>
+      <c r="P8">
+        <v>3.57225</v>
+      </c>
+      <c r="Q8">
+        <v>0.009569381194749531</v>
+      </c>
+      <c r="R8">
+        <v>0.5052687411598302</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>35.3</v>
+      </c>
+      <c r="V8">
+        <v>0.09456201446557727</v>
+      </c>
+      <c r="W8">
+        <v>0.2148936170212766</v>
+      </c>
+      <c r="X8">
+        <v>0.0587541313700611</v>
+      </c>
+      <c r="Y8">
+        <v>0.1561394856512155</v>
+      </c>
+      <c r="Z8">
+        <v>8.643282594308404</v>
+      </c>
+      <c r="AA8">
+        <v>0.502442406479468</v>
+      </c>
+      <c r="AB8">
+        <v>0.0581923487351157</v>
+      </c>
+      <c r="AC8">
+        <v>0.4442500577443523</v>
+      </c>
+      <c r="AD8">
+        <v>14</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>14</v>
+      </c>
+      <c r="AG8">
+        <v>-21.3</v>
+      </c>
+      <c r="AH8">
+        <v>0.03614768912987348</v>
+      </c>
+      <c r="AI8">
+        <v>0.2540834845735027</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.06051136363636363</v>
+      </c>
+      <c r="AK8">
+        <v>-1.075757575757575</v>
+      </c>
+      <c r="AL8">
+        <v>0.091</v>
+      </c>
+      <c r="AM8">
+        <v>-0.9590000000000001</v>
+      </c>
+      <c r="AN8">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="AO8">
+        <v>117.5824175824176</v>
+      </c>
+      <c r="AP8">
+        <v>-1.479166666666667</v>
+      </c>
+      <c r="AQ8">
+        <v>-11.15745568300313</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Japan Exchange Group, Inc. (TSE:8697)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0612</v>
+      </c>
+      <c r="E9">
+        <v>0.0572</v>
+      </c>
+      <c r="G9">
+        <v>0.6125766053823608</v>
+      </c>
+      <c r="H9">
+        <v>0.6125766053823608</v>
+      </c>
+      <c r="I9">
+        <v>0.5538680166977529</v>
+      </c>
+      <c r="J9">
+        <v>0.3852385825909125</v>
+      </c>
+      <c r="K9">
+        <v>430.7</v>
+      </c>
+      <c r="L9">
+        <v>0.3825384137134736</v>
+      </c>
+      <c r="M9">
+        <v>150.726</v>
+      </c>
+      <c r="N9">
+        <v>0.01286705764847492</v>
+      </c>
+      <c r="O9">
+        <v>0.3499558857673555</v>
+      </c>
+      <c r="P9">
+        <v>145.656</v>
+      </c>
+      <c r="Q9">
+        <v>0.0124342459087766</v>
+      </c>
+      <c r="R9">
+        <v>0.3381843510564199</v>
+      </c>
+      <c r="S9">
+        <v>5.069999999999993</v>
+      </c>
+      <c r="T9">
+        <v>0.0336371959714979</v>
+      </c>
+      <c r="U9">
+        <v>604.3</v>
+      </c>
+      <c r="V9">
+        <v>0.05158740321492901</v>
+      </c>
+      <c r="W9">
+        <v>0.1998329698881826</v>
+      </c>
+      <c r="X9">
+        <v>0.058699529477364</v>
+      </c>
+      <c r="Y9">
+        <v>0.1411334404108186</v>
+      </c>
+      <c r="Z9">
+        <v>0.8834052569635149</v>
+      </c>
+      <c r="AA9">
+        <v>0.3403217890459853</v>
+      </c>
+      <c r="AB9">
+        <v>0.05815631324120295</v>
+      </c>
+      <c r="AC9">
+        <v>0.2821654758047824</v>
+      </c>
+      <c r="AD9">
+        <v>366.3</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>366.3</v>
+      </c>
+      <c r="AG9">
+        <v>-237.9999999999999</v>
+      </c>
+      <c r="AH9">
+        <v>0.03032184364756134</v>
+      </c>
+      <c r="AI9">
+        <v>0.1337740121247535</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.02073875271215831</v>
+      </c>
+      <c r="AK9">
+        <v>-0.1115328740803224</v>
+      </c>
+      <c r="AL9">
+        <v>0.838</v>
+      </c>
+      <c r="AM9">
+        <v>0.224</v>
+      </c>
+      <c r="AN9">
+        <v>0.4873602980308675</v>
+      </c>
+      <c r="AO9">
+        <v>744.1527446300717</v>
+      </c>
+      <c r="AP9">
+        <v>-0.3166577967003725</v>
+      </c>
+      <c r="AQ9">
+        <v>2783.928571428572</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Anshin Guarantor Service Co., Ltd. (TSE:7183)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.0876</v>
+      </c>
+      <c r="E10">
+        <v>0.123</v>
+      </c>
+      <c r="G10">
+        <v>0.1028125</v>
+      </c>
+      <c r="H10">
+        <v>0.1028125</v>
+      </c>
+      <c r="I10">
+        <v>0.0909375</v>
+      </c>
+      <c r="J10">
+        <v>0.06170758928571429</v>
+      </c>
+      <c r="K10">
+        <v>2.47</v>
+      </c>
+      <c r="L10">
+        <v>0.07718750000000001</v>
+      </c>
+      <c r="M10">
+        <v>1.08</v>
+      </c>
+      <c r="N10">
+        <v>0.06390532544378699</v>
+      </c>
+      <c r="O10">
+        <v>0.4372469635627531</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>1.08</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>8.01</v>
+      </c>
+      <c r="V10">
+        <v>0.4739644970414201</v>
+      </c>
+      <c r="W10">
+        <v>0.1515337423312884</v>
+      </c>
+      <c r="X10">
+        <v>0.06014126286714352</v>
+      </c>
+      <c r="Y10">
+        <v>0.09139247946414483</v>
+      </c>
+      <c r="Z10">
+        <v>3.665521191294387</v>
+      </c>
+      <c r="AA10">
+        <v>0.2261904761904762</v>
+      </c>
+      <c r="AB10">
+        <v>0.05697100893479988</v>
+      </c>
+      <c r="AC10">
+        <v>0.1692194672556763</v>
+      </c>
+      <c r="AD10">
+        <v>3.31</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>3.31</v>
+      </c>
+      <c r="AG10">
+        <v>-4.699999999999999</v>
+      </c>
+      <c r="AH10">
+        <v>0.1637803067788224</v>
+      </c>
+      <c r="AI10">
+        <v>0.1769107429182255</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.3852459016393442</v>
+      </c>
+      <c r="AK10">
+        <v>-0.439252336448598</v>
+      </c>
+      <c r="AL10">
+        <v>0.132</v>
+      </c>
+      <c r="AM10">
+        <v>0.132</v>
+      </c>
+      <c r="AN10">
+        <v>1.006079027355623</v>
+      </c>
+      <c r="AO10">
+        <v>22.04545454545455</v>
+      </c>
+      <c r="AP10">
+        <v>-1.428571428571428</v>
+      </c>
+      <c r="AQ10">
+        <v>22.04545454545455</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ZENKOKU HOSHO Co.,Ltd. (TSE:7164)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.032</v>
+      </c>
+      <c r="E11">
+        <v>0.0294</v>
+      </c>
+      <c r="G11">
+        <v>0.7119476268412438</v>
+      </c>
+      <c r="H11">
+        <v>0.7119476268412438</v>
+      </c>
+      <c r="I11">
+        <v>0.7340425531914894</v>
+      </c>
+      <c r="J11">
+        <v>0.5103051570203883</v>
+      </c>
+      <c r="K11">
+        <v>199.8</v>
+      </c>
+      <c r="L11">
+        <v>0.5450081833060556</v>
+      </c>
+      <c r="M11">
+        <v>129.225</v>
+      </c>
+      <c r="N11">
+        <v>0.05428937528882914</v>
+      </c>
+      <c r="O11">
+        <v>0.6467717717717717</v>
+      </c>
+      <c r="P11">
+        <v>80.325</v>
+      </c>
+      <c r="Q11">
+        <v>0.03374574633449565</v>
+      </c>
+      <c r="R11">
+        <v>0.402027027027027</v>
+      </c>
+      <c r="S11">
+        <v>48.89999999999999</v>
+      </c>
+      <c r="T11">
+        <v>0.3784097504352872</v>
+      </c>
+      <c r="U11">
+        <v>741.8</v>
+      </c>
+      <c r="V11">
+        <v>0.3116413897407889</v>
+      </c>
+      <c r="W11">
+        <v>0.1435963777490298</v>
+      </c>
+      <c r="X11">
+        <v>0.05919622009573729</v>
+      </c>
+      <c r="Y11">
+        <v>0.08440015765329245</v>
+      </c>
+      <c r="Z11">
+        <v>0.427023878858474</v>
+      </c>
+      <c r="AA11">
+        <v>0.2179124875523288</v>
+      </c>
+      <c r="AB11">
+        <v>0.05770747204473585</v>
+      </c>
+      <c r="AC11">
+        <v>0.160205015507593</v>
+      </c>
+      <c r="AD11">
+        <v>209.4</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>209.4</v>
+      </c>
+      <c r="AG11">
+        <v>-532.4</v>
+      </c>
+      <c r="AH11">
+        <v>0.08085878673205391</v>
+      </c>
+      <c r="AI11">
+        <v>0.1207891093677896</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.2881108285080361</v>
+      </c>
+      <c r="AK11">
+        <v>-0.5368017745513207</v>
+      </c>
+      <c r="AL11">
+        <v>5.66</v>
+      </c>
+      <c r="AM11">
+        <v>-20.64</v>
+      </c>
+      <c r="AN11">
+        <v>0.7661909989023051</v>
+      </c>
+      <c r="AO11">
+        <v>47.54416961130742</v>
+      </c>
+      <c r="AP11">
+        <v>-1.948042444200512</v>
+      </c>
+      <c r="AQ11">
+        <v>-13.03779069767442</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Premium Group Co., Ltd. (TSE:7199)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.232</v>
+      </c>
+      <c r="E12">
+        <v>0.163</v>
+      </c>
+      <c r="G12">
+        <v>0.2145816072908036</v>
+      </c>
+      <c r="H12">
+        <v>0.2145816072908036</v>
+      </c>
+      <c r="I12">
+        <v>0.2162386081193041</v>
+      </c>
+      <c r="J12">
+        <v>0.1533929705779384</v>
+      </c>
+      <c r="K12">
+        <v>37.1</v>
+      </c>
+      <c r="L12">
+        <v>0.1536868268434134</v>
+      </c>
+      <c r="M12">
+        <v>23.672</v>
+      </c>
+      <c r="N12">
+        <v>0.03793589743589744</v>
+      </c>
+      <c r="O12">
+        <v>0.6380592991913746</v>
+      </c>
+      <c r="P12">
+        <v>9.272</v>
+      </c>
+      <c r="Q12">
+        <v>0.01485897435897436</v>
+      </c>
+      <c r="R12">
+        <v>0.2499191374663073</v>
+      </c>
+      <c r="S12">
+        <v>14.4</v>
+      </c>
+      <c r="T12">
+        <v>0.6083136194660358</v>
+      </c>
+      <c r="U12">
+        <v>127.6</v>
+      </c>
+      <c r="V12">
+        <v>0.2044871794871795</v>
+      </c>
+      <c r="W12">
+        <v>0.3651574803149606</v>
+      </c>
+      <c r="X12">
+        <v>0.06251064500224851</v>
+      </c>
+      <c r="Y12">
+        <v>0.3026468353127121</v>
+      </c>
+      <c r="Z12">
+        <v>1.291599785981809</v>
+      </c>
+      <c r="AA12">
+        <v>0.1981223279695792</v>
+      </c>
+      <c r="AB12">
+        <v>0.05637330267896916</v>
+      </c>
+      <c r="AC12">
+        <v>0.14174902529061</v>
+      </c>
+      <c r="AD12">
+        <v>291</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>291</v>
+      </c>
+      <c r="AG12">
+        <v>163.4</v>
+      </c>
+      <c r="AH12">
+        <v>0.3180327868852459</v>
+      </c>
+      <c r="AI12">
+        <v>0.7013738250180767</v>
+      </c>
+      <c r="AJ12">
+        <v>0.2075184150368301</v>
+      </c>
+      <c r="AK12">
+        <v>0.5687434737208493</v>
+      </c>
+      <c r="AL12">
+        <v>0.161</v>
+      </c>
+      <c r="AM12">
+        <v>0.091</v>
+      </c>
+      <c r="AN12">
+        <v>4.511627906976744</v>
+      </c>
+      <c r="AO12">
+        <v>324.2236024844721</v>
+      </c>
+      <c r="AP12">
+        <v>2.533333333333333</v>
+      </c>
+      <c r="AQ12">
+        <v>573.6263736263737</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Casa Inc. (TSE:7196)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.0533</v>
+      </c>
+      <c r="E13">
+        <v>-0.0361</v>
+      </c>
+      <c r="G13">
+        <v>0.1004731457800511</v>
+      </c>
+      <c r="H13">
+        <v>0.100383631713555</v>
+      </c>
+      <c r="I13">
+        <v>0.02020460358056266</v>
+      </c>
+      <c r="J13">
+        <v>0.01010230179028133</v>
+      </c>
+      <c r="K13">
+        <v>-0.571</v>
+      </c>
+      <c r="L13">
+        <v>-0.007301790281329923</v>
+      </c>
+      <c r="M13">
+        <v>1.9897</v>
+      </c>
+      <c r="N13">
+        <v>0.03644139194139194</v>
+      </c>
+      <c r="O13">
+        <v>-3.484588441330998</v>
+      </c>
+      <c r="P13">
+        <v>1.9897</v>
+      </c>
+      <c r="Q13">
+        <v>0.03644139194139194</v>
+      </c>
+      <c r="R13">
+        <v>-3.484588441330998</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>21.3</v>
+      </c>
+      <c r="V13">
+        <v>0.3901098901098901</v>
+      </c>
+      <c r="W13">
+        <v>-0.01266075388026607</v>
+      </c>
+      <c r="X13">
+        <v>0.05861011325711982</v>
+      </c>
+      <c r="Y13">
+        <v>-0.0712708671373859</v>
+      </c>
+      <c r="Z13">
+        <v>15.45454545454546</v>
+      </c>
+      <c r="AA13">
+        <v>0.1561264822134388</v>
+      </c>
+      <c r="AB13">
+        <v>0.05824241035504018</v>
+      </c>
+      <c r="AC13">
+        <v>0.09788407185839859</v>
+      </c>
+      <c r="AD13">
+        <v>1.15</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>1.15</v>
+      </c>
+      <c r="AG13">
+        <v>-20.15</v>
+      </c>
+      <c r="AH13">
+        <v>0.02062780269058296</v>
+      </c>
+      <c r="AI13">
+        <v>0.02622576966932725</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.5849056603773585</v>
+      </c>
+      <c r="AK13">
+        <v>-0.8935698447893571</v>
+      </c>
+      <c r="AL13">
+        <v>0.013</v>
+      </c>
+      <c r="AM13">
+        <v>0.005999999999999999</v>
+      </c>
+      <c r="AN13">
+        <v>0.2853598014888337</v>
+      </c>
+      <c r="AO13">
+        <v>121.5384615384615</v>
+      </c>
+      <c r="AP13">
+        <v>-5</v>
+      </c>
+      <c r="AQ13">
+        <v>263.3333333333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Financial Partners Group Co.,Ltd. (TSE:7148)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.323</v>
+      </c>
+      <c r="E14">
+        <v>0.153</v>
+      </c>
+      <c r="G14">
+        <v>0.270105011298684</v>
+      </c>
+      <c r="H14">
+        <v>0.270105011298684</v>
+      </c>
+      <c r="I14">
+        <v>0.267050246758408</v>
+      </c>
+      <c r="J14">
+        <v>0.185700633877258</v>
+      </c>
+      <c r="K14">
+        <v>142.8</v>
+      </c>
+      <c r="L14">
+        <v>0.1898178917984847</v>
+      </c>
+      <c r="M14">
+        <v>13.3</v>
+      </c>
+      <c r="N14">
+        <v>0.008557457212713936</v>
+      </c>
+      <c r="O14">
+        <v>0.09313725490196079</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>13.3</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>121.7</v>
+      </c>
+      <c r="V14">
+        <v>0.07830395058551023</v>
+      </c>
+      <c r="W14">
+        <v>0.4825954714430551</v>
+      </c>
+      <c r="X14">
+        <v>0.06435024685648433</v>
+      </c>
+      <c r="Y14">
+        <v>0.4182452245865708</v>
+      </c>
+      <c r="Z14">
+        <v>0.7923697443057959</v>
+      </c>
+      <c r="AA14">
+        <v>0.1471435637827471</v>
+      </c>
+      <c r="AB14">
+        <v>0.05582197962722266</v>
+      </c>
+      <c r="AC14">
+        <v>0.09132158415552447</v>
+      </c>
+      <c r="AD14">
+        <v>1044.4</v>
+      </c>
+      <c r="AE14">
+        <v>6.790496818248231</v>
+      </c>
+      <c r="AF14">
+        <v>1051.190496818248</v>
+      </c>
+      <c r="AG14">
+        <v>929.4904968182482</v>
+      </c>
+      <c r="AH14">
+        <v>0.403467540893383</v>
+      </c>
+      <c r="AI14">
+        <v>0.7385116727756782</v>
+      </c>
+      <c r="AJ14">
+        <v>0.3742376507898144</v>
+      </c>
+      <c r="AK14">
+        <v>0.7140641335941401</v>
+      </c>
+      <c r="AL14">
+        <v>5.03</v>
+      </c>
+      <c r="AM14">
+        <v>-2.999999999999999</v>
+      </c>
+      <c r="AN14">
+        <v>5.078284547311097</v>
+      </c>
+      <c r="AO14">
+        <v>39.72166998011929</v>
+      </c>
+      <c r="AP14">
+        <v>4.519549240582749</v>
+      </c>
+      <c r="AQ14">
+        <v>-66.60000000000002</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Money Partners Group Co.,Ltd. (TSE:8732)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.00722</v>
+      </c>
+      <c r="E15">
+        <v>0.0698</v>
+      </c>
+      <c r="G15">
+        <v>0.2389294403892944</v>
+      </c>
+      <c r="H15">
+        <v>0.2389294403892944</v>
+      </c>
+      <c r="I15">
+        <v>0.1625304136253041</v>
+      </c>
+      <c r="J15">
+        <v>0.1110085214041128</v>
+      </c>
+      <c r="K15">
+        <v>4.46</v>
+      </c>
+      <c r="L15">
+        <v>0.1085158150851581</v>
+      </c>
+      <c r="M15">
+        <v>2.4563</v>
+      </c>
+      <c r="N15">
+        <v>0.02558645833333333</v>
+      </c>
+      <c r="O15">
+        <v>0.5507399103139012</v>
+      </c>
+      <c r="P15">
+        <v>2.4563</v>
+      </c>
+      <c r="Q15">
+        <v>0.02558645833333333</v>
+      </c>
+      <c r="R15">
+        <v>0.5507399103139012</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="V15">
+        <v>0.7041666666666666</v>
+      </c>
+      <c r="W15">
+        <v>0.04868995633187773</v>
+      </c>
+      <c r="X15">
+        <v>0.05852781103459021</v>
+      </c>
+      <c r="Y15">
+        <v>-0.009837854702712479</v>
+      </c>
+      <c r="Z15">
+        <v>1.340508806262231</v>
+      </c>
+      <c r="AA15">
+        <v>0.1488079005123626</v>
+      </c>
+      <c r="AB15">
+        <v>0.05837119906604181</v>
+      </c>
+      <c r="AC15">
+        <v>0.09043670144632075</v>
+      </c>
+      <c r="AD15">
+        <v>1.12</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>1.12</v>
+      </c>
+      <c r="AG15">
+        <v>-66.47999999999999</v>
+      </c>
+      <c r="AH15">
+        <v>0.01153212520593081</v>
+      </c>
+      <c r="AI15">
+        <v>0.01135672277428514</v>
+      </c>
+      <c r="AJ15">
+        <v>-2.252032520325202</v>
+      </c>
+      <c r="AK15">
+        <v>-2.143133462282397</v>
+      </c>
+      <c r="AL15">
+        <v>0.035</v>
+      </c>
+      <c r="AM15">
+        <v>0.021</v>
+      </c>
+      <c r="AN15">
+        <v>0.1171548117154812</v>
+      </c>
+      <c r="AO15">
+        <v>190.8571428571428</v>
+      </c>
+      <c r="AP15">
+        <v>-6.953974895397488</v>
+      </c>
+      <c r="AQ15">
+        <v>318.095238095238</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SBI Global Asset Management Co., Ltd. (TSE:4765)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.123</v>
+      </c>
+      <c r="E16">
+        <v>0.053</v>
+      </c>
+      <c r="G16">
+        <v>0.2276315789473684</v>
+      </c>
+      <c r="H16">
+        <v>0.2276315789473684</v>
+      </c>
+      <c r="I16">
+        <v>0.2026315789473684</v>
+      </c>
+      <c r="J16">
+        <v>0.1300690973243164</v>
+      </c>
+      <c r="K16">
+        <v>11.4</v>
+      </c>
+      <c r="L16">
+        <v>0.15</v>
+      </c>
+      <c r="M16">
+        <v>18.9267</v>
+      </c>
+      <c r="N16">
+        <v>0.04937829376467519</v>
+      </c>
+      <c r="O16">
+        <v>1.660236842105263</v>
+      </c>
+      <c r="P16">
+        <v>18.9267</v>
+      </c>
+      <c r="Q16">
+        <v>0.04937829376467519</v>
+      </c>
+      <c r="R16">
+        <v>1.660236842105263</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>22.4</v>
+      </c>
+      <c r="V16">
+        <v>0.05843986433602921</v>
+      </c>
+      <c r="W16">
+        <v>0.1067415730337079</v>
+      </c>
+      <c r="X16">
+        <v>0.05845943791142861</v>
+      </c>
+      <c r="Y16">
+        <v>0.04828213512227927</v>
+      </c>
+      <c r="Z16">
+        <v>1.064873196020737</v>
+      </c>
+      <c r="AA16">
+        <v>0.1385070953712771</v>
+      </c>
+      <c r="AB16">
+        <v>0.05839145390924955</v>
+      </c>
+      <c r="AC16">
+        <v>0.08011564146202754</v>
+      </c>
+      <c r="AD16">
+        <v>1.48</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1.48</v>
+      </c>
+      <c r="AG16">
+        <v>-20.92</v>
+      </c>
+      <c r="AH16">
+        <v>0.003846353760590467</v>
+      </c>
+      <c r="AI16">
+        <v>0.01325214899713467</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.05772945526795076</v>
+      </c>
+      <c r="AK16">
+        <v>-0.2343189964157706</v>
+      </c>
+      <c r="AL16">
+        <v>0.357</v>
+      </c>
+      <c r="AM16">
+        <v>-1.793</v>
+      </c>
+      <c r="AN16">
+        <v>0.07668393782383419</v>
+      </c>
+      <c r="AO16">
+        <v>43.13725490196079</v>
+      </c>
+      <c r="AP16">
+        <v>-1.083937823834197</v>
+      </c>
+      <c r="AQ16">
+        <v>-8.588957055214724</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Net Protections Holdings, Inc. (TSE:7383)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0.04446721311475409</v>
+      </c>
+      <c r="H17">
+        <v>0.04446721311475409</v>
+      </c>
+      <c r="I17">
+        <v>0.03954918032786885</v>
+      </c>
+      <c r="J17">
+        <v>0.01977459016393443</v>
+      </c>
+      <c r="K17">
+        <v>0.949</v>
+      </c>
+      <c r="L17">
+        <v>0.006482240437158469</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>-0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="V17">
+        <v>0.2995419847328244</v>
+      </c>
+      <c r="W17">
+        <v>0.007888611803823773</v>
+      </c>
+      <c r="X17">
+        <v>0.06060282319768357</v>
+      </c>
+      <c r="Y17">
+        <v>-0.0527142113938598</v>
+      </c>
+      <c r="Z17">
+        <v>4.490797546012269</v>
+      </c>
+      <c r="AA17">
+        <v>0.08880368098159507</v>
+      </c>
+      <c r="AB17">
+        <v>0.05748627078385082</v>
+      </c>
+      <c r="AC17">
+        <v>0.03131741019774425</v>
+      </c>
+      <c r="AD17">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="AG17">
+        <v>-16.69999999999999</v>
+      </c>
+      <c r="AH17">
+        <v>0.1990706774272439</v>
+      </c>
+      <c r="AI17">
+        <v>0.3904076738609113</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.05373230373230369</v>
+      </c>
+      <c r="AK17">
+        <v>-0.1512681159420289</v>
+      </c>
+      <c r="AL17">
+        <v>0.524</v>
+      </c>
+      <c r="AM17">
+        <v>0.503</v>
+      </c>
+      <c r="AN17">
+        <v>4.625</v>
+      </c>
+      <c r="AO17">
+        <v>11.04961832061069</v>
+      </c>
+      <c r="AP17">
+        <v>-0.9488636363636357</v>
+      </c>
+      <c r="AQ17">
+        <v>11.51093439363817</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mortgage Service Japan Limited (TSE:7192)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.018</v>
+      </c>
+      <c r="E18">
+        <v>-0.0286</v>
+      </c>
+      <c r="G18">
+        <v>0.1984126984126984</v>
+      </c>
+      <c r="H18">
+        <v>0.1984126984126984</v>
+      </c>
+      <c r="I18">
+        <v>0.1767857142857143</v>
+      </c>
+      <c r="J18">
+        <v>0.1125956632653061</v>
+      </c>
+      <c r="K18">
+        <v>5.45</v>
+      </c>
+      <c r="L18">
+        <v>0.1081349206349206</v>
+      </c>
+      <c r="M18">
+        <v>2.058</v>
+      </c>
+      <c r="N18">
+        <v>0.05170854271356785</v>
+      </c>
+      <c r="O18">
+        <v>0.3776146788990826</v>
+      </c>
+      <c r="P18">
+        <v>2.058</v>
+      </c>
+      <c r="Q18">
+        <v>0.05170854271356785</v>
+      </c>
+      <c r="R18">
+        <v>0.3776146788990826</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>33.8</v>
+      </c>
+      <c r="V18">
+        <v>0.8492462311557789</v>
+      </c>
+      <c r="W18">
+        <v>0.105009633911368</v>
+      </c>
+      <c r="X18">
+        <v>0.0691220742751965</v>
+      </c>
+      <c r="Y18">
+        <v>0.03588755963617153</v>
+      </c>
+      <c r="Z18">
+        <v>0.5656565656565656</v>
+      </c>
+      <c r="AA18">
+        <v>0.0636904761904762</v>
+      </c>
+      <c r="AB18">
+        <v>0.05354282846229109</v>
+      </c>
+      <c r="AC18">
+        <v>0.01014764772818511</v>
+      </c>
+      <c r="AD18">
+        <v>48.6</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>48.6</v>
+      </c>
+      <c r="AG18">
+        <v>14.8</v>
+      </c>
+      <c r="AH18">
+        <v>0.5497737556561085</v>
+      </c>
+      <c r="AI18">
+        <v>0.4580584354382658</v>
+      </c>
+      <c r="AJ18">
+        <v>0.2710622710622712</v>
+      </c>
+      <c r="AK18">
+        <v>0.2047026279391425</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1.99</v>
+      </c>
+      <c r="AN18">
+        <v>4.964249233912156</v>
+      </c>
+      <c r="AP18">
+        <v>1.511746680286007</v>
+      </c>
+      <c r="AQ18">
+        <v>-4.477386934673367</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Acom Co., Ltd. (TSE:8572)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.0191</v>
+      </c>
+      <c r="E19">
+        <v>0.0528</v>
+      </c>
+      <c r="G19">
+        <v>0.294161606725829</v>
+      </c>
+      <c r="H19">
+        <v>0.294161606725829</v>
+      </c>
+      <c r="I19">
+        <v>0.3125543734904371</v>
+      </c>
+      <c r="J19">
+        <v>0.2070024143164334</v>
+      </c>
+      <c r="K19">
+        <v>388.5</v>
+      </c>
+      <c r="L19">
+        <v>0.1814572629612331</v>
+      </c>
+      <c r="M19">
+        <v>120.3</v>
+      </c>
+      <c r="N19">
+        <v>0.03145344732920229</v>
+      </c>
+      <c r="O19">
+        <v>0.3096525096525096</v>
+      </c>
+      <c r="P19">
+        <v>120.3</v>
+      </c>
+      <c r="Q19">
+        <v>0.03145344732920229</v>
+      </c>
+      <c r="R19">
+        <v>0.3096525096525096</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>420.4</v>
+      </c>
+      <c r="V19">
+        <v>0.1099171176824326</v>
+      </c>
+      <c r="W19">
+        <v>0.09553435302218069</v>
+      </c>
+      <c r="X19">
+        <v>0.06932841316678948</v>
+      </c>
+      <c r="Y19">
+        <v>0.02620593985539121</v>
+      </c>
+      <c r="Z19">
+        <v>0.2735233452247763</v>
+      </c>
+      <c r="AA19">
+        <v>0.05661999283343598</v>
+      </c>
+      <c r="AB19">
+        <v>0.05350086628484917</v>
+      </c>
+      <c r="AC19">
+        <v>0.003119126548586815</v>
+      </c>
+      <c r="AD19">
+        <v>4752.5</v>
+      </c>
+      <c r="AE19">
+        <v>7.955431784870584</v>
+      </c>
+      <c r="AF19">
+        <v>4760.455431784871</v>
+      </c>
+      <c r="AG19">
+        <v>4340.055431784871</v>
+      </c>
+      <c r="AH19">
+        <v>0.5544984560396202</v>
+      </c>
+      <c r="AI19">
+        <v>0.4917594492666492</v>
+      </c>
+      <c r="AJ19">
+        <v>0.5315597592659436</v>
+      </c>
+      <c r="AK19">
+        <v>0.4686856859288074</v>
+      </c>
+      <c r="AL19">
+        <v>29.5</v>
+      </c>
+      <c r="AM19">
+        <v>29.458</v>
+      </c>
+      <c r="AN19">
+        <v>6.792487887146797</v>
+      </c>
+      <c r="AO19">
+        <v>22.62033898305085</v>
+      </c>
+      <c r="AP19">
+        <v>6.20300346132444</v>
+      </c>
+      <c r="AQ19">
+        <v>22.65259012831828</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Showa Holdings Co., Ltd. (TSE:5103)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>-0.119</v>
+      </c>
+      <c r="G20">
+        <v>0.01037828947368421</v>
+      </c>
+      <c r="H20">
+        <v>0.007401315789473685</v>
+      </c>
+      <c r="I20">
+        <v>0.008783289733110851</v>
+      </c>
+      <c r="J20">
+        <v>0.008783289733110851</v>
+      </c>
+      <c r="K20">
+        <v>-4.2</v>
+      </c>
+      <c r="L20">
+        <v>-0.06907894736842106</v>
+      </c>
+      <c r="M20">
+        <v>4.46</v>
+      </c>
+      <c r="N20">
+        <v>0.2197044334975369</v>
+      </c>
+      <c r="O20">
+        <v>-1.061904761904762</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>4.46</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>6.37</v>
+      </c>
+      <c r="V20">
+        <v>0.3137931034482759</v>
+      </c>
+      <c r="W20">
+        <v>-0.3206106870229008</v>
+      </c>
+      <c r="X20">
+        <v>0.06237172167119142</v>
+      </c>
+      <c r="Y20">
+        <v>-0.3829824086940922</v>
+      </c>
+      <c r="Z20">
+        <v>5.809908996395806</v>
+      </c>
+      <c r="AA20">
+        <v>0.05103011403835165</v>
+      </c>
+      <c r="AB20">
+        <v>0.05566724864262872</v>
+      </c>
+      <c r="AC20">
+        <v>-0.004637134604277067</v>
+      </c>
+      <c r="AD20">
+        <v>5.94</v>
+      </c>
+      <c r="AE20">
+        <v>3.204879921134301</v>
+      </c>
+      <c r="AF20">
+        <v>9.144879921134301</v>
+      </c>
+      <c r="AG20">
+        <v>2.774879921134301</v>
+      </c>
+      <c r="AH20">
+        <v>0.3105762341577929</v>
+      </c>
+      <c r="AI20">
+        <v>0.3003749709252782</v>
+      </c>
+      <c r="AJ20">
+        <v>0.1202554436087351</v>
+      </c>
+      <c r="AK20">
+        <v>0.1152603846924426</v>
+      </c>
+      <c r="AL20">
+        <v>0.077</v>
+      </c>
+      <c r="AM20">
+        <v>-0.08400000000000001</v>
+      </c>
+      <c r="AN20">
+        <v>3.427582227351414</v>
+      </c>
+      <c r="AO20">
+        <v>-4.350649350649351</v>
+      </c>
+      <c r="AP20">
+        <v>1.601200185305425</v>
+      </c>
+      <c r="AQ20">
+        <v>3.988095238095238</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ORIX Corporation (TSE:8591)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.0445</v>
+      </c>
+      <c r="E21">
+        <v>0.0411</v>
+      </c>
+      <c r="F21">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="G21">
+        <v>0.3036868091932128</v>
+      </c>
+      <c r="H21">
+        <v>0.3036868091932128</v>
+      </c>
+      <c r="I21">
+        <v>0.1872821215543639</v>
+      </c>
+      <c r="J21">
+        <v>0.1346638921932612</v>
+      </c>
+      <c r="K21">
+        <v>2798.9</v>
+      </c>
+      <c r="L21">
+        <v>0.1402992556204416</v>
+      </c>
+      <c r="M21">
+        <v>1172.9</v>
+      </c>
+      <c r="N21">
+        <v>0.04750333118679351</v>
+      </c>
+      <c r="O21">
+        <v>0.4190574868698417</v>
+      </c>
+      <c r="P21">
+        <v>796.4</v>
+      </c>
+      <c r="Q21">
+        <v>0.03225479832650895</v>
+      </c>
+      <c r="R21">
+        <v>0.2845403551395191</v>
+      </c>
+      <c r="S21">
+        <v>376.5000000000001</v>
+      </c>
+      <c r="T21">
+        <v>0.320999232671157</v>
+      </c>
+      <c r="U21">
+        <v>8159.4</v>
+      </c>
+      <c r="V21">
+        <v>0.3304618300669477</v>
+      </c>
+      <c r="W21">
+        <v>0.1111508234350366</v>
+      </c>
+      <c r="X21">
+        <v>0.07437858981164039</v>
+      </c>
+      <c r="Y21">
+        <v>0.03677223362339621</v>
+      </c>
+      <c r="Z21">
+        <v>0.3533606985133169</v>
+      </c>
+      <c r="AA21">
+        <v>0.04758492700993277</v>
+      </c>
+      <c r="AB21">
+        <v>0.05475251687375746</v>
+      </c>
+      <c r="AC21">
+        <v>-0.007167589863824694</v>
+      </c>
+      <c r="AD21">
+        <v>43574.2</v>
+      </c>
+      <c r="AE21">
+        <v>1392.576580256081</v>
+      </c>
+      <c r="AF21">
+        <v>44966.77658025608</v>
+      </c>
+      <c r="AG21">
+        <v>36807.37658025607</v>
+      </c>
+      <c r="AH21">
+        <v>0.6455394263466082</v>
+      </c>
+      <c r="AI21">
+        <v>0.6180365055769202</v>
+      </c>
+      <c r="AJ21">
+        <v>0.5985107002506315</v>
+      </c>
+      <c r="AK21">
+        <v>0.5697905963891496</v>
+      </c>
+      <c r="AL21">
+        <v>1263.9</v>
+      </c>
+      <c r="AM21">
+        <v>1254.43</v>
+      </c>
+      <c r="AN21">
+        <v>6.491307521563603</v>
+      </c>
+      <c r="AO21">
+        <v>2.911780995331909</v>
+      </c>
+      <c r="AP21">
+        <v>5.48324468250571</v>
+      </c>
+      <c r="AQ21">
+        <v>2.933762744832314</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SBI ARUHI Corporation (TSE:7198)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>-0.026</v>
+      </c>
+      <c r="E22">
+        <v>-0.175</v>
+      </c>
+      <c r="G22">
+        <v>0.1673101673101673</v>
+      </c>
+      <c r="H22">
+        <v>0.1673101673101673</v>
+      </c>
+      <c r="I22">
+        <v>0.1332046332046332</v>
+      </c>
+      <c r="J22">
+        <v>0.08694391083553644</v>
+      </c>
+      <c r="K22">
+        <v>13.3</v>
+      </c>
+      <c r="L22">
+        <v>0.08558558558558559</v>
+      </c>
+      <c r="M22">
+        <v>12.3597</v>
+      </c>
+      <c r="N22">
+        <v>0.05300042881646656</v>
+      </c>
+      <c r="O22">
+        <v>0.9293007518796992</v>
+      </c>
+      <c r="P22">
+        <v>12.3597</v>
+      </c>
+      <c r="Q22">
+        <v>0.05300042881646656</v>
+      </c>
+      <c r="R22">
+        <v>0.9293007518796992</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>108.5</v>
+      </c>
+      <c r="V22">
+        <v>0.4652658662092625</v>
+      </c>
+      <c r="W22">
+        <v>0.06120570639668661</v>
+      </c>
+      <c r="X22">
+        <v>0.08284521031903913</v>
+      </c>
+      <c r="Y22">
+        <v>-0.02163950392235253</v>
+      </c>
+      <c r="Z22">
+        <v>0.469486404833837</v>
+      </c>
+      <c r="AA22">
+        <v>0.04081898412036969</v>
+      </c>
+      <c r="AB22">
+        <v>0.05188895837082462</v>
+      </c>
+      <c r="AC22">
+        <v>-0.01106997425045493</v>
+      </c>
+      <c r="AD22">
+        <v>650.1</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>650.1</v>
+      </c>
+      <c r="AG22">
+        <v>541.6</v>
+      </c>
+      <c r="AH22">
+        <v>0.7359900373599004</v>
+      </c>
+      <c r="AI22">
+        <v>0.6897612732095491</v>
+      </c>
+      <c r="AJ22">
+        <v>0.6990191017036655</v>
+      </c>
+      <c r="AK22">
+        <v>0.649400479616307</v>
+      </c>
+      <c r="AL22">
+        <v>0.796</v>
+      </c>
+      <c r="AM22">
+        <v>0.736</v>
+      </c>
+      <c r="AN22">
+        <v>20.4433962264151</v>
+      </c>
+      <c r="AO22">
+        <v>26.00502512562814</v>
+      </c>
+      <c r="AP22">
+        <v>17.0314465408805</v>
+      </c>
+      <c r="AQ22">
+        <v>28.125</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Marui Group Co., Ltd. (TSE:8252)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>-0.00527</v>
+      </c>
+      <c r="E23">
+        <v>-0.0115</v>
+      </c>
+      <c r="G23">
+        <v>0.2048248666202737</v>
+      </c>
+      <c r="H23">
+        <v>0.2048248666202737</v>
+      </c>
+      <c r="I23">
+        <v>0.1805822285808033</v>
+      </c>
+      <c r="J23">
+        <v>0.1200959481338352</v>
+      </c>
+      <c r="K23">
+        <v>176.9</v>
+      </c>
+      <c r="L23">
+        <v>0.1025864068661563</v>
+      </c>
+      <c r="M23">
+        <v>166.836</v>
+      </c>
+      <c r="N23">
+        <v>0.05609441194270729</v>
+      </c>
+      <c r="O23">
+        <v>0.9431091011871114</v>
+      </c>
+      <c r="P23">
+        <v>135.036</v>
+      </c>
+      <c r="Q23">
+        <v>0.04540246116602784</v>
+      </c>
+      <c r="R23">
+        <v>0.7633465234595816</v>
+      </c>
+      <c r="S23">
+        <v>31.80000000000001</v>
+      </c>
+      <c r="T23">
+        <v>0.1906063439545422</v>
+      </c>
+      <c r="U23">
+        <v>390.8</v>
+      </c>
+      <c r="V23">
+        <v>0.1313966780983122</v>
+      </c>
+      <c r="W23">
+        <v>0.1045137658040884</v>
+      </c>
+      <c r="X23">
+        <v>0.07256181170164462</v>
+      </c>
+      <c r="Y23">
+        <v>0.03195195410244377</v>
+      </c>
+      <c r="Z23">
+        <v>0.3131048643679207</v>
+      </c>
+      <c r="AA23">
+        <v>0.0376026255515813</v>
+      </c>
+      <c r="AB23">
+        <v>0.05294209323236795</v>
+      </c>
+      <c r="AC23">
+        <v>-0.01533946768078665</v>
+      </c>
+      <c r="AD23">
+        <v>4767.7</v>
+      </c>
+      <c r="AE23">
+        <v>32.02002517631396</v>
+      </c>
+      <c r="AF23">
+        <v>4799.720025176313</v>
+      </c>
+      <c r="AG23">
+        <v>4408.920025176313</v>
+      </c>
+      <c r="AH23">
+        <v>0.6174130952765308</v>
+      </c>
+      <c r="AI23">
+        <v>0.7293720054969616</v>
+      </c>
+      <c r="AJ23">
+        <v>0.5971621767141766</v>
+      </c>
+      <c r="AK23">
+        <v>0.712285657295945</v>
+      </c>
+      <c r="AL23">
+        <v>17</v>
+      </c>
+      <c r="AM23">
+        <v>11.42</v>
+      </c>
+      <c r="AN23">
+        <v>11.59178215414539</v>
+      </c>
+      <c r="AO23">
+        <v>17.92941176470588</v>
+      </c>
+      <c r="AP23">
+        <v>10.71947489709777</v>
+      </c>
+      <c r="AQ23">
+        <v>26.69001751313485</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Japan Investment Adviser Co., Ltd. (TSE:7172)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.05860000000000001</v>
+      </c>
+      <c r="E24">
+        <v>-0.17</v>
+      </c>
+      <c r="G24">
+        <v>0.2135575942915393</v>
+      </c>
+      <c r="H24">
+        <v>0.2135575942915393</v>
+      </c>
+      <c r="I24">
+        <v>0.3868501529051988</v>
+      </c>
+      <c r="J24">
+        <v>0.2308787384712725</v>
+      </c>
+      <c r="K24">
+        <v>23.4</v>
+      </c>
+      <c r="L24">
+        <v>0.1192660550458716</v>
+      </c>
+      <c r="M24">
+        <v>11.7975</v>
+      </c>
+      <c r="N24">
+        <v>0.02683079372299295</v>
+      </c>
+      <c r="O24">
+        <v>0.5041666666666668</v>
+      </c>
+      <c r="P24">
+        <v>11.7975</v>
+      </c>
+      <c r="Q24">
+        <v>0.02683079372299295</v>
+      </c>
+      <c r="R24">
+        <v>0.5041666666666668</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>303.2</v>
+      </c>
+      <c r="V24">
+        <v>0.689561064362065</v>
+      </c>
+      <c r="W24">
+        <v>0.07191149354640443</v>
+      </c>
+      <c r="X24">
+        <v>0.07849691176057003</v>
+      </c>
+      <c r="Y24">
+        <v>-0.006585418214165598</v>
+      </c>
+      <c r="Z24">
+        <v>0.1689776935664456</v>
+      </c>
+      <c r="AA24">
+        <v>0.03901335672040623</v>
+      </c>
+      <c r="AB24">
+        <v>0.05514062535868362</v>
+      </c>
+      <c r="AC24">
+        <v>-0.0161272686382774</v>
+      </c>
+      <c r="AD24">
+        <v>1007.5</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>1007.5</v>
+      </c>
+      <c r="AG24">
+        <v>704.3</v>
+      </c>
+      <c r="AH24">
+        <v>0.6961719181868435</v>
+      </c>
+      <c r="AI24">
+        <v>0.7009670910735407</v>
+      </c>
+      <c r="AJ24">
+        <v>0.6156468531468531</v>
+      </c>
+      <c r="AK24">
+        <v>0.6210210739793669</v>
+      </c>
+      <c r="AL24">
+        <v>13.1</v>
+      </c>
+      <c r="AM24">
+        <v>9.74</v>
+      </c>
+      <c r="AN24">
+        <v>12.88363171355499</v>
+      </c>
+      <c r="AO24">
+        <v>5.793893129770993</v>
+      </c>
+      <c r="AP24">
+        <v>9.006393861892581</v>
+      </c>
+      <c r="AQ24">
+        <v>7.792607802874744</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Asax Co., Ltd. (TSE:8772)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.0418</v>
+      </c>
+      <c r="E25">
+        <v>0.0283</v>
+      </c>
+      <c r="G25">
+        <v>0.6444444444444444</v>
+      </c>
+      <c r="H25">
+        <v>0.6444444444444444</v>
+      </c>
+      <c r="I25">
+        <v>0.705050505050505</v>
+      </c>
+      <c r="J25">
+        <v>0.4604861111111111</v>
+      </c>
+      <c r="K25">
+        <v>21</v>
+      </c>
+      <c r="L25">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="M25">
+        <v>-0</v>
+      </c>
+      <c r="N25">
+        <v>-0</v>
+      </c>
+      <c r="O25">
+        <v>-0</v>
+      </c>
+      <c r="P25">
+        <v>-0</v>
+      </c>
+      <c r="Q25">
+        <v>-0</v>
+      </c>
+      <c r="R25">
+        <v>-0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>40.2</v>
+      </c>
+      <c r="V25">
+        <v>0.2707070707070707</v>
+      </c>
+      <c r="W25">
+        <v>0.07021063189568706</v>
+      </c>
+      <c r="X25">
+        <v>0.08421497366389599</v>
+      </c>
+      <c r="Y25">
+        <v>-0.01400434176820893</v>
+      </c>
+      <c r="Z25">
+        <v>0.07662538699690402</v>
+      </c>
+      <c r="AA25">
+        <v>0.03528492647058824</v>
+      </c>
+      <c r="AB25">
+        <v>0.0517959945451638</v>
+      </c>
+      <c r="AC25">
+        <v>-0.01651106807457556</v>
+      </c>
+      <c r="AD25">
+        <v>437.2</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>437.2</v>
+      </c>
+      <c r="AG25">
+        <v>397</v>
+      </c>
+      <c r="AH25">
+        <v>0.7464572306641625</v>
+      </c>
+      <c r="AI25">
+        <v>0.5712045989025346</v>
+      </c>
+      <c r="AJ25">
+        <v>0.7277726856095326</v>
+      </c>
+      <c r="AK25">
+        <v>0.5474351902923331</v>
+      </c>
+      <c r="AL25">
+        <v>0.307</v>
+      </c>
+      <c r="AM25">
+        <v>0.112</v>
+      </c>
+      <c r="AN25">
+        <v>12.31549295774648</v>
+      </c>
+      <c r="AO25">
+        <v>113.6807817589577</v>
+      </c>
+      <c r="AP25">
+        <v>11.1830985915493</v>
+      </c>
+      <c r="AQ25">
+        <v>311.6071428571429</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aiful Corporation (TSE:8515)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.0784</v>
+      </c>
+      <c r="E26">
+        <v>0.19</v>
+      </c>
+      <c r="G26">
+        <v>0.134940743767879</v>
+      </c>
+      <c r="H26">
+        <v>0.134940743767879</v>
+      </c>
+      <c r="I26">
+        <v>0.1342868818961994</v>
+      </c>
+      <c r="J26">
+        <v>0.1298937579109909</v>
+      </c>
+      <c r="K26">
+        <v>156.3</v>
+      </c>
+      <c r="L26">
+        <v>0.1277482631794034</v>
+      </c>
+      <c r="M26">
+        <v>17.3516</v>
+      </c>
+      <c r="N26">
+        <v>0.0168543953375425</v>
+      </c>
+      <c r="O26">
+        <v>0.1110147152911068</v>
+      </c>
+      <c r="P26">
+        <v>3.3516</v>
+      </c>
+      <c r="Q26">
+        <v>0.003255560951918407</v>
+      </c>
+      <c r="R26">
+        <v>0.02144337811900192</v>
+      </c>
+      <c r="S26">
+        <v>14</v>
+      </c>
+      <c r="T26">
+        <v>0.8068420203324188</v>
+      </c>
+      <c r="U26">
+        <v>339.3</v>
+      </c>
+      <c r="V26">
+        <v>0.3295774647887324</v>
+      </c>
+      <c r="W26">
+        <v>0.1279050736497545</v>
+      </c>
+      <c r="X26">
+        <v>0.101360246232739</v>
+      </c>
+      <c r="Y26">
+        <v>0.02654482741701553</v>
+      </c>
+      <c r="Z26">
+        <v>0.2466087517384556</v>
+      </c>
+      <c r="AA26">
+        <v>0.0320329374970466</v>
+      </c>
+      <c r="AB26">
+        <v>0.05104913858494459</v>
+      </c>
+      <c r="AC26">
+        <v>-0.01901620108789799</v>
+      </c>
+      <c r="AD26">
+        <v>5046</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>5046</v>
+      </c>
+      <c r="AG26">
+        <v>4706.7</v>
+      </c>
+      <c r="AH26">
+        <v>0.8305489260143198</v>
+      </c>
+      <c r="AI26">
+        <v>0.778175313059034</v>
+      </c>
+      <c r="AJ26">
+        <v>0.820525783619818</v>
+      </c>
+      <c r="AK26">
+        <v>0.7659273242095327</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-0.51</v>
+      </c>
+      <c r="AN26">
+        <v>25.81074168797954</v>
+      </c>
+      <c r="AP26">
+        <v>24.07519181585678</v>
+      </c>
+      <c r="AQ26">
+        <v>-322.1568627450981</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kyushu Leasing Service Co., Ltd. (TSE:8596)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0.09369999999999999</v>
+      </c>
+      <c r="E27">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="G27">
+        <v>0.142485119047619</v>
+      </c>
+      <c r="H27">
+        <v>0.142485119047619</v>
+      </c>
+      <c r="I27">
+        <v>0.1401582328645249</v>
+      </c>
+      <c r="J27">
+        <v>0.0958774724815019</v>
+      </c>
+      <c r="K27">
+        <v>23</v>
+      </c>
+      <c r="L27">
+        <v>0.08556547619047619</v>
+      </c>
+      <c r="M27">
+        <v>7.110200000000001</v>
+      </c>
+      <c r="N27">
+        <v>0.04563671373555841</v>
+      </c>
+      <c r="O27">
+        <v>0.3091391304347826</v>
+      </c>
+      <c r="P27">
+        <v>5.1302</v>
+      </c>
+      <c r="Q27">
+        <v>0.03292811296534018</v>
+      </c>
+      <c r="R27">
+        <v>0.2230521739130435</v>
+      </c>
+      <c r="S27">
+        <v>1.98</v>
+      </c>
+      <c r="T27">
+        <v>0.2784731793761076</v>
+      </c>
+      <c r="U27">
+        <v>33.3</v>
+      </c>
+      <c r="V27">
+        <v>0.2137355584082156</v>
+      </c>
+      <c r="W27">
+        <v>0.08798775822494262</v>
+      </c>
+      <c r="X27">
+        <v>0.1121938719541959</v>
+      </c>
+      <c r="Y27">
+        <v>-0.0242061137292533</v>
+      </c>
+      <c r="Z27">
+        <v>0.2485144294106852</v>
+      </c>
+      <c r="AA27">
+        <v>0.02382693536707912</v>
+      </c>
+      <c r="AB27">
+        <v>0.05287650128555334</v>
+      </c>
+      <c r="AC27">
+        <v>-0.02904956591847422</v>
+      </c>
+      <c r="AD27">
+        <v>939.8</v>
+      </c>
+      <c r="AE27">
+        <v>16.52733503007857</v>
+      </c>
+      <c r="AF27">
+        <v>956.3273350300785</v>
+      </c>
+      <c r="AG27">
+        <v>923.0273350300786</v>
+      </c>
+      <c r="AH27">
+        <v>0.8599081282398421</v>
+      </c>
+      <c r="AI27">
+        <v>0.7654737939493289</v>
+      </c>
+      <c r="AJ27">
+        <v>0.8555839336461973</v>
+      </c>
+      <c r="AK27">
+        <v>0.7590514690257744</v>
+      </c>
+      <c r="AL27">
+        <v>0.921</v>
+      </c>
+      <c r="AM27">
+        <v>0.544</v>
+      </c>
+      <c r="AN27">
+        <v>19.22667757774141</v>
+      </c>
+      <c r="AO27">
+        <v>40.60803474484256</v>
+      </c>
+      <c r="AP27">
+        <v>18.88353795069719</v>
+      </c>
+      <c r="AQ27">
+        <v>68.74999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fuyo General Lease Co., Ltd. (TSE:8424)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.00685</v>
+      </c>
+      <c r="E28">
+        <v>0.119</v>
+      </c>
+      <c r="G28">
+        <v>0.1563148717097069</v>
+      </c>
+      <c r="H28">
+        <v>0.1563148717097069</v>
+      </c>
+      <c r="I28">
+        <v>0.108845847679129</v>
+      </c>
+      <c r="J28">
+        <v>0.07958373367563747</v>
+      </c>
+      <c r="K28">
+        <v>328</v>
+      </c>
+      <c r="L28">
+        <v>0.0680893465083451</v>
+      </c>
+      <c r="M28">
+        <v>98.72799999999999</v>
+      </c>
+      <c r="N28">
+        <v>0.04405926454837557</v>
+      </c>
+      <c r="O28">
+        <v>0.301</v>
+      </c>
+      <c r="P28">
+        <v>98.72799999999999</v>
+      </c>
+      <c r="Q28">
+        <v>0.04405926454837557</v>
+      </c>
+      <c r="R28">
+        <v>0.301</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>676.7</v>
+      </c>
+      <c r="V28">
+        <v>0.3019903605855052</v>
+      </c>
+      <c r="W28">
+        <v>0.1212166007612994</v>
+      </c>
+      <c r="X28">
+        <v>0.1411917324246454</v>
+      </c>
+      <c r="Y28">
+        <v>-0.01997513166334601</v>
+      </c>
+      <c r="Z28">
+        <v>0.225264500356679</v>
+      </c>
+      <c r="AA28">
+        <v>0.01792739000296148</v>
+      </c>
+      <c r="AB28">
+        <v>0.05039418399070642</v>
+      </c>
+      <c r="AC28">
+        <v>-0.03246679398774494</v>
+      </c>
+      <c r="AD28">
+        <v>18989</v>
+      </c>
+      <c r="AE28">
+        <v>2183.3389128005</v>
+      </c>
+      <c r="AF28">
+        <v>21172.3389128005</v>
+      </c>
+      <c r="AG28">
+        <v>20495.6389128005</v>
+      </c>
+      <c r="AH28">
+        <v>0.9042930549233233</v>
+      </c>
+      <c r="AI28">
+        <v>0.8551702736784169</v>
+      </c>
+      <c r="AJ28">
+        <v>0.9014445486122965</v>
+      </c>
+      <c r="AK28">
+        <v>0.8511004719054881</v>
+      </c>
+      <c r="AL28">
+        <v>16.7</v>
+      </c>
+      <c r="AM28">
+        <v>-5.699999999999999</v>
+      </c>
+      <c r="AN28">
+        <v>14.12872023809524</v>
+      </c>
+      <c r="AO28">
+        <v>26.97604790419162</v>
+      </c>
+      <c r="AP28">
+        <v>15.24973133392894</v>
+      </c>
+      <c r="AQ28">
+        <v>-79.03508771929826</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Credit Saison Co., Ltd. (TSE:8253)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>0.0058</v>
+      </c>
+      <c r="E29">
+        <v>0.133</v>
+      </c>
+      <c r="G29">
+        <v>0.1915568490239037</v>
+      </c>
+      <c r="H29">
+        <v>0.1915568490239037</v>
+      </c>
+      <c r="I29">
+        <v>0.1364899774369707</v>
+      </c>
+      <c r="J29">
+        <v>0.09860178081201733</v>
+      </c>
+      <c r="K29">
+        <v>400.8</v>
+      </c>
+      <c r="L29">
+        <v>0.1310617703803015</v>
+      </c>
+      <c r="M29">
+        <v>251.9684</v>
+      </c>
+      <c r="N29">
+        <v>0.06920307607800055</v>
+      </c>
+      <c r="O29">
+        <v>0.6286636726546906</v>
+      </c>
+      <c r="P29">
+        <v>113.4684</v>
+      </c>
+      <c r="Q29">
+        <v>0.03116407580335073</v>
+      </c>
+      <c r="R29">
+        <v>0.2831047904191617</v>
+      </c>
+      <c r="S29">
+        <v>138.5</v>
+      </c>
+      <c r="T29">
+        <v>0.549672101739742</v>
+      </c>
+      <c r="U29">
+        <v>693.9</v>
+      </c>
+      <c r="V29">
+        <v>0.1905795111233178</v>
+      </c>
+      <c r="W29">
+        <v>0.09119453924914676</v>
+      </c>
+      <c r="X29">
+        <v>0.1129120443964841</v>
+      </c>
+      <c r="Y29">
+        <v>-0.02171750514733729</v>
+      </c>
+      <c r="Z29">
+        <v>0.1333179297597042</v>
+      </c>
+      <c r="AA29">
+        <v>0.01314538528847828</v>
+      </c>
+      <c r="AB29">
+        <v>0.05077425801630319</v>
+      </c>
+      <c r="AC29">
+        <v>-0.03762887272782491</v>
+      </c>
+      <c r="AD29">
+        <v>22647.6</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>22647.6</v>
+      </c>
+      <c r="AG29">
+        <v>21953.7</v>
+      </c>
+      <c r="AH29">
+        <v>0.8614989006641662</v>
+      </c>
+      <c r="AI29">
+        <v>0.8229386200781965</v>
+      </c>
+      <c r="AJ29">
+        <v>0.8577439860596139</v>
+      </c>
+      <c r="AK29">
+        <v>0.81835871246715</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="AN29">
+        <v>34.88539741219962</v>
+      </c>
+      <c r="AP29">
+        <v>33.81654343807763</v>
+      </c>
+      <c r="AQ29">
+        <v>-46.95163104611923</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mizuho Leasing Company, Limited (TSE:8425)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.08220000000000001</v>
+      </c>
+      <c r="E30">
+        <v>0.206</v>
+      </c>
+      <c r="G30">
+        <v>0.08040960214873258</v>
+      </c>
+      <c r="H30">
+        <v>0.08040960214873258</v>
+      </c>
+      <c r="I30">
+        <v>0.06566407386356102</v>
+      </c>
+      <c r="J30">
+        <v>0.04979147682342898</v>
+      </c>
+      <c r="K30">
+        <v>299.6</v>
+      </c>
+      <c r="L30">
+        <v>0.06286721504112809</v>
+      </c>
+      <c r="M30">
+        <v>81.73079999999999</v>
+      </c>
+      <c r="N30">
+        <v>0.04346920540368045</v>
+      </c>
+      <c r="O30">
+        <v>0.272799732977303</v>
+      </c>
+      <c r="P30">
+        <v>81.73079999999999</v>
+      </c>
+      <c r="Q30">
+        <v>0.04346920540368045</v>
+      </c>
+      <c r="R30">
+        <v>0.272799732977303</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>334</v>
+      </c>
+      <c r="V30">
+        <v>0.177640676523774</v>
+      </c>
+      <c r="W30">
+        <v>0.1531071136549469</v>
+      </c>
+      <c r="X30">
+        <v>0.1581542943408506</v>
+      </c>
+      <c r="Y30">
+        <v>-0.005047180685903707</v>
+      </c>
+      <c r="Z30">
+        <v>0.2394582970788205</v>
+      </c>
+      <c r="AA30">
+        <v>0.01192298224917786</v>
+      </c>
+      <c r="AB30">
+        <v>0.05026128073655609</v>
+      </c>
+      <c r="AC30">
+        <v>-0.03833829848737823</v>
+      </c>
+      <c r="AD30">
+        <v>21406</v>
+      </c>
+      <c r="AE30">
+        <v>0.08644797906788472</v>
+      </c>
+      <c r="AF30">
+        <v>21406.08644797907</v>
+      </c>
+      <c r="AG30">
+        <v>21072.08644797907</v>
+      </c>
+      <c r="AH30">
+        <v>0.9192571986864322</v>
+      </c>
+      <c r="AI30">
+        <v>0.8847542587618334</v>
+      </c>
+      <c r="AJ30">
+        <v>0.9180822353249452</v>
+      </c>
+      <c r="AK30">
+        <v>0.8831410377162536</v>
+      </c>
+      <c r="AL30">
+        <v>27.5</v>
+      </c>
+      <c r="AM30">
+        <v>21.47</v>
+      </c>
+      <c r="AN30">
+        <v>47.70181795492328</v>
+      </c>
+      <c r="AO30">
+        <v>11.37818181818182</v>
+      </c>
+      <c r="AP30">
+        <v>46.95771427038697</v>
+      </c>
+      <c r="AQ30">
+        <v>14.57382394038193</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mitsubishi HC Capital Inc. (TSE:8593)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.179</v>
+      </c>
+      <c r="E31">
+        <v>0.123</v>
+      </c>
+      <c r="G31">
+        <v>0.2258883073719341</v>
+      </c>
+      <c r="H31">
+        <v>0.2258883073719341</v>
+      </c>
+      <c r="I31">
+        <v>0.08944001257439513</v>
+      </c>
+      <c r="J31">
+        <v>0.06451592389803058</v>
+      </c>
+      <c r="K31">
+        <v>927.1</v>
+      </c>
+      <c r="L31">
+        <v>0.06392779076422361</v>
+      </c>
+      <c r="M31">
+        <v>390.3472</v>
+      </c>
+      <c r="N31">
+        <v>0.04103647946847206</v>
+      </c>
+      <c r="O31">
+        <v>0.4210410958904109</v>
+      </c>
+      <c r="P31">
+        <v>390.3472</v>
+      </c>
+      <c r="Q31">
+        <v>0.04103647946847206</v>
+      </c>
+      <c r="R31">
+        <v>0.4210410958904109</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>2668.5</v>
+      </c>
+      <c r="V31">
+        <v>0.2805344715207838</v>
+      </c>
+      <c r="W31">
+        <v>0.08325550486727253</v>
+      </c>
+      <c r="X31">
+        <v>0.1134791916180213</v>
+      </c>
+      <c r="Y31">
+        <v>-0.03022368675074881</v>
+      </c>
+      <c r="Z31">
+        <v>0.2232604477720556</v>
+      </c>
+      <c r="AA31">
+        <v>0.01440385405790217</v>
+      </c>
+      <c r="AB31">
+        <v>0.05285829233351799</v>
+      </c>
+      <c r="AC31">
+        <v>-0.03845443827561582</v>
+      </c>
+      <c r="AD31">
+        <v>59730.7</v>
+      </c>
+      <c r="AE31">
+        <v>52.57052821174747</v>
+      </c>
+      <c r="AF31">
+        <v>59783.27052821175</v>
+      </c>
+      <c r="AG31">
+        <v>57114.77052821175</v>
+      </c>
+      <c r="AH31">
+        <v>0.8627298447143472</v>
+      </c>
+      <c r="AI31">
+        <v>0.8310102796000964</v>
+      </c>
+      <c r="AJ31">
+        <v>0.8572319899195736</v>
+      </c>
+      <c r="AK31">
+        <v>0.8245004450241695</v>
+      </c>
+      <c r="AL31">
+        <v>66.2</v>
+      </c>
+      <c r="AM31">
+        <v>41.6</v>
+      </c>
+      <c r="AN31">
+        <v>15.04172752455301</v>
+      </c>
+      <c r="AO31">
+        <v>19.40030211480362</v>
+      </c>
+      <c r="AP31">
+        <v>14.38296915845171</v>
+      </c>
+      <c r="AQ31">
+        <v>30.87259615384615</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tokyo Century Corporation (TSE:8439)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.0375</v>
+      </c>
+      <c r="E32">
+        <v>0.0799</v>
+      </c>
+      <c r="G32">
+        <v>0.250588591053416</v>
+      </c>
+      <c r="H32">
+        <v>0.250588591053416</v>
+      </c>
+      <c r="I32">
+        <v>0.08098796898287146</v>
+      </c>
+      <c r="J32">
+        <v>0.05716958485030352</v>
+      </c>
+      <c r="K32">
+        <v>556</v>
+      </c>
+      <c r="L32">
+        <v>0.06004708728427328</v>
+      </c>
+      <c r="M32">
+        <v>212.2689</v>
+      </c>
+      <c r="N32">
+        <v>0.04266883090777519</v>
+      </c>
+      <c r="O32">
+        <v>0.3817785971223022</v>
+      </c>
+      <c r="P32">
+        <v>190.7689</v>
+      </c>
+      <c r="Q32">
+        <v>0.03834704912760312</v>
+      </c>
+      <c r="R32">
+        <v>0.3431095323741007</v>
+      </c>
+      <c r="S32">
+        <v>21.5</v>
+      </c>
+      <c r="T32">
+        <v>0.1012866227695155</v>
+      </c>
+      <c r="U32">
+        <v>1233.7</v>
+      </c>
+      <c r="V32">
+        <v>0.2479898689394548</v>
+      </c>
+      <c r="W32">
+        <v>0.09531646437632861</v>
+      </c>
+      <c r="X32">
+        <v>0.1207232413354036</v>
+      </c>
+      <c r="Y32">
+        <v>-0.02540677695907502</v>
+      </c>
+      <c r="Z32">
+        <v>0.2654400972387854</v>
+      </c>
+      <c r="AA32">
+        <v>0.01517510016176556</v>
+      </c>
+      <c r="AB32">
+        <v>0.05428866341774055</v>
+      </c>
+      <c r="AC32">
+        <v>-0.03911356325597499</v>
+      </c>
+      <c r="AD32">
+        <v>35380.2</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>35380.2</v>
+      </c>
+      <c r="AG32">
+        <v>34146.5</v>
+      </c>
+      <c r="AH32">
+        <v>0.8767240738446288</v>
+      </c>
+      <c r="AI32">
+        <v>0.8119044996420114</v>
+      </c>
+      <c r="AJ32">
+        <v>0.8728365366181593</v>
+      </c>
+      <c r="AK32">
+        <v>0.8064241871757146</v>
+      </c>
+      <c r="AL32">
+        <v>60.6</v>
+      </c>
+      <c r="AM32">
+        <v>44.3</v>
+      </c>
+      <c r="AN32">
+        <v>13.81014091104258</v>
+      </c>
+      <c r="AO32">
+        <v>12.37458745874587</v>
+      </c>
+      <c r="AP32">
+        <v>13.32858425387408</v>
+      </c>
+      <c r="AQ32">
+        <v>16.92776523702032</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ricoh Leasing Company, Ltd. (TSE:8566)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>-0.0111</v>
+      </c>
+      <c r="E33">
+        <v>0.0306</v>
+      </c>
+      <c r="G33">
+        <v>0.1253561253561254</v>
+      </c>
+      <c r="H33">
+        <v>0.1253561253561254</v>
+      </c>
+      <c r="I33">
+        <v>0.06943664537083973</v>
+      </c>
+      <c r="J33">
+        <v>0.04790402711995215</v>
+      </c>
+      <c r="K33">
+        <v>99</v>
+      </c>
+      <c r="L33">
+        <v>0.04623791509037411</v>
+      </c>
+      <c r="M33">
+        <v>33.264</v>
+      </c>
+      <c r="N33">
+        <v>0.03237687366167023</v>
+      </c>
+      <c r="O33">
+        <v>0.336</v>
+      </c>
+      <c r="P33">
+        <v>33.264</v>
+      </c>
+      <c r="Q33">
+        <v>0.03237687366167023</v>
+      </c>
+      <c r="R33">
+        <v>0.336</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>25.4</v>
+      </c>
+      <c r="V33">
+        <v>0.02472260073973136</v>
+      </c>
+      <c r="W33">
+        <v>0.06804591380850918</v>
+      </c>
+      <c r="X33">
+        <v>0.1178721041097145</v>
+      </c>
+      <c r="Y33">
+        <v>-0.04982619030120532</v>
+      </c>
+      <c r="Z33">
+        <v>0.2878230332657079</v>
+      </c>
+      <c r="AA33">
+        <v>0.01378788239130736</v>
+      </c>
+      <c r="AB33">
+        <v>0.05431297932250781</v>
+      </c>
+      <c r="AC33">
+        <v>-0.04052509693120045</v>
+      </c>
+      <c r="AD33">
+        <v>6920.7</v>
+      </c>
+      <c r="AE33">
+        <v>51.64599298247533</v>
+      </c>
+      <c r="AF33">
+        <v>6972.345992982475</v>
+      </c>
+      <c r="AG33">
+        <v>6946.945992982475</v>
+      </c>
+      <c r="AH33">
+        <v>0.8715709222641251</v>
+      </c>
+      <c r="AI33">
+        <v>0.8143888308934576</v>
+      </c>
+      <c r="AJ33">
+        <v>0.8711618481435186</v>
+      </c>
+      <c r="AK33">
+        <v>0.813836523220891</v>
+      </c>
+      <c r="AL33">
+        <v>1.98</v>
+      </c>
+      <c r="AM33">
+        <v>-4.289999999999999</v>
+      </c>
+      <c r="AN33">
+        <v>22.72807881773399</v>
+      </c>
+      <c r="AO33">
+        <v>73.8888888888889</v>
+      </c>
+      <c r="AP33">
+        <v>22.81427255495066</v>
+      </c>
+      <c r="AQ33">
+        <v>-34.10256410256411</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NEC Capital Solutions Limited (TSE:8793)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.0326</v>
+      </c>
+      <c r="E34">
+        <v>-0.0134</v>
+      </c>
+      <c r="G34">
+        <v>0.1448991031390134</v>
+      </c>
+      <c r="H34">
+        <v>0.1448991031390134</v>
+      </c>
+      <c r="I34">
+        <v>0.04966367713004484</v>
+      </c>
+      <c r="J34">
+        <v>0.0336597894893859</v>
+      </c>
+      <c r="K34">
+        <v>59.1</v>
+      </c>
+      <c r="L34">
+        <v>0.03312780269058296</v>
+      </c>
+      <c r="M34">
+        <v>21.0055</v>
+      </c>
+      <c r="N34">
+        <v>0.03900742804085422</v>
+      </c>
+      <c r="O34">
+        <v>0.3554230118443316</v>
+      </c>
+      <c r="P34">
+        <v>21.0055</v>
+      </c>
+      <c r="Q34">
+        <v>0.03900742804085422</v>
+      </c>
+      <c r="R34">
+        <v>0.3554230118443316</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>259.4</v>
+      </c>
+      <c r="V34">
+        <v>0.4817084493964716</v>
+      </c>
+      <c r="W34">
+        <v>0.07864271457085828</v>
+      </c>
+      <c r="X34">
+        <v>0.1605841386802203</v>
+      </c>
+      <c r="Y34">
+        <v>-0.08194142410936198</v>
+      </c>
+      <c r="Z34">
+        <v>0.2832645284217212</v>
+      </c>
+      <c r="AA34">
+        <v>0.009534624396485303</v>
+      </c>
+      <c r="AB34">
+        <v>0.0502455712029392</v>
+      </c>
+      <c r="AC34">
+        <v>-0.0407109468064539</v>
+      </c>
+      <c r="AD34">
+        <v>6280.2</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>6280.2</v>
+      </c>
+      <c r="AG34">
+        <v>6020.8</v>
+      </c>
+      <c r="AH34">
+        <v>0.9210260020238462</v>
+      </c>
+      <c r="AI34">
+        <v>0.8659955874241588</v>
+      </c>
+      <c r="AJ34">
+        <v>0.9179028249965697</v>
+      </c>
+      <c r="AK34">
+        <v>0.8610245116265767</v>
+      </c>
+      <c r="AL34">
+        <v>2.92</v>
+      </c>
+      <c r="AM34">
+        <v>-5.43</v>
+      </c>
+      <c r="AN34">
+        <v>21.51490236382323</v>
+      </c>
+      <c r="AO34">
+        <v>30.34246575342465</v>
+      </c>
+      <c r="AP34">
+        <v>20.62624186365194</v>
+      </c>
+      <c r="AQ34">
+        <v>-16.31675874769797</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JACCS Co., Ltd. (TSE:8584)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.0436</v>
+      </c>
+      <c r="E35">
+        <v>0.177</v>
+      </c>
+      <c r="G35">
+        <v>0.2242848447961047</v>
+      </c>
+      <c r="H35">
+        <v>0.2242848447961047</v>
+      </c>
+      <c r="I35">
+        <v>0.163496652465003</v>
+      </c>
+      <c r="J35">
+        <v>0.1140911219693479</v>
+      </c>
+      <c r="K35">
+        <v>158.1</v>
+      </c>
+      <c r="L35">
+        <v>0.1202830188679245</v>
+      </c>
+      <c r="M35">
+        <v>48.608</v>
+      </c>
+      <c r="N35">
+        <v>0.05633750579508576</v>
+      </c>
+      <c r="O35">
+        <v>0.3074509803921568</v>
+      </c>
+      <c r="P35">
+        <v>48.58</v>
+      </c>
+      <c r="Q35">
+        <v>0.05630505331478906</v>
+      </c>
+      <c r="R35">
+        <v>0.3072738772928526</v>
+      </c>
+      <c r="S35">
+        <v>0.02799999999999869</v>
+      </c>
+      <c r="T35">
+        <v>0.0005760368663594201</v>
+      </c>
+      <c r="U35">
+        <v>781.8</v>
+      </c>
+      <c r="V35">
+        <v>0.9061196105702365</v>
+      </c>
+      <c r="W35">
+        <v>0.1076975476839237</v>
+      </c>
+      <c r="X35">
+        <v>0.2643200721947529</v>
+      </c>
+      <c r="Y35">
+        <v>-0.1566225245108292</v>
+      </c>
+      <c r="Z35">
+        <v>0.06667014963755968</v>
+      </c>
+      <c r="AA35">
+        <v>0.007606472174013498</v>
+      </c>
+      <c r="AB35">
+        <v>0.04990660384315736</v>
+      </c>
+      <c r="AC35">
+        <v>-0.04230013166914386</v>
+      </c>
+      <c r="AD35">
+        <v>20280</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>20280</v>
+      </c>
+      <c r="AG35">
+        <v>19498.2</v>
+      </c>
+      <c r="AH35">
+        <v>0.9591917815994098</v>
+      </c>
+      <c r="AI35">
+        <v>0.9213156460112666</v>
+      </c>
+      <c r="AJ35">
+        <v>0.9576248710770591</v>
+      </c>
+      <c r="AK35">
+        <v>0.9184181025143427</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
+        <v>68.67592279038266</v>
+      </c>
+      <c r="AP35">
+        <v>66.02844564849306</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Orient Corporation (TSE:8585)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>-0.0003500000000000001</v>
+      </c>
+      <c r="E36">
+        <v>-0.222</v>
+      </c>
+      <c r="G36">
+        <v>0.149806259314456</v>
+      </c>
+      <c r="H36">
+        <v>0.149806259314456</v>
+      </c>
+      <c r="I36">
+        <v>0.07236959761549926</v>
+      </c>
+      <c r="J36">
+        <v>0.03618479880774963</v>
+      </c>
+      <c r="K36">
+        <v>43.2</v>
+      </c>
+      <c r="L36">
+        <v>0.02575260804769001</v>
+      </c>
+      <c r="M36">
+        <v>52.0748</v>
+      </c>
+      <c r="N36">
+        <v>0.05645576756287945</v>
+      </c>
+      <c r="O36">
+        <v>1.205435185185185</v>
+      </c>
+      <c r="P36">
+        <v>47.7648</v>
+      </c>
+      <c r="Q36">
+        <v>0.05178317432784042</v>
+      </c>
+      <c r="R36">
+        <v>1.105666666666667</v>
+      </c>
+      <c r="S36">
+        <v>4.310000000000002</v>
+      </c>
+      <c r="T36">
+        <v>0.08276556030940113</v>
+      </c>
+      <c r="U36">
+        <v>1839</v>
+      </c>
+      <c r="V36">
+        <v>1.993712055507372</v>
+      </c>
+      <c r="W36">
+        <v>0.028125</v>
+      </c>
+      <c r="X36">
+        <v>0.2041232009435579</v>
+      </c>
+      <c r="Y36">
+        <v>-0.1759982009435579</v>
+      </c>
+      <c r="Z36">
+        <v>0.1301840814552679</v>
+      </c>
+      <c r="AA36">
+        <v>0.004710684795430558</v>
+      </c>
+      <c r="AB36">
+        <v>0.05004785663280965</v>
+      </c>
+      <c r="AC36">
+        <v>-0.04533717183737909</v>
+      </c>
+      <c r="AD36">
+        <v>15342.1</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>15342.1</v>
+      </c>
+      <c r="AG36">
+        <v>13503.1</v>
+      </c>
+      <c r="AH36">
+        <v>0.9432875280518922</v>
+      </c>
+      <c r="AI36">
+        <v>0.9013577265864134</v>
+      </c>
+      <c r="AJ36">
+        <v>0.9360576756438252</v>
+      </c>
+      <c r="AK36">
+        <v>0.8894092385111414</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>58.57999236349752</v>
+      </c>
+      <c r="AP36">
+        <v>51.55822833142421</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>Japan Securities Finance Co., Ltd. (TSE:8511)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D37">
         <v>0.147</v>
       </c>
-      <c r="E7">
+      <c r="E37">
         <v>0.197</v>
       </c>
-      <c r="G7">
+      <c r="G37">
         <v>0.1894277190127475</v>
       </c>
-      <c r="H7">
+      <c r="H37">
         <v>0.1893138052617304</v>
       </c>
-      <c r="I7">
+      <c r="I37">
         <v>0.1941958231624627</v>
       </c>
-      <c r="J7">
+      <c r="J37">
         <v>0.1408499564305375</v>
       </c>
-      <c r="K7">
+      <c r="K37">
         <v>66.8</v>
       </c>
-      <c r="L7">
+      <c r="L37">
         <v>0.1811771087605099</v>
       </c>
-      <c r="M7">
+      <c r="M37">
         <v>63.99040000000001</v>
       </c>
-      <c r="N7">
+      <c r="N37">
         <v>0.05883633688856198</v>
       </c>
-      <c r="O7">
+      <c r="O37">
         <v>0.9579401197604792</v>
       </c>
-      <c r="P7">
+      <c r="P37">
         <v>37.1904</v>
       </c>
-      <c r="Q7">
+      <c r="Q37">
         <v>0.03419492460463406</v>
       </c>
-      <c r="R7">
+      <c r="R37">
         <v>0.55674251497006</v>
       </c>
-      <c r="S7">
+      <c r="S37">
         <v>26.8</v>
       </c>
-      <c r="T7">
+      <c r="T37">
         <v>0.4188128219232885</v>
       </c>
-      <c r="U7">
+      <c r="U37">
         <v>13332.4</v>
       </c>
-      <c r="V7">
+      <c r="V37">
         <v>12.2585509378448</v>
       </c>
-      <c r="W7">
+      <c r="W37">
         <v>0.07013859722805543</v>
       </c>
-      <c r="X7">
-        <v>0.2173711322407752</v>
-      </c>
-      <c r="Y7">
-        <v>-0.1472325350127198</v>
-      </c>
-      <c r="Z7">
+      <c r="X37">
+        <v>0.2172953822501438</v>
+      </c>
+      <c r="Y37">
+        <v>-0.1471567850220884</v>
+      </c>
+      <c r="Z37">
         <v>0.03505752591043073</v>
       </c>
-      <c r="AA7">
+      <c r="AA37">
         <v>0.00493785099704661</v>
       </c>
-      <c r="AB7">
-        <v>0.05165609745249023</v>
-      </c>
-      <c r="AC7">
-        <v>-0.04671824645544362</v>
-      </c>
-      <c r="AD7">
+      <c r="AB37">
+        <v>0.05165213905698501</v>
+      </c>
+      <c r="AC37">
+        <v>-0.04671428805993839</v>
+      </c>
+      <c r="AD37">
         <v>19725.3</v>
       </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
         <v>19725.3</v>
       </c>
-      <c r="AG7">
+      <c r="AG37">
         <v>6392.9</v>
       </c>
-      <c r="AH7">
+      <c r="AH37">
         <v>0.9477439472634761</v>
       </c>
-      <c r="AI7">
+      <c r="AI37">
         <v>0.9526645222985309</v>
       </c>
-      <c r="AJ7">
+      <c r="AJ37">
         <v>0.8546086491544682</v>
       </c>
-      <c r="AK7">
+      <c r="AK37">
         <v>0.8670690356706903</v>
       </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
         <v>-3.2</v>
       </c>
-      <c r="AN7">
+      <c r="AN37">
         <v>261.2622516556291</v>
       </c>
-      <c r="AP7">
+      <c r="AP37">
         <v>84.67417218543046</v>
       </c>
-      <c r="AQ7">
+      <c r="AQ37">
         <v>-22.375</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bank of Japan (TSE:8301)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>15319</v>
+      </c>
+      <c r="L38">
+        <v>0.5461591665894199</v>
+      </c>
+      <c r="M38">
+        <v>-0</v>
+      </c>
+      <c r="N38">
+        <v>-0</v>
+      </c>
+      <c r="O38">
+        <v>-0</v>
+      </c>
+      <c r="P38">
+        <v>-0</v>
+      </c>
+      <c r="Q38">
+        <v>-0</v>
+      </c>
+      <c r="R38">
+        <v>-0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>3256.6</v>
+      </c>
+      <c r="V38">
+        <v>19.61807228915663</v>
+      </c>
+      <c r="W38">
+        <v>0.4177825534398403</v>
+      </c>
+      <c r="X38">
+        <v>51.85891649542663</v>
+      </c>
+      <c r="Y38">
+        <v>-51.44113394198679</v>
+      </c>
+      <c r="Z38">
+        <v>0.03209567528952487</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0.0495456694333857</v>
+      </c>
+      <c r="AC38">
+        <v>-0.0495456694333857</v>
+      </c>
+      <c r="AD38">
+        <v>981646.5</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>981646.5</v>
+      </c>
+      <c r="AG38">
+        <v>978389.9</v>
+      </c>
+      <c r="AH38">
+        <v>0.9998309249474824</v>
+      </c>
+      <c r="AI38">
+        <v>0.9623732435265426</v>
+      </c>
+      <c r="AJ38">
+        <v>0.9998303622715882</v>
+      </c>
+      <c r="AK38">
+        <v>0.9622527292794379</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Global Communication Planning Co.,Ltd. (TSE:4073)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0.04317073170731707</v>
+      </c>
+      <c r="H39">
+        <v>0.03235772357723577</v>
+      </c>
+      <c r="I39">
+        <v>0.002845528455284553</v>
+      </c>
+      <c r="J39">
+        <v>0.002845528455284553</v>
+      </c>
+      <c r="K39">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L39">
+        <v>0.005691056910569106</v>
+      </c>
+      <c r="M39">
+        <v>-0</v>
+      </c>
+      <c r="N39">
+        <v>-0</v>
+      </c>
+      <c r="O39">
+        <v>-0</v>
+      </c>
+      <c r="P39">
+        <v>-0</v>
+      </c>
+      <c r="Q39">
+        <v>-0</v>
+      </c>
+      <c r="R39">
+        <v>-0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>3.8</v>
+      </c>
+      <c r="V39">
+        <v>0.4303510758776897</v>
+      </c>
+      <c r="W39">
+        <v>0.02651515151515152</v>
+      </c>
+      <c r="X39">
+        <v>0.06484406887461565</v>
+      </c>
+      <c r="Y39">
+        <v>-0.03832891735946413</v>
+      </c>
+      <c r="Z39">
+        <v>2.97820823244552</v>
+      </c>
+      <c r="AA39">
+        <v>0.008474576271186441</v>
+      </c>
+      <c r="AB39">
+        <v>0.05827857809090686</v>
+      </c>
+      <c r="AC39">
+        <v>-0.04980400181972042</v>
+      </c>
+      <c r="AD39">
+        <v>6.47</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>6.47</v>
+      </c>
+      <c r="AG39">
+        <v>2.67</v>
+      </c>
+      <c r="AH39">
+        <v>0.422875816993464</v>
+      </c>
+      <c r="AI39">
+        <v>0.6964477933261572</v>
+      </c>
+      <c r="AJ39">
+        <v>0.2321739130434783</v>
+      </c>
+      <c r="AK39">
+        <v>0.4863387978142076</v>
+      </c>
+      <c r="AL39">
+        <v>0.049</v>
+      </c>
+      <c r="AM39">
+        <v>0.049</v>
+      </c>
+      <c r="AN39">
+        <v>-924.2857142857142</v>
+      </c>
+      <c r="AO39">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AP39">
+        <v>-381.4285714285714</v>
+      </c>
+      <c r="AQ39">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AEON Financial Service Co., Ltd. (TSE:8570)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>148.7</v>
+      </c>
+      <c r="L40">
+        <v>0.05005722749612872</v>
+      </c>
+      <c r="M40">
+        <v>72.75830000000001</v>
+      </c>
+      <c r="N40">
+        <v>0.04152633982078649</v>
+      </c>
+      <c r="O40">
+        <v>0.4892958977807667</v>
+      </c>
+      <c r="P40">
+        <v>72.75830000000001</v>
+      </c>
+      <c r="Q40">
+        <v>0.04152633982078649</v>
+      </c>
+      <c r="R40">
+        <v>0.4892958977807667</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>2672.9</v>
+      </c>
+      <c r="V40">
+        <v>1.525540779635866</v>
+      </c>
+      <c r="W40">
+        <v>0.04738234075773507</v>
+      </c>
+      <c r="X40">
+        <v>0.09915367117517625</v>
+      </c>
+      <c r="Y40">
+        <v>-0.05177133041744118</v>
+      </c>
+      <c r="Z40">
+        <v>0.4621631713236666</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0.05111624274347162</v>
+      </c>
+      <c r="AC40">
+        <v>-0.05111624274347162</v>
+      </c>
+      <c r="AD40">
+        <v>8146.4</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>8146.4</v>
+      </c>
+      <c r="AG40">
+        <v>5473.5</v>
+      </c>
+      <c r="AH40">
+        <v>0.8229933828357832</v>
+      </c>
+      <c r="AI40">
+        <v>0.6881335315583187</v>
+      </c>
+      <c r="AJ40">
+        <v>0.7575149468556244</v>
+      </c>
+      <c r="AK40">
+        <v>0.5971850962849817</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Wedge Holdings CO.,LTD. (TSE:2388)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>-0.379</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>-0.036</v>
+      </c>
+      <c r="J41">
+        <v>-0.036</v>
+      </c>
+      <c r="K41">
+        <v>-6.58</v>
+      </c>
+      <c r="L41">
+        <v>-1.096666666666667</v>
+      </c>
+      <c r="M41">
+        <v>-0</v>
+      </c>
+      <c r="N41">
+        <v>-0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>-0</v>
+      </c>
+      <c r="Q41">
+        <v>-0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>3.57</v>
+      </c>
+      <c r="V41">
+        <v>0.21</v>
+      </c>
+      <c r="W41">
+        <v>-0.2898678414096916</v>
+      </c>
+      <c r="X41">
+        <v>0.06004872704021957</v>
+      </c>
+      <c r="Y41">
+        <v>-0.3499165684499112</v>
+      </c>
+      <c r="Z41">
+        <v>0.2862595419847329</v>
+      </c>
+      <c r="AA41">
+        <v>-0.01030534351145038</v>
+      </c>
+      <c r="AB41">
+        <v>0.05741681043343402</v>
+      </c>
+      <c r="AC41">
+        <v>-0.0677221539448844</v>
+      </c>
+      <c r="AD41">
+        <v>3.15</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>3.15</v>
+      </c>
+      <c r="AG41">
+        <v>-0.4199999999999999</v>
+      </c>
+      <c r="AH41">
+        <v>0.1563275434243176</v>
+      </c>
+      <c r="AI41">
+        <v>0.1288343558282209</v>
+      </c>
+      <c r="AJ41">
+        <v>-0.02533172496984318</v>
+      </c>
+      <c r="AK41">
+        <v>-0.02011494252873562</v>
+      </c>
+      <c r="AL41">
+        <v>0.077</v>
+      </c>
+      <c r="AM41">
+        <v>-0.195</v>
+      </c>
+      <c r="AO41">
+        <v>-2.805194805194805</v>
+      </c>
+      <c r="AQ41">
+        <v>1.107692307692308</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MINKABU THE INFONOID, Inc. (TSE:4436)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>0.00545</v>
+      </c>
+      <c r="G42">
+        <v>0.0461864406779661</v>
+      </c>
+      <c r="H42">
+        <v>0.0461864406779661</v>
+      </c>
+      <c r="I42">
+        <v>-0.05354325332094809</v>
+      </c>
+      <c r="J42">
+        <v>-0.05354325332094809</v>
+      </c>
+      <c r="K42">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="L42">
+        <v>-0.1231638418079096</v>
+      </c>
+      <c r="M42">
+        <v>2.715</v>
+      </c>
+      <c r="N42">
+        <v>0.03294902912621359</v>
+      </c>
+      <c r="O42">
+        <v>-0.3113532110091743</v>
+      </c>
+      <c r="P42">
+        <v>2.715</v>
+      </c>
+      <c r="Q42">
+        <v>0.03294902912621359</v>
+      </c>
+      <c r="R42">
+        <v>-0.3113532110091743</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>3.46</v>
+      </c>
+      <c r="V42">
+        <v>0.04199029126213592</v>
+      </c>
+      <c r="W42">
+        <v>-0.1820459290187892</v>
+      </c>
+      <c r="X42">
+        <v>0.06416662193636047</v>
+      </c>
+      <c r="Y42">
+        <v>-0.2462125509551496</v>
+      </c>
+      <c r="Z42">
+        <v>1.291869158380497</v>
+      </c>
+      <c r="AA42">
+        <v>-0.06917087760468695</v>
+      </c>
+      <c r="AB42">
+        <v>0.05587072681320895</v>
+      </c>
+      <c r="AC42">
+        <v>-0.1250416044178959</v>
+      </c>
+      <c r="AD42">
+        <v>51</v>
+      </c>
+      <c r="AE42">
+        <v>3.004311675615621</v>
+      </c>
+      <c r="AF42">
+        <v>54.00431167561562</v>
+      </c>
+      <c r="AG42">
+        <v>50.54431167561562</v>
+      </c>
+      <c r="AH42">
+        <v>0.3959135236431806</v>
+      </c>
+      <c r="AI42">
+        <v>0.5825436886321285</v>
+      </c>
+      <c r="AJ42">
+        <v>0.3801916083400683</v>
+      </c>
+      <c r="AK42">
+        <v>0.5663589166257856</v>
+      </c>
+      <c r="AL42">
+        <v>0.496</v>
+      </c>
+      <c r="AM42">
+        <v>0.461</v>
+      </c>
+      <c r="AN42">
+        <v>10</v>
+      </c>
+      <c r="AO42">
+        <v>-9.97983870967742</v>
+      </c>
+      <c r="AP42">
+        <v>9.910649348159925</v>
+      </c>
+      <c r="AQ42">
+        <v>-10.73752711496746</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Daikokuya Holdings Co.,Ltd. (TSE:6993)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>-0.122</v>
+      </c>
+      <c r="G43">
+        <v>-0.006794520547945206</v>
+      </c>
+      <c r="H43">
+        <v>-0.006794520547945206</v>
+      </c>
+      <c r="I43">
+        <v>-0.04767123287671233</v>
+      </c>
+      <c r="J43">
+        <v>-0.04767123287671233</v>
+      </c>
+      <c r="K43">
+        <v>-5.74</v>
+      </c>
+      <c r="L43">
+        <v>-0.07863013698630138</v>
+      </c>
+      <c r="M43">
+        <v>-0</v>
+      </c>
+      <c r="N43">
+        <v>-0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>-0</v>
+      </c>
+      <c r="Q43">
+        <v>-0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>6.62</v>
+      </c>
+      <c r="V43">
+        <v>0.2691056910569106</v>
+      </c>
+      <c r="W43">
+        <v>-3.521472392638037</v>
+      </c>
+      <c r="X43">
+        <v>0.06985589238700896</v>
+      </c>
+      <c r="Y43">
+        <v>-3.591328285025046</v>
+      </c>
+      <c r="Z43">
+        <v>2.631578947368421</v>
+      </c>
+      <c r="AA43">
+        <v>-0.1254506128334535</v>
+      </c>
+      <c r="AB43">
+        <v>0.05477224599380269</v>
+      </c>
+      <c r="AC43">
+        <v>-0.1802228588272562</v>
+      </c>
+      <c r="AD43">
+        <v>32.1</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>32.1</v>
+      </c>
+      <c r="AG43">
+        <v>25.48</v>
+      </c>
+      <c r="AH43">
+        <v>0.5661375661375662</v>
+      </c>
+      <c r="AI43">
+        <v>0.7920059215396003</v>
+      </c>
+      <c r="AJ43">
+        <v>0.5087859424920128</v>
+      </c>
+      <c r="AK43">
+        <v>0.7514007667354764</v>
+      </c>
+      <c r="AL43">
+        <v>1.1</v>
+      </c>
+      <c r="AM43">
+        <v>1.093</v>
+      </c>
+      <c r="AN43">
+        <v>-10.73578595317726</v>
+      </c>
+      <c r="AO43">
+        <v>-3.163636363636364</v>
+      </c>
+      <c r="AP43">
+        <v>-8.521739130434781</v>
+      </c>
+      <c r="AQ43">
+        <v>-3.183897529734675</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>J Trust Co., Ltd. (TSE:8508)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0.01674587010635891</v>
+      </c>
+      <c r="H44">
+        <v>0.01674587010635891</v>
+      </c>
+      <c r="I44">
+        <v>-0.07411178999773704</v>
+      </c>
+      <c r="J44">
+        <v>-0.07411178999773704</v>
+      </c>
+      <c r="K44">
+        <v>14.1</v>
+      </c>
+      <c r="L44">
+        <v>0.01595383570943652</v>
+      </c>
+      <c r="M44">
+        <v>24.3848</v>
+      </c>
+      <c r="N44">
+        <v>0.05962053789731052</v>
+      </c>
+      <c r="O44">
+        <v>1.729418439716312</v>
+      </c>
+      <c r="P44">
+        <v>12.0848</v>
+      </c>
+      <c r="Q44">
+        <v>0.02954718826405868</v>
+      </c>
+      <c r="R44">
+        <v>0.8570780141843973</v>
+      </c>
+      <c r="S44">
+        <v>12.3</v>
+      </c>
+      <c r="T44">
+        <v>0.5044125848889472</v>
+      </c>
+      <c r="U44">
+        <v>911.7</v>
+      </c>
+      <c r="V44">
+        <v>2.229095354523228</v>
+      </c>
+      <c r="W44">
+        <v>0.0134992819530876</v>
+      </c>
+      <c r="X44">
+        <v>0.06817260168308716</v>
+      </c>
+      <c r="Y44">
+        <v>-0.05467331972999955</v>
+      </c>
+      <c r="Z44">
+        <v>1.758805970149253</v>
+      </c>
+      <c r="AA44">
+        <v>-0.1303482587064676</v>
+      </c>
+      <c r="AB44">
+        <v>0.05502690275621884</v>
+      </c>
+      <c r="AC44">
+        <v>-0.1853751614626865</v>
+      </c>
+      <c r="AD44">
+        <v>455.1</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>455.1</v>
+      </c>
+      <c r="AG44">
+        <v>-456.6</v>
+      </c>
+      <c r="AH44">
+        <v>0.5266751533387339</v>
+      </c>
+      <c r="AI44">
+        <v>0.2766565349544073</v>
+      </c>
+      <c r="AJ44">
+        <v>9.592436974789912</v>
+      </c>
+      <c r="AK44">
+        <v>-0.6226646665757534</v>
+      </c>
+      <c r="AL44">
+        <v>3.08</v>
+      </c>
+      <c r="AM44">
+        <v>3.08</v>
+      </c>
+      <c r="AN44">
+        <v>-15.58561643835617</v>
+      </c>
+      <c r="AO44">
+        <v>-21.26623376623376</v>
+      </c>
+      <c r="AP44">
+        <v>15.63698630136986</v>
+      </c>
+      <c r="AQ44">
+        <v>-21.26623376623376</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FISCO Ltd. (TSE:3807)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>0.929637526652452</v>
+      </c>
+      <c r="H45">
+        <v>0.929637526652452</v>
+      </c>
+      <c r="I45">
+        <v>-0.8315565031982941</v>
+      </c>
+      <c r="J45">
+        <v>-0.8315565031982941</v>
+      </c>
+      <c r="K45">
+        <v>-12.5</v>
+      </c>
+      <c r="L45">
+        <v>-2.665245202558635</v>
+      </c>
+      <c r="M45">
+        <v>-0</v>
+      </c>
+      <c r="N45">
+        <v>-0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>-0</v>
+      </c>
+      <c r="Q45">
+        <v>-0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>1.58</v>
+      </c>
+      <c r="V45">
+        <v>0.03390557939914163</v>
+      </c>
+      <c r="W45">
+        <v>-2.450980392156863</v>
+      </c>
+      <c r="X45">
+        <v>0.05843614171758736</v>
+      </c>
+      <c r="Y45">
+        <v>-2.50941653387445</v>
+      </c>
+      <c r="Z45">
+        <v>1.205965543841605</v>
+      </c>
+      <c r="AA45">
+        <v>-1</v>
+      </c>
+      <c r="AB45">
+        <v>0.05841995142614535</v>
+      </c>
+      <c r="AC45">
+        <v>-1.058419951426145</v>
+      </c>
+      <c r="AD45">
+        <v>0.056</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0.056</v>
+      </c>
+      <c r="AG45">
+        <v>-1.524</v>
+      </c>
+      <c r="AH45">
+        <v>0.001200274348422497</v>
+      </c>
+      <c r="AI45">
+        <v>0.05313092979127135</v>
+      </c>
+      <c r="AJ45">
+        <v>-0.03380956606619931</v>
+      </c>
+      <c r="AK45">
+        <v>2.897338403041825</v>
+      </c>
+      <c r="AL45">
+        <v>0.007</v>
+      </c>
+      <c r="AM45">
+        <v>0.007</v>
+      </c>
+      <c r="AO45">
+        <v>-557.1428571428571</v>
+      </c>
+      <c r="AQ45">
+        <v>-557.1428571428571</v>
       </c>
     </row>
   </sheetData>
